--- a/python/table_metadata.xlsx
+++ b/python/table_metadata.xlsx
@@ -12,6 +12,9 @@
     <sheet name="Relationships" sheetId="3" r:id="rId3"/>
     <sheet name="Triggers" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$D$109</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="318">
   <si>
     <t>TableName</t>
   </si>
@@ -53,7 +56,7 @@
     <t>Subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Id is INTEGER PK for JOINs. WorkOrderNumber is TEXT never use as integer. IsDeleted=false for active. branches = Offices table. organizations = AbpOrganizationUnits table. For count by group always use COUNT(Id) with GROUP BY. For project-wise counts use ProjectId -&gt; Projects. For phase-wise counts use PhaseId -&gt; Phases.
+    <t xml:space="preserve">Id is INTEGER PK for JOINs. WorkOrderNumber is TEXT never use as integer. IsDeleted=false for active. branches = Offices table. organizations = AbpOrganizationUnits table. For count by group always use COUNT(Id) with GROUP BY. For project-wise counts use ProjectId -&gt; Projects. For phase-wise counts use PhaseId -&gt; Phases. For day-wise/daily count queries use: COUNT("WorkOrders"."Id") GROUP BY "WorkOrders"."CreationTime"::date ORDER BY date. For per-day results always cast timestamp to date using ::date.
 </t>
   </si>
   <si>
@@ -300,423 +303,405 @@
     <t>-&gt; Clients.Id</t>
   </si>
   <si>
+    <t>CreatorUserId</t>
+  </si>
+  <si>
+    <t>INTEGER FK — NEVER filter by username directly. Always JOIN AbpUsers: JOIN "AbpUsers" u ON w."CreatorUserId" = u."Id" WHERE u."UserName" = 'ssanka'</t>
+  </si>
+  <si>
+    <t>-&gt; AbpUsers.Id</t>
+  </si>
+  <si>
+    <t>TechUserId</t>
+  </si>
+  <si>
+    <t>INTEGER FK — NEVER filter by username directly. Always JOIN AbpUsers: JOIN "AbpUsers" u ON w."TechUserId" = u."Id" WHERE u."UserName" = 'value'</t>
+  </si>
+  <si>
+    <t>RequestedBy</t>
+  </si>
+  <si>
+    <t>INTEGER FK — NEVER filter by username directly. Always JOIN AbpUsers: JOIN "AbpUsers" u ON w."RequestedBy" = u."Id" WHERE u."UserName" = 'value'</t>
+  </si>
+  <si>
+    <t>SchedulerId</t>
+  </si>
+  <si>
+    <t>Scheduler assigned.</t>
+  </si>
+  <si>
+    <t>-&gt; Schedulers.Id</t>
+  </si>
+  <si>
+    <t>WorkFlowStateId</t>
+  </si>
+  <si>
+    <t>Current workflow state.</t>
+  </si>
+  <si>
+    <t>-&gt; WorkflowStates.Id</t>
+  </si>
+  <si>
+    <t>StartDate</t>
+  </si>
+  <si>
+    <t>Scheduled start date/time.</t>
+  </si>
+  <si>
+    <t>EndDate</t>
+  </si>
+  <si>
+    <t>Scheduled end date/time.</t>
+  </si>
+  <si>
+    <t>FieldUserIds</t>
+  </si>
+  <si>
+    <t>Comma-separated string of field user IDs. Use LIKE '%userId%' to search. Not a proper FK.</t>
+  </si>
+  <si>
+    <t>FormIds</t>
+  </si>
+  <si>
+    <t>Comma-separated form IDs. Use WorkOrderTests for proper form queries.</t>
+  </si>
+  <si>
+    <t>IsFailedTest</t>
+  </si>
+  <si>
+    <t>True if this WO has a failed test result.</t>
+  </si>
+  <si>
+    <t>IsCertified</t>
+  </si>
+  <si>
+    <t>True if WO is certified.</t>
+  </si>
+  <si>
+    <t>WorkOrderType</t>
+  </si>
+  <si>
+    <t>Type code integer.</t>
+  </si>
+  <si>
+    <t>Primary key integer.</t>
+  </si>
+  <si>
+    <t>Human-readable project name. ALWAYS USE FOR DISPLAY.</t>
+  </si>
+  <si>
+    <t>ProjectNumber</t>
+  </si>
+  <si>
+    <t>Unique human-readable project number e.g. 08.25001260.</t>
+  </si>
+  <si>
+    <t>Linked client.</t>
+  </si>
+  <si>
+    <t>Linked office.</t>
+  </si>
+  <si>
+    <t>-&gt; Offices.Id</t>
+  </si>
+  <si>
     <t>OrganizationId</t>
   </si>
   <si>
-    <t>Org unit this WO belongs to.</t>
+    <t>Organization unit.</t>
   </si>
   <si>
     <t>-&gt; AbpOrganizationUnits.Id</t>
   </si>
   <si>
-    <t>CreatorUserId</t>
-  </si>
-  <si>
-    <t>INTEGER FK — NEVER filter by username directly. Always JOIN AbpUsers: JOIN "AbpUsers" u ON w."CreatorUserId" = u."Id" WHERE u."UserName" = 'ssanka'</t>
-  </si>
-  <si>
-    <t>-&gt; AbpUsers.Id</t>
-  </si>
-  <si>
-    <t>TechUserId</t>
-  </si>
-  <si>
-    <t>INTEGER FK — NEVER filter by username directly. Always JOIN AbpUsers: JOIN "AbpUsers" u ON w."TechUserId" = u."Id" WHERE u."UserName" = 'value'</t>
-  </si>
-  <si>
-    <t>RequestedBy</t>
-  </si>
-  <si>
-    <t>INTEGER FK — NEVER filter by username directly. Always JOIN AbpUsers: JOIN "AbpUsers" u ON w."RequestedBy" = u."Id" WHERE u."UserName" = 'value'</t>
+    <t>PMUserId</t>
+  </si>
+  <si>
+    <t>Project Manager — links to user.</t>
+  </si>
+  <si>
+    <t>User who created this project.</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>Project status integer code.</t>
+  </si>
+  <si>
+    <t>IsDeleted</t>
+  </si>
+  <si>
+    <t>Soft delete boolean. Use = false for active.</t>
+  </si>
+  <si>
+    <t>Primary key. Referenced by WorkOrders.OfficeId and Projects.OfficeId.</t>
+  </si>
+  <si>
+    <t>Full office name e.g. Fort Myers 2, Charleston. USE FOR DISPLAY AND FILTERING WITH ILIKE.</t>
+  </si>
+  <si>
+    <t>Alternate display label for the office.</t>
+  </si>
+  <si>
+    <t>OfficeCode</t>
+  </si>
+  <si>
+    <t>Short office code.</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>3-letter abbreviation.</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>City where office is located.</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>State where office is located.</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Street address.</t>
+  </si>
+  <si>
+    <t>AreaId</t>
+  </si>
+  <si>
+    <t>Geographic area.</t>
+  </si>
+  <si>
+    <t>-&gt; Areas.Id</t>
+  </si>
+  <si>
+    <t>Soft delete. Use = false for active offices.</t>
+  </si>
+  <si>
+    <t>Primary key bigint. Referenced by many tables as CreatorUserId TechUserId etc.</t>
+  </si>
+  <si>
+    <t>Login username. Use for filtering by login name e.g. WHERE UserName = 'ssanka'.</t>
+  </si>
+  <si>
+    <t>First name of the user.</t>
+  </si>
+  <si>
+    <t>Surname</t>
+  </si>
+  <si>
+    <t>Last name of the user.</t>
+  </si>
+  <si>
+    <t>EmailAddress</t>
+  </si>
+  <si>
+    <t>User email address.</t>
+  </si>
+  <si>
+    <t>IsActive</t>
+  </si>
+  <si>
+    <t>Boolean — TRUE means user is active/enabled. USE = true TO FILTER ACTIVE USERS.</t>
+  </si>
+  <si>
+    <t>Soft delete boolean. Use = false for non-deleted users.</t>
+  </si>
+  <si>
+    <t>DefaultRole</t>
+  </si>
+  <si>
+    <t>User default role name as text string.</t>
+  </si>
+  <si>
+    <t>PhoneNumber</t>
+  </si>
+  <si>
+    <t>Phone number.</t>
+  </si>
+  <si>
+    <t>Primary key. Referenced by AbpUserRoles.RoleId.</t>
+  </si>
+  <si>
+    <t>Human-readable role name. ALWAYS USE FOR WHERE AND SELECT. e.g. Project Manager Field User Admin.</t>
+  </si>
+  <si>
+    <t>Internal GUID code. NEVER USE FOR FILTERING OR DISPLAY.</t>
+  </si>
+  <si>
+    <t>Soft delete boolean.</t>
+  </si>
+  <si>
+    <t>Primary key.</t>
+  </si>
+  <si>
+    <t>UserId</t>
+  </si>
+  <si>
+    <t>The user assigned to a role.</t>
+  </si>
+  <si>
+    <t>RoleId</t>
+  </si>
+  <si>
+    <t>The role assigned to the user.</t>
+  </si>
+  <si>
+    <t>-&gt; AbpRoles.Id</t>
+  </si>
+  <si>
+    <t>WorkOrderId</t>
+  </si>
+  <si>
+    <t>INTEGER FK to WorkOrders. NOT WorkOrderNumber.</t>
+  </si>
+  <si>
+    <t>-&gt; WorkOrders.Id</t>
+  </si>
+  <si>
+    <t>FormId</t>
+  </si>
+  <si>
+    <t>The test form type used.</t>
+  </si>
+  <si>
+    <t>-&gt; Forms.Id</t>
+  </si>
+  <si>
+    <t>RecordId</t>
+  </si>
+  <si>
+    <t>The specimen result for this test.</t>
+  </si>
+  <si>
+    <t>-&gt; SampleSpecimens.Id</t>
+  </si>
+  <si>
+    <t>Technician who performed the test.</t>
+  </si>
+  <si>
+    <t>TestNumber</t>
+  </si>
+  <si>
+    <t>Sequential test number within WO.</t>
+  </si>
+  <si>
+    <t>IsBilled</t>
+  </si>
+  <si>
+    <t>True if this test has been billed.</t>
+  </si>
+  <si>
+    <t>Soft delete.</t>
+  </si>
+  <si>
+    <t>Primary key. Referenced by WorkOrderTests.RecordId.</t>
+  </si>
+  <si>
+    <t>SampleId</t>
+  </si>
+  <si>
+    <t>Parent sample.</t>
+  </si>
+  <si>
+    <t>-&gt; Samples.Id</t>
+  </si>
+  <si>
+    <t>Project this specimen belongs to.</t>
+  </si>
+  <si>
+    <t>Human-readable specimen number.</t>
+  </si>
+  <si>
+    <t>Specimen status.</t>
+  </si>
+  <si>
+    <t>Organization unit this WO belongs to. Can represent an office/region. JOIN AbpOrganizationUnits to filter by org name.</t>
+  </si>
+  <si>
+    <t>Human-readable org unit name e.g. Fort Myers, Charleston. USE FOR DISPLAY AND FILTERING WITH ILIKE</t>
+  </si>
+  <si>
+    <t>Hierarchical code for the org unit.</t>
   </si>
   <si>
     <t>PhaseId</t>
   </si>
   <si>
-    <t>Project phase.</t>
-  </si>
-  <si>
-    <t>-&gt; Phases.Id</t>
-  </si>
-  <si>
-    <t>SchedulerId</t>
-  </si>
-  <si>
-    <t>Scheduler assigned.</t>
-  </si>
-  <si>
-    <t>-&gt; Schedulers.Id</t>
-  </si>
-  <si>
-    <t>WorkFlowStateId</t>
-  </si>
-  <si>
-    <t>Current workflow state.</t>
-  </si>
-  <si>
-    <t>-&gt; WorkflowStates.Id</t>
+    <t>Project phase this WO belongs to. JOIN Phases to get phase name.</t>
+  </si>
+  <si>
+    <t>-&gt; Phase.Id</t>
+  </si>
+  <si>
+    <t>Primary key. Referenced by WorkOrders.PhaseId.</t>
+  </si>
+  <si>
+    <t>Phase name — USE THIS for display and GROUP BY. The column is PhaseName not Name.</t>
+  </si>
+  <si>
+    <t>Soft delete. Use = false for active phases.</t>
+  </si>
+  <si>
+    <t>Primary key bigint. Referenced by WorkOrders.OrganizationId</t>
+  </si>
+  <si>
+    <t>Human-readable name e.g. Fort Myers, Charleston. USE FOR DISPLAY AND ILIKE FILTERING.</t>
+  </si>
+  <si>
+    <t>ParentId</t>
+  </si>
+  <si>
+    <t>Parent org unit for hierarchy.</t>
+  </si>
+  <si>
+    <t>Hierarchical code.</t>
+  </si>
+  <si>
+    <t>Soft delete. Use = false for active.</t>
+  </si>
+  <si>
+    <t>The role assigned to org unit.</t>
+  </si>
+  <si>
+    <t>OrganizationUnitId</t>
+  </si>
+  <si>
+    <t>The org unit.</t>
+  </si>
+  <si>
+    <t>Permission name.</t>
+  </si>
+  <si>
+    <t>IsGranted</t>
+  </si>
+  <si>
+    <t>True if permission is granted.</t>
+  </si>
+  <si>
+    <t>Role this permission belongs to.</t>
+  </si>
+  <si>
+    <t>User this permission belongs to.</t>
+  </si>
+  <si>
+    <t>CreationTime</t>
+  </si>
+  <si>
+    <t>Date the WO was CREATED in DB. For date range: "WorkOrders"."CreationTime" &gt;= 'YYYY-MM-DD' AND "WorkOrders"."CreationTime" &lt; 'YYYY-MM-DD'. For today: "WorkOrders"."CreationTime"::date = CURRENT_DATE. For day-wise count: SELECT "WorkOrders"."CreationTime"::date AS "Date", COUNT("WorkOrders"."Id") AS "Count" GROUP BY "WorkOrders"."CreationTime"::date ORDER BY "Date". Never use BETWEEN for timestamps.</t>
   </si>
   <si>
     <t>RequestedOn</t>
   </si>
   <si>
-    <t>Date/time WO was REQUESTED. Use for date range queries e.g. BETWEEN '2025-07-01' AND '2025-07-07'.</t>
-  </si>
-  <si>
-    <t>StartDate</t>
-  </si>
-  <si>
-    <t>Scheduled start date/time.</t>
-  </si>
-  <si>
-    <t>EndDate</t>
-  </si>
-  <si>
-    <t>Scheduled end date/time.</t>
-  </si>
-  <si>
-    <t>CreationTime</t>
-  </si>
-  <si>
-    <t>Database record creation timestamp.</t>
-  </si>
-  <si>
-    <t>FieldUserIds</t>
-  </si>
-  <si>
-    <t>Comma-separated string of field user IDs. Use LIKE '%userId%' to search. Not a proper FK.</t>
-  </si>
-  <si>
-    <t>FormIds</t>
-  </si>
-  <si>
-    <t>Comma-separated form IDs. Use WorkOrderTests for proper form queries.</t>
-  </si>
-  <si>
-    <t>IsDeleted</t>
-  </si>
-  <si>
-    <t>Soft delete boolean. ALWAYS filter = false for active records.</t>
-  </si>
-  <si>
-    <t>IsFailedTest</t>
-  </si>
-  <si>
-    <t>True if this WO has a failed test result.</t>
-  </si>
-  <si>
-    <t>IsCertified</t>
-  </si>
-  <si>
-    <t>True if WO is certified.</t>
-  </si>
-  <si>
-    <t>WorkOrderType</t>
-  </si>
-  <si>
-    <t>Type code integer.</t>
-  </si>
-  <si>
-    <t>Primary key integer.</t>
-  </si>
-  <si>
-    <t>Human-readable project name. ALWAYS USE FOR DISPLAY.</t>
-  </si>
-  <si>
-    <t>ProjectNumber</t>
-  </si>
-  <si>
-    <t>Unique human-readable project number e.g. 08.25001260.</t>
-  </si>
-  <si>
-    <t>Linked client.</t>
-  </si>
-  <si>
-    <t>Linked office.</t>
-  </si>
-  <si>
-    <t>-&gt; Offices.Id</t>
-  </si>
-  <si>
-    <t>Organization unit.</t>
-  </si>
-  <si>
-    <t>PMUserId</t>
-  </si>
-  <si>
-    <t>Project Manager — links to user.</t>
-  </si>
-  <si>
-    <t>User who created this project.</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>Project status integer code.</t>
-  </si>
-  <si>
-    <t>Soft delete boolean. Use = false for active.</t>
-  </si>
-  <si>
-    <t>Primary key. Referenced by WorkOrders.OfficeId and Projects.OfficeId.</t>
-  </si>
-  <si>
-    <t>Full office name e.g. Fort Myers 2, Charleston. USE FOR DISPLAY AND FILTERING WITH ILIKE.</t>
-  </si>
-  <si>
-    <t>Alternate display label for the office.</t>
-  </si>
-  <si>
-    <t>OfficeCode</t>
-  </si>
-  <si>
-    <t>Short office code.</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>3-letter abbreviation.</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>City where office is located.</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>State where office is located.</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Street address.</t>
-  </si>
-  <si>
-    <t>AreaId</t>
-  </si>
-  <si>
-    <t>Geographic area.</t>
-  </si>
-  <si>
-    <t>-&gt; Areas.Id</t>
-  </si>
-  <si>
-    <t>Soft delete. Use = false for active offices.</t>
-  </si>
-  <si>
-    <t>Primary key bigint. Referenced by many tables as CreatorUserId TechUserId etc.</t>
-  </si>
-  <si>
-    <t>Login username. Use for filtering by login name e.g. WHERE UserName = 'ssanka'.</t>
-  </si>
-  <si>
-    <t>First name of the user.</t>
-  </si>
-  <si>
-    <t>Surname</t>
-  </si>
-  <si>
-    <t>Last name of the user.</t>
-  </si>
-  <si>
-    <t>EmailAddress</t>
-  </si>
-  <si>
-    <t>User email address.</t>
-  </si>
-  <si>
-    <t>IsActive</t>
-  </si>
-  <si>
-    <t>Boolean — TRUE means user is active/enabled. USE = true TO FILTER ACTIVE USERS.</t>
-  </si>
-  <si>
-    <t>Soft delete boolean. Use = false for non-deleted users.</t>
-  </si>
-  <si>
-    <t>DefaultRole</t>
-  </si>
-  <si>
-    <t>User default role name as text string.</t>
-  </si>
-  <si>
-    <t>PhoneNumber</t>
-  </si>
-  <si>
-    <t>Phone number.</t>
-  </si>
-  <si>
-    <t>Primary key. Referenced by AbpUserRoles.RoleId.</t>
-  </si>
-  <si>
-    <t>Human-readable role name. ALWAYS USE FOR WHERE AND SELECT. e.g. Project Manager Field User Admin.</t>
-  </si>
-  <si>
-    <t>Internal GUID code. NEVER USE FOR FILTERING OR DISPLAY.</t>
-  </si>
-  <si>
-    <t>Soft delete boolean.</t>
-  </si>
-  <si>
-    <t>Primary key.</t>
-  </si>
-  <si>
-    <t>UserId</t>
-  </si>
-  <si>
-    <t>The user assigned to a role.</t>
-  </si>
-  <si>
-    <t>RoleId</t>
-  </si>
-  <si>
-    <t>The role assigned to the user.</t>
-  </si>
-  <si>
-    <t>-&gt; AbpRoles.Id</t>
-  </si>
-  <si>
-    <t>WorkOrderId</t>
-  </si>
-  <si>
-    <t>INTEGER FK to WorkOrders. NOT WorkOrderNumber.</t>
-  </si>
-  <si>
-    <t>-&gt; WorkOrders.Id</t>
-  </si>
-  <si>
-    <t>FormId</t>
-  </si>
-  <si>
-    <t>The test form type used.</t>
-  </si>
-  <si>
-    <t>-&gt; Forms.Id</t>
-  </si>
-  <si>
-    <t>RecordId</t>
-  </si>
-  <si>
-    <t>The specimen result for this test.</t>
-  </si>
-  <si>
-    <t>-&gt; SampleSpecimens.Id</t>
-  </si>
-  <si>
-    <t>Technician who performed the test.</t>
-  </si>
-  <si>
-    <t>TestNumber</t>
-  </si>
-  <si>
-    <t>Sequential test number within WO.</t>
-  </si>
-  <si>
-    <t>IsBilled</t>
-  </si>
-  <si>
-    <t>True if this test has been billed.</t>
-  </si>
-  <si>
-    <t>Soft delete.</t>
-  </si>
-  <si>
-    <t>Primary key. Referenced by WorkOrderTests.RecordId.</t>
-  </si>
-  <si>
-    <t>SampleId</t>
-  </si>
-  <si>
-    <t>Parent sample.</t>
-  </si>
-  <si>
-    <t>-&gt; Samples.Id</t>
-  </si>
-  <si>
-    <t>Project this specimen belongs to.</t>
-  </si>
-  <si>
-    <t>Human-readable specimen number.</t>
-  </si>
-  <si>
-    <t>Specimen status.</t>
-  </si>
-  <si>
-    <t>Organization unit this WO belongs to. Can represent an office/region. JOIN AbpOrganizationUnits to filter by org name.</t>
-  </si>
-  <si>
-    <t>Human-readable org unit name e.g. Fort Myers, Charleston. USE FOR DISPLAY AND FILTERING WITH ILIKE</t>
-  </si>
-  <si>
-    <t>Hierarchical code for the org unit.</t>
-  </si>
-  <si>
-    <t>Project phase this WO belongs to. JOIN Phases to get phase name.</t>
-  </si>
-  <si>
-    <t>-&gt; Phase.Id</t>
-  </si>
-  <si>
-    <t>Primary key. Referenced by WorkOrders.PhaseId.</t>
-  </si>
-  <si>
-    <t>Phase name — USE THIS for display and GROUP BY. The column is PhaseName not Name.</t>
-  </si>
-  <si>
-    <t>Soft delete. Use = false for active phases.</t>
-  </si>
-  <si>
-    <t>Primary key bigint. Referenced by WorkOrders.OrganizationId</t>
-  </si>
-  <si>
-    <t>Human-readable name e.g. Fort Myers, Charleston. USE FOR DISPLAY AND ILIKE FILTERING.</t>
-  </si>
-  <si>
-    <t>ParentId</t>
-  </si>
-  <si>
-    <t>Parent org unit for hierarchy.</t>
-  </si>
-  <si>
-    <t>Hierarchical code.</t>
-  </si>
-  <si>
-    <t>Soft delete. Use = false for active.</t>
-  </si>
-  <si>
-    <t>The role assigned to org unit.</t>
-  </si>
-  <si>
-    <t>OrganizationUnitId</t>
-  </si>
-  <si>
-    <t>The org unit.</t>
-  </si>
-  <si>
-    <t>Permission name.</t>
-  </si>
-  <si>
-    <t>IsGranted</t>
-  </si>
-  <si>
-    <t>True if permission is granted.</t>
-  </si>
-  <si>
-    <t>Role this permission belongs to.</t>
-  </si>
-  <si>
-    <t>User this permission belongs to.</t>
-  </si>
-  <si>
-    <t>Date the WO record was CREATED in DB. Use for date queries. For today: CreationTime::date = CURRENT_DATE. For this week: CreationTime &gt;= date_trunc('week', CURRENT_DATE). For this month: CreationTime &gt;= date_trunc('month', CURRENT_DATE). For last 30 days: CreationTime &gt;= CURRENT_DATE - INTERVAL '30 days'. For specific range: CreationTime BETWEEN 'start_date' AND 'end_date'.</t>
-  </si>
-  <si>
     <t>Date the work order was REQUESTED by the user. Different from creation date.</t>
   </si>
   <si>
@@ -768,7 +753,7 @@
     <t>Soft delete. Always write "Projects"."IsDeleted" = false — never bare "IsDeleted"</t>
   </si>
   <si>
-    <t>Soft delete. Always write "WorkOrders"."IsDeleted" = false — never bare "IsDeleted"</t>
+    <t>Soft delete. Always write "WorkOrders"."IsDeleted" = false — never bare "IsDeleted".</t>
   </si>
   <si>
     <t>Soft delete. Always write "AbpUsers"."IsDeleted" = false — never bare "IsDeleted"</t>
@@ -2333,13 +2318,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D114"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="65" style="4" customWidth="1"/>
+    <col min="3" max="3" width="81.8888888888889" style="4" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2454,45 +2439,45 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:4">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>94</v>
+      <c r="D11" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4">
@@ -2500,13 +2485,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4">
@@ -2524,31 +2509,31 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>107</v>
+      <c r="D15" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4">
@@ -2556,10 +2541,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>22</v>
@@ -2570,1032 +2555,1023 @@
         <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:4">
+      <c r="A18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C18" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" spans="1:4">
-      <c r="A18" s="2" t="s">
+      <c r="D18" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:4">
+      <c r="A19" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" spans="1:4">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:4">
+      <c r="A20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1" spans="1:4">
-      <c r="A20" s="2" t="s">
+      <c r="D20" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A22" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A24" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A28" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A30" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="40" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A50" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A55" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="59" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="60" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="61" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A65" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A66" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="67" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A67" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A68" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A69" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A70" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1" spans="1:4">
+      <c r="A71" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1" spans="1:4">
-      <c r="A21" s="3" t="s">
+      <c r="B71" t="s">
+        <v>123</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="72" ht="28.8" hidden="1" spans="1:4">
+      <c r="A72" t="s">
+        <v>59</v>
+      </c>
+      <c r="B72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="73" hidden="1" spans="1:4">
+      <c r="A73" t="s">
+        <v>59</v>
+      </c>
+      <c r="B73" t="s">
+        <v>138</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
         <v>4</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1" spans="1:4">
-      <c r="A22" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1" spans="1:4">
-      <c r="A23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1" spans="1:4">
-      <c r="A24" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1" spans="1:4">
-      <c r="A25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1" spans="1:4">
-      <c r="A26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1" spans="1:4">
-      <c r="A27" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1" spans="1:4">
-      <c r="A28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C28" s="5" t="s">
+      <c r="B74" t="s">
+        <v>199</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D74" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="75" hidden="1" spans="1:4">
+      <c r="A75" t="s">
+        <v>50</v>
+      </c>
+      <c r="B75" t="s">
+        <v>74</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="76" ht="28.8" hidden="1" spans="1:4">
+      <c r="A76" t="s">
+        <v>50</v>
+      </c>
+      <c r="B76" t="s">
+        <v>52</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="77" hidden="1" spans="1:4">
+      <c r="A77" t="s">
+        <v>50</v>
+      </c>
+      <c r="B77" t="s">
         <v>131</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1" spans="1:4">
-      <c r="A29" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1" spans="1:4">
-      <c r="A30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1" spans="1:4">
-      <c r="A31" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1" spans="1:4">
-      <c r="A33" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1" spans="1:4">
-      <c r="A34" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1" spans="1:4">
-      <c r="A35" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1" spans="1:4">
-      <c r="A36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1" spans="1:4">
-      <c r="A37" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1" spans="1:4">
-      <c r="A38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1" spans="1:4">
-      <c r="A39" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1" spans="1:4">
-      <c r="A40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1" spans="1:4">
-      <c r="A41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1" spans="1:4">
-      <c r="A42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1" spans="1:4">
-      <c r="A43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1" spans="1:4">
-      <c r="A44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1" spans="1:4">
-      <c r="A45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1" spans="1:4">
-      <c r="A46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1" spans="1:4">
-      <c r="A47" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1" spans="1:4">
-      <c r="A48" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1" spans="1:4">
-      <c r="A49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1" spans="1:4">
-      <c r="A50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1" spans="1:4">
-      <c r="A51" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1" spans="1:4">
-      <c r="A52" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1" spans="1:4">
-      <c r="A53" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1" spans="1:4">
-      <c r="A54" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1" spans="1:4">
-      <c r="A55" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1" spans="1:4">
-      <c r="A56" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1" spans="1:4">
-      <c r="A57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1" spans="1:4">
-      <c r="A58" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1" spans="1:4">
-      <c r="A59" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1" spans="1:4">
-      <c r="A60" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="61" ht="30" customHeight="1" spans="1:4">
-      <c r="A61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="62" ht="30" customHeight="1" spans="1:4">
-      <c r="A62" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" ht="30" customHeight="1" spans="1:4">
-      <c r="A63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1" spans="1:4">
-      <c r="A64" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="65" ht="30" customHeight="1" spans="1:4">
-      <c r="A65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="66" ht="30" customHeight="1" spans="1:4">
-      <c r="A66" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1" spans="1:4">
-      <c r="A67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1" spans="1:4">
-      <c r="A68" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1" spans="1:4">
-      <c r="A69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" ht="30" customHeight="1" spans="1:4">
-      <c r="A70" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="71" ht="30" customHeight="1" spans="1:4">
-      <c r="A71" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="72" ht="30" customHeight="1" spans="1:4">
-      <c r="A72" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="73" ht="30" customHeight="1" spans="1:4">
-      <c r="A73" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74" ht="30" customHeight="1" spans="1:4">
-      <c r="A74" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C74" s="5" t="s">
+      <c r="C77" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" ht="30" customHeight="1" spans="1:4">
-      <c r="A75" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="76" ht="30" customHeight="1" spans="1:4">
-      <c r="A76" t="s">
-        <v>4</v>
-      </c>
-      <c r="B76" t="s">
-        <v>89</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="77" ht="28.8" spans="1:4">
-      <c r="A77" t="s">
-        <v>59</v>
-      </c>
-      <c r="B77" t="s">
-        <v>18</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
+    </row>
+    <row r="78" hidden="1" spans="1:4">
       <c r="A78" t="s">
         <v>59</v>
       </c>
       <c r="B78" t="s">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="C78" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="79" ht="28.8" hidden="1" spans="1:4">
+      <c r="A79" t="s">
+        <v>59</v>
+      </c>
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="80" hidden="1" spans="1:4">
+      <c r="A80" t="s">
+        <v>59</v>
+      </c>
+      <c r="B80" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" t="s">
+      <c r="C80" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D80" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="81" hidden="1" spans="1:4">
+      <c r="A81" t="s">
+        <v>59</v>
+      </c>
+      <c r="B81" t="s">
+        <v>138</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="82" hidden="1" spans="1:4">
+      <c r="A82" t="s">
+        <v>59</v>
+      </c>
+      <c r="B82" t="s">
+        <v>131</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="83" hidden="1" spans="1:4">
+      <c r="A83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B83" t="s">
+        <v>171</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D83" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="84" hidden="1" spans="1:4">
+      <c r="A84" t="s">
+        <v>62</v>
+      </c>
+      <c r="B84" t="s">
+        <v>212</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D84" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="85" hidden="1" spans="1:4">
+      <c r="A85" t="s">
+        <v>62</v>
+      </c>
+      <c r="B85" t="s">
+        <v>131</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="86" hidden="1" spans="1:4">
+      <c r="A86" t="s">
+        <v>65</v>
+      </c>
+      <c r="B86" t="s">
+        <v>74</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="87" hidden="1" spans="1:4">
+      <c r="A87" t="s">
+        <v>65</v>
+      </c>
+      <c r="B87" t="s">
+        <v>42</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="88" hidden="1" spans="1:4">
+      <c r="A88" t="s">
+        <v>65</v>
+      </c>
+      <c r="B88" t="s">
+        <v>215</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="89" hidden="1" spans="1:4">
+      <c r="A89" t="s">
+        <v>65</v>
+      </c>
+      <c r="B89" t="s">
+        <v>171</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D89" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="90" hidden="1" spans="1:4">
+      <c r="A90" t="s">
+        <v>65</v>
+      </c>
+      <c r="B90" t="s">
+        <v>169</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D90" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="91" ht="115.2" spans="1:4">
+      <c r="A91" t="s">
         <v>4</v>
       </c>
-      <c r="B79" t="s">
-        <v>99</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="D79" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" t="s">
-        <v>50</v>
-      </c>
-      <c r="B80" t="s">
-        <v>74</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="81" ht="28.8" spans="1:4">
-      <c r="A81" t="s">
-        <v>50</v>
-      </c>
-      <c r="B81" t="s">
-        <v>52</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" t="s">
-        <v>50</v>
-      </c>
-      <c r="B82" t="s">
-        <v>120</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" t="s">
-        <v>59</v>
-      </c>
-      <c r="B83" t="s">
-        <v>74</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="84" ht="28.8" spans="1:4">
-      <c r="A84" t="s">
-        <v>59</v>
-      </c>
-      <c r="B84" t="s">
-        <v>18</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" t="s">
-        <v>59</v>
-      </c>
-      <c r="B85" t="s">
-        <v>215</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="D85" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" t="s">
-        <v>59</v>
-      </c>
-      <c r="B86" t="s">
-        <v>147</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" t="s">
-        <v>59</v>
-      </c>
-      <c r="B87" t="s">
-        <v>120</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" t="s">
-        <v>62</v>
-      </c>
-      <c r="B88" t="s">
-        <v>180</v>
-      </c>
-      <c r="C88" s="4" t="s">
+      <c r="B91" t="s">
         <v>219</v>
       </c>
-      <c r="D88" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" t="s">
-        <v>62</v>
-      </c>
-      <c r="B89" t="s">
+      <c r="C91" s="8" t="s">
         <v>220</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D89" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" t="s">
-        <v>62</v>
-      </c>
-      <c r="B90" t="s">
-        <v>120</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" t="s">
-        <v>65</v>
-      </c>
-      <c r="B91" t="s">
-        <v>74</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="B92" t="s">
-        <v>42</v>
+        <v>221</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" hidden="1" spans="1:4">
       <c r="A93" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B93" t="s">
         <v>223</v>
@@ -3604,253 +3580,200 @@
         <v>224</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" hidden="1" spans="1:4">
       <c r="A94" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D94" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="95" hidden="1" spans="1:4">
       <c r="A95" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>178</v>
+        <v>227</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="D95" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" ht="86.4" spans="1:4">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="96" hidden="1" spans="1:4">
       <c r="A96" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="B96" t="s">
-        <v>114</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+        <v>229</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="97" hidden="1" spans="1:4">
       <c r="A97" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="98" hidden="1" spans="1:4">
       <c r="A98" t="s">
         <v>68</v>
       </c>
       <c r="B98" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="99" hidden="1" spans="1:4">
       <c r="A99" t="s">
         <v>68</v>
       </c>
       <c r="B99" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
+        <v>235</v>
+      </c>
+      <c r="D99" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="100" ht="28.8" hidden="1" spans="1:4">
       <c r="A100" t="s">
         <v>68</v>
       </c>
       <c r="B100" t="s">
-        <v>233</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
+        <v>126</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D100" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" ht="28.8" hidden="1" spans="1:4">
       <c r="A101" t="s">
         <v>68</v>
       </c>
       <c r="B101" t="s">
-        <v>235</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
+        <v>89</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D101" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="102" ht="28.8" hidden="1" spans="1:4">
       <c r="A102" t="s">
         <v>68</v>
       </c>
       <c r="B102" t="s">
-        <v>114</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
+        <v>131</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="103" ht="28.8" spans="1:4">
       <c r="A103" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="B103" t="s">
-        <v>238</v>
-      </c>
-      <c r="C103" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C103" s="9" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" ht="28.8" hidden="1" spans="1:4">
       <c r="A104" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
+        <v>131</v>
+      </c>
+      <c r="C104" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="C104" s="4" t="s">
+    </row>
+    <row r="105" ht="28.8" hidden="1" spans="1:4">
+      <c r="A105" t="s">
+        <v>59</v>
+      </c>
+      <c r="B105" t="s">
+        <v>131</v>
+      </c>
+      <c r="C105" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="D104" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="105" ht="28.8" spans="1:4">
-      <c r="A105" t="s">
-        <v>68</v>
-      </c>
-      <c r="B105" t="s">
-        <v>136</v>
-      </c>
-      <c r="C105" s="8" t="s">
+    </row>
+    <row r="106" ht="28.8" hidden="1" spans="1:4">
+      <c r="A106" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" t="s">
+        <v>131</v>
+      </c>
+      <c r="C106" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="D105" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="106" ht="28.8" spans="1:4">
-      <c r="A106" t="s">
-        <v>68</v>
-      </c>
-      <c r="B106" t="s">
-        <v>92</v>
-      </c>
-      <c r="C106" s="8" t="s">
+    </row>
+    <row r="107" ht="28.8" hidden="1" spans="1:4">
+      <c r="A107" t="s">
+        <v>16</v>
+      </c>
+      <c r="B107" t="s">
+        <v>131</v>
+      </c>
+      <c r="C107" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="D106" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="107" ht="28.8" spans="1:4">
-      <c r="A107" t="s">
-        <v>68</v>
-      </c>
-      <c r="B107" t="s">
-        <v>120</v>
-      </c>
-      <c r="C107" s="9" t="s">
+    </row>
+    <row r="108" hidden="1" spans="1:4">
+      <c r="A108" t="s">
+        <v>40</v>
+      </c>
+      <c r="B108" t="s">
+        <v>131</v>
+      </c>
+      <c r="C108" s="9" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="108" ht="28.8" spans="1:4">
-      <c r="A108" t="s">
-        <v>4</v>
-      </c>
-      <c r="B108" t="s">
-        <v>120</v>
-      </c>
-      <c r="C108" s="9" t="s">
+    <row r="109" ht="28.8" hidden="1" spans="1:4">
+      <c r="A109" t="s">
+        <v>50</v>
+      </c>
+      <c r="B109" t="s">
+        <v>131</v>
+      </c>
+      <c r="C109" s="9" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="109" ht="28.8" spans="1:4">
-      <c r="A109" t="s">
-        <v>12</v>
-      </c>
-      <c r="B109" t="s">
-        <v>120</v>
-      </c>
-      <c r="C109" s="9" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="110" ht="28.8" spans="1:4">
-      <c r="A110" t="s">
-        <v>59</v>
-      </c>
-      <c r="B110" t="s">
-        <v>120</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="111" ht="28.8" spans="1:4">
-      <c r="A111" t="s">
-        <v>8</v>
-      </c>
-      <c r="B111" t="s">
-        <v>120</v>
-      </c>
-      <c r="C111" s="9" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="112" ht="28.8" spans="1:4">
-      <c r="A112" t="s">
-        <v>16</v>
-      </c>
-      <c r="B112" t="s">
-        <v>120</v>
-      </c>
-      <c r="C112" s="9" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" t="s">
-        <v>40</v>
-      </c>
-      <c r="B113" t="s">
-        <v>120</v>
-      </c>
-      <c r="C113" s="9" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="114" ht="28.8" spans="1:3">
-      <c r="A114" t="s">
-        <v>50</v>
-      </c>
-      <c r="B114" t="s">
-        <v>120</v>
-      </c>
-      <c r="C114" s="9" t="s">
-        <v>251</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D109" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="WorkOrders"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -3869,19 +3792,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5">
@@ -3898,7 +3821,7 @@
         <v>74</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5">
@@ -3915,7 +3838,7 @@
         <v>74</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5">
@@ -3923,7 +3846,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>59</v>
@@ -3932,7 +3855,7 @@
         <v>74</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5">
@@ -3940,7 +3863,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>12</v>
@@ -3949,7 +3872,7 @@
         <v>74</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5">
@@ -3957,7 +3880,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>12</v>
@@ -3966,7 +3889,7 @@
         <v>74</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5">
@@ -3974,7 +3897,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>12</v>
@@ -3983,7 +3906,7 @@
         <v>74</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5">
@@ -3991,7 +3914,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>50</v>
@@ -4000,7 +3923,7 @@
         <v>74</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5">
@@ -4008,16 +3931,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5">
@@ -4025,16 +3948,16 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5">
@@ -4042,16 +3965,16 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5">
@@ -4059,7 +3982,7 @@
         <v>68</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>12</v>
@@ -4068,7 +3991,7 @@
         <v>74</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5">
@@ -4085,7 +4008,7 @@
         <v>74</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5">
@@ -4093,7 +4016,7 @@
         <v>68</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>12</v>
@@ -4102,7 +4025,7 @@
         <v>74</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5">
@@ -4119,7 +4042,7 @@
         <v>74</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5">
@@ -4127,7 +4050,7 @@
         <v>68</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>59</v>
@@ -4136,7 +4059,7 @@
         <v>74</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5">
@@ -4144,7 +4067,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>12</v>
@@ -4153,7 +4076,7 @@
         <v>74</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:5">
@@ -4161,7 +4084,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>16</v>
@@ -4170,7 +4093,7 @@
         <v>74</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:5">
@@ -4178,7 +4101,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>4</v>
@@ -4187,7 +4110,7 @@
         <v>74</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:5">
@@ -4195,7 +4118,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>47</v>
@@ -4204,7 +4127,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:5">
@@ -4212,7 +4135,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>33</v>
@@ -4221,7 +4144,7 @@
         <v>74</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:5">
@@ -4229,7 +4152,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>12</v>
@@ -4238,7 +4161,7 @@
         <v>74</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:5">
@@ -4246,7 +4169,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>4</v>
@@ -4255,7 +4178,7 @@
         <v>74</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:5">
@@ -4263,7 +4186,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>12</v>
@@ -4272,7 +4195,7 @@
         <v>74</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:5">
@@ -4280,7 +4203,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>4</v>
@@ -4289,7 +4212,7 @@
         <v>74</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:5">
@@ -4297,7 +4220,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>44</v>
@@ -4306,7 +4229,7 @@
         <v>74</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:5">
@@ -4314,16 +4237,16 @@
         <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:5">
@@ -4340,7 +4263,7 @@
         <v>74</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:5">
@@ -4348,7 +4271,7 @@
         <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>4</v>
@@ -4357,7 +4280,7 @@
         <v>74</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:5">
@@ -4365,7 +4288,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>47</v>
@@ -4374,7 +4297,7 @@
         <v>74</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:5">
@@ -4382,7 +4305,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>12</v>
@@ -4391,7 +4314,7 @@
         <v>74</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:5">
@@ -4399,16 +4322,16 @@
         <v>8</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -4416,7 +4339,7 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
         <v>59</v>
@@ -4425,7 +4348,7 @@
         <v>74</v>
       </c>
       <c r="E33" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -4433,16 +4356,16 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="C34" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D34" t="s">
         <v>74</v>
       </c>
       <c r="E34" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -4450,7 +4373,7 @@
         <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
@@ -4459,7 +4382,7 @@
         <v>74</v>
       </c>
       <c r="E35" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -4467,7 +4390,7 @@
         <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C36" t="s">
         <v>59</v>
@@ -4476,7 +4399,7 @@
         <v>74</v>
       </c>
       <c r="E36" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -4484,7 +4407,7 @@
         <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C37" t="s">
         <v>16</v>
@@ -4493,7 +4416,7 @@
         <v>74</v>
       </c>
       <c r="E37" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -4501,7 +4424,7 @@
         <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -4510,7 +4433,7 @@
         <v>74</v>
       </c>
       <c r="E38" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -4518,7 +4441,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C39" t="s">
         <v>68</v>
@@ -4527,7 +4450,7 @@
         <v>74</v>
       </c>
       <c r="E39" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4552,10 +4475,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4563,10 +4486,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4574,10 +4497,10 @@
         <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4585,10 +4508,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C4" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4596,10 +4519,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C5" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4607,10 +4530,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C6" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4618,10 +4541,10 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="C7" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4629,10 +4552,10 @@
         <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C8" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4640,10 +4563,10 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C9" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4651,10 +4574,10 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C10" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4662,10 +4585,10 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C11" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4673,10 +4596,10 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C12" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4684,10 +4607,10 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C13" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4695,10 +4618,10 @@
         <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C14" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4706,10 +4629,10 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C15" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4717,32 +4640,32 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C16" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B17" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C17" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B18" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C18" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4750,10 +4673,10 @@
         <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C19" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4761,10 +4684,10 @@
         <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C20" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/python/table_metadata.xlsx
+++ b/python/table_metadata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10440" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="317">
   <si>
     <t>TableName</t>
   </si>
@@ -53,223 +53,222 @@
     <t>Core work order records. Central table — almost every query involves this table. Each WO belongs to a project and an office.</t>
   </si>
   <si>
+    <t>WorkOrderNumber</t>
+  </si>
+  <si>
+    <t>Id is INTEGER PK for JOINs. WorkOrderNumber is TEXT never use as integer. IsDeleted=false for active. OfficeId is NULL for all records — NEVER USE OfficeId. branches = AbpOrganizationUnits table. organizations = AbpOrganizationUnits table. For location/branch/office/fort myers queries always JOIN AbpOrganizationUnits ON OrganizationId=Id and filter by DisplayName ILIKE. For count by group always use COUNT(Id) with GROUP BY. For project-wise counts use ProjectId -&gt; Projects. For phase-wise counts use PhaseId -&gt; Phases. For day-wise/daily count queries use: COUNT("WorkOrders"."Id") GROUP BY "WorkOrders"."CreationTime"::date ORDER BY date. For per-day results always cast timestamp to date using ::date. Always SELECT WorkOrderNumber and Subject for display.</t>
+  </si>
+  <si>
+    <t>Offices</t>
+  </si>
+  <si>
+    <t>Office/branch locations. Work orders and projects are linked to an office via OfficeId.</t>
+  </si>
+  <si>
+    <t>OfficeName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEVER JOIN this table for location filtering. OfficeId is NULL in WorkOrders and Projects. For any location/branch/city/office name filter always use AbpOrganizationUnits table instead.Offices are also called BRANCHES. Use OfficeName for display and filtering with ILIKE. To count WOs by branch: JOIN WorkOrders ON OfficeId=Id, GROUP BY OfficeName. IsDeleted=false. </t>
+  </si>
+  <si>
+    <t>AbpUsers</t>
+  </si>
+  <si>
+    <t>All users in the system: field users, project managers, admins, technicians.</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>IsActive=true for active users. Use UserName for filtering by login. Name+Surname for full name. To get users by role JOIN AbpUserRoles then AbpRoles.</t>
+  </si>
+  <si>
+    <t>AbpRoles</t>
+  </si>
+  <si>
+    <t>Role definitions. Name column contains GUIDs — NEVER use Name for filtering or display.</t>
+  </si>
+  <si>
+    <t>DisplayName</t>
+  </si>
+  <si>
+    <t>CRITICAL: ALWAYS use DisplayName for both SELECT and WHERE. Name column is GUID not readable. Known roles: Admin, User, Field User, Project Manager, Engineer of Record, Lab Manager, Dispatcher</t>
+  </si>
+  <si>
+    <t>AbpUserRoles</t>
+  </si>
+  <si>
+    <t>Junction table mapping users to roles. Use to find which users have a specific role.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>NO IsDeleted column — filter active users via AbpUsers.IsActive=true. JOIN AbpUsers ON UserId=AbpUsers.Id and JOIN AbpRoles ON RoleId=AbpRoles.Id</t>
+  </si>
+  <si>
+    <t>WorkOrderTests</t>
+  </si>
+  <si>
+    <t>Individual tests performed within a work order. One WO can have many tests.</t>
+  </si>
+  <si>
+    <t>WorkOrderId is INTEGER FK to WorkOrders.Id — not WorkOrderNumber. RecordId links to SampleSpecimens.Id for specimen data.</t>
+  </si>
+  <si>
+    <t>WorkOrderUsers</t>
+  </si>
+  <si>
+    <t>Users explicitly assigned to a work order. Tracks acceptance and rejection.</t>
+  </si>
+  <si>
+    <t>NO IsDeleted column. Filter via WorkOrders.IsDeleted. UserId-&gt;AbpUsers.Id, WorkOrderId-&gt;WorkOrders.Id</t>
+  </si>
+  <si>
+    <t>WorkOrderEquipments</t>
+  </si>
+  <si>
+    <t>Equipment items assigned to a work order.</t>
+  </si>
+  <si>
+    <t>WorkOrderId-&gt;WorkOrders.Id, EquipmentId-&gt;Equipments.Id</t>
+  </si>
+  <si>
+    <t>SampleSpecimens</t>
+  </si>
+  <si>
+    <t>Physical specimens for lab testing. NOTE: The Specimens table is EMPTY — always use SampleSpecimens.</t>
+  </si>
+  <si>
+    <t>SpecimenNumber</t>
+  </si>
+  <si>
+    <t>Does NOT link directly to WorkOrders. Path: WorkOrders -&gt; WorkOrderTests.RecordId -&gt; SampleSpecimens.Id. SampleId-&gt;Samples.Id, ProjectId-&gt;Projects.Id</t>
+  </si>
+  <si>
+    <t>FormWorkFlowStates</t>
+  </si>
+  <si>
+    <t>Tracks workflow state history of forms within work orders.</t>
+  </si>
+  <si>
+    <t>WorkOrderId-&gt;WorkOrders.Id, FormId-&gt;Forms.Id, UserId-&gt;AbpUsers.Id (user who changed state)</t>
+  </si>
+  <si>
+    <t>Clients</t>
+  </si>
+  <si>
+    <t>Client companies that own projects.</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>IsDeleted=false for active. ClientId in Projects and WorkOrders links here.</t>
+  </si>
+  <si>
+    <t>Equipments</t>
+  </si>
+  <si>
+    <t>Equipment items used in field work orders.</t>
+  </si>
+  <si>
+    <t>Referenced by WorkOrderEquipments.EquipmentId</t>
+  </si>
+  <si>
+    <t>Forms</t>
+  </si>
+  <si>
+    <t>Test form templates used in work orders.</t>
+  </si>
+  <si>
+    <t>Referenced by WorkOrderTests.FormId and FormWorkFlowStates.FormId</t>
+  </si>
+  <si>
+    <t>Phases</t>
+  </si>
+  <si>
+    <t>Project phases. WorkOrders.PhaseId links here.</t>
+  </si>
+  <si>
+    <t>PhaseName</t>
+  </si>
+  <si>
+    <t>Use PhaseName for display and GROUP BY. PhaseId in WorkOrders links here.</t>
+  </si>
+  <si>
+    <t>Regions</t>
+  </si>
+  <si>
+    <t>Geographic regions.</t>
+  </si>
+  <si>
+    <t>Departments</t>
+  </si>
+  <si>
+    <t>Departments within the organization.</t>
+  </si>
+  <si>
+    <t>IsDeleted=false for active</t>
+  </si>
+  <si>
+    <t>AbpOrganizationUnits</t>
+  </si>
+  <si>
+    <t>Organization hierarchy units: regions, divisions. WorkOrders.OrganizationId and Projects.OrganizationId link here. Organization hierarchy units. WorkOrders.OrganizationId links here. Represents branches and organizations.</t>
+  </si>
+  <si>
+    <t>THIS is the correct table for ALL location queries. Use DisplayName ILIKE for filtering by office name, city, branch or any location. JOIN via WorkOrders.OrganizationId or Projects.OrganizationId. Any office name like Charleston, Fort Myers etc will be in DisplayName column of this table. Organizations are also called ORG UNITS. Use DisplayName for display and ILIKE filtering. To count WOs by organization: JOIN WorkOrders ON OrganizationId=Id, GROUP BY DisplayName.Use DisplayName for display and ILIKE filtering. To count WOs by org: JOIN WorkOrders ON OrganizationId=Id GROUP BY DisplayName. branches and organizations both use this table.</t>
+  </si>
+  <si>
+    <t>AbpOrganizationUnitRoles</t>
+  </si>
+  <si>
+    <t>Maps roles to organization units.</t>
+  </si>
+  <si>
+    <t>RoleId-&gt;AbpRoles.Id, OrganizationUnitId-&gt;AbpOrganizationUnits.Id</t>
+  </si>
+  <si>
+    <t>AbpPermissions</t>
+  </si>
+  <si>
+    <t>Permission grants for roles and users.</t>
+  </si>
+  <si>
+    <t>RoleId-&gt;AbpRoles.Id, UserId-&gt;AbpUsers.Id. IsGranted=true for active permissions.</t>
+  </si>
+  <si>
+    <t>Projects</t>
+  </si>
+  <si>
+    <t>Stores all projects. Each project belongs to a client, office and organization. Work orders link to projects via ProjectId. Stores all projects. Each project belongs to a client, office and has an assigned Project Manager.</t>
+  </si>
+  <si>
+    <t>ProjectName</t>
+  </si>
+  <si>
+    <t>OfficeId is NULL for all records — NEVER USE OfficeId. For location/office/branch queries always JOIN AbpOrganizationUnits ON Projects.OrganizationId=AbpOrganizationUnits.Id and filter by DisplayName ILIKE.Use ProjectName for display. ProjectNumber is human-readable lookup. IsDeleted=false for active. PMUserId links to Project Manager in AbpUsers. CreatorUserId links to AbpUsers. For project-wise WO count: JOIN WorkOrders ON ProjectId=Projects.Id GROUP BY ProjectName. Use ProjectName for display. ProjectNumber is human-readable lookup ID. IsDeleted=false for active. PMUserId links to AbpUsers.Id. For project-wise WO count: JOIN WorkOrders ON WorkOrders.ProjectId=Projects.Id GROUP BY ProjectName. CreatorUserId and PMUserId are INTEGER FKs — NEVER filter by username directly, always JOIN AbpUsers.</t>
+  </si>
+  <si>
+    <t>ColumnName</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Primary key INTEGER. Use in all JOINs. NOT same as WorkOrderNumber.</t>
+  </si>
+  <si>
     <t>Subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Id is INTEGER PK for JOINs. WorkOrderNumber is TEXT never use as integer. IsDeleted=false for active. branches = Offices table. organizations = AbpOrganizationUnits table. For count by group always use COUNT(Id) with GROUP BY. For project-wise counts use ProjectId -&gt; Projects. For phase-wise counts use PhaseId -&gt; Phases. For day-wise/daily count queries use: COUNT("WorkOrders"."Id") GROUP BY "WorkOrders"."CreationTime"::date ORDER BY date. For per-day results always cast timestamp to date using ::date.
-</t>
-  </si>
-  <si>
-    <t>Offices</t>
-  </si>
-  <si>
-    <t>Office/branch locations. Work orders and projects are linked to an office via OfficeId.</t>
-  </si>
-  <si>
-    <t>OfficeName</t>
-  </si>
-  <si>
-    <t>Offices are also called BRANCHES. Use OfficeName for display and filtering with ILIKE. To count WOs by branch: JOIN WorkOrders ON OfficeId=Id, GROUP BY OfficeName. IsDeleted=false.</t>
-  </si>
-  <si>
-    <t>AbpUsers</t>
-  </si>
-  <si>
-    <t>All users in the system: field users, project managers, admins, technicians.</t>
-  </si>
-  <si>
-    <t>UserName</t>
-  </si>
-  <si>
-    <t>IsActive=true for active users. Use UserName for filtering by login. Name+Surname for full name. To get users by role JOIN AbpUserRoles then AbpRoles.</t>
-  </si>
-  <si>
-    <t>AbpRoles</t>
-  </si>
-  <si>
-    <t>Role definitions. Name column contains GUIDs — NEVER use Name for filtering or display.</t>
-  </si>
-  <si>
-    <t>DisplayName</t>
-  </si>
-  <si>
-    <t>CRITICAL: ALWAYS use DisplayName for both SELECT and WHERE. Name column is GUID not readable. Known roles: Admin, User, Field User, Project Manager, Engineer of Record, Lab Manager, Dispatcher</t>
-  </si>
-  <si>
-    <t>AbpUserRoles</t>
-  </si>
-  <si>
-    <t>Junction table mapping users to roles. Use to find which users have a specific role.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>NO IsDeleted column — filter active users via AbpUsers.IsActive=true. JOIN AbpUsers ON UserId=AbpUsers.Id and JOIN AbpRoles ON RoleId=AbpRoles.Id</t>
-  </si>
-  <si>
-    <t>WorkOrderTests</t>
-  </si>
-  <si>
-    <t>Individual tests performed within a work order. One WO can have many tests.</t>
-  </si>
-  <si>
-    <t>WorkOrderId is INTEGER FK to WorkOrders.Id — not WorkOrderNumber. RecordId links to SampleSpecimens.Id for specimen data.</t>
-  </si>
-  <si>
-    <t>WorkOrderUsers</t>
-  </si>
-  <si>
-    <t>Users explicitly assigned to a work order. Tracks acceptance and rejection.</t>
-  </si>
-  <si>
-    <t>NO IsDeleted column. Filter via WorkOrders.IsDeleted. UserId-&gt;AbpUsers.Id, WorkOrderId-&gt;WorkOrders.Id</t>
-  </si>
-  <si>
-    <t>WorkOrderEquipments</t>
-  </si>
-  <si>
-    <t>Equipment items assigned to a work order.</t>
-  </si>
-  <si>
-    <t>WorkOrderId-&gt;WorkOrders.Id, EquipmentId-&gt;Equipments.Id</t>
-  </si>
-  <si>
-    <t>SampleSpecimens</t>
-  </si>
-  <si>
-    <t>Physical specimens for lab testing. NOTE: The Specimens table is EMPTY — always use SampleSpecimens.</t>
-  </si>
-  <si>
-    <t>SpecimenNumber</t>
-  </si>
-  <si>
-    <t>Does NOT link directly to WorkOrders. Path: WorkOrders -&gt; WorkOrderTests.RecordId -&gt; SampleSpecimens.Id. SampleId-&gt;Samples.Id, ProjectId-&gt;Projects.Id</t>
-  </si>
-  <si>
-    <t>FormWorkFlowStates</t>
-  </si>
-  <si>
-    <t>Tracks workflow state history of forms within work orders.</t>
-  </si>
-  <si>
-    <t>WorkOrderId-&gt;WorkOrders.Id, FormId-&gt;Forms.Id, UserId-&gt;AbpUsers.Id (user who changed state)</t>
-  </si>
-  <si>
-    <t>Clients</t>
-  </si>
-  <si>
-    <t>Client companies that own projects.</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>IsDeleted=false for active. ClientId in Projects and WorkOrders links here.</t>
-  </si>
-  <si>
-    <t>Equipments</t>
-  </si>
-  <si>
-    <t>Equipment items used in field work orders.</t>
-  </si>
-  <si>
-    <t>Referenced by WorkOrderEquipments.EquipmentId</t>
-  </si>
-  <si>
-    <t>Forms</t>
-  </si>
-  <si>
-    <t>Test form templates used in work orders.</t>
-  </si>
-  <si>
-    <t>Referenced by WorkOrderTests.FormId and FormWorkFlowStates.FormId</t>
-  </si>
-  <si>
-    <t>Phases</t>
-  </si>
-  <si>
-    <t>Project phases. WorkOrders.PhaseId links here.</t>
-  </si>
-  <si>
-    <t>PhaseName</t>
-  </si>
-  <si>
-    <t>Use PhaseName for display and GROUP BY. PhaseId in WorkOrders links here.</t>
-  </si>
-  <si>
-    <t>Regions</t>
-  </si>
-  <si>
-    <t>Geographic regions.</t>
-  </si>
-  <si>
-    <t>Departments</t>
-  </si>
-  <si>
-    <t>Departments within the organization.</t>
-  </si>
-  <si>
-    <t>IsDeleted=false for active</t>
-  </si>
-  <si>
-    <t>AbpOrganizationUnits</t>
-  </si>
-  <si>
-    <t>Organization hierarchy units: regions, divisions. WorkOrders.OrganizationId and Projects.OrganizationId link here. Organization hierarchy units. WorkOrders.OrganizationId links here. Represents branches and organizations.</t>
-  </si>
-  <si>
-    <t>Organizations are also called ORG UNITS. Use DisplayName for display and ILIKE filtering. To count WOs by organization: JOIN WorkOrders ON OrganizationId=Id, GROUP BY DisplayName.Use DisplayName for display and ILIKE filtering. To count WOs by org: JOIN WorkOrders ON OrganizationId=Id GROUP BY DisplayName. branches and organizations both use this table.</t>
-  </si>
-  <si>
-    <t>AbpOrganizationUnitRoles</t>
-  </si>
-  <si>
-    <t>Maps roles to organization units.</t>
-  </si>
-  <si>
-    <t>RoleId-&gt;AbpRoles.Id, OrganizationUnitId-&gt;AbpOrganizationUnits.Id</t>
-  </si>
-  <si>
-    <t>AbpPermissions</t>
-  </si>
-  <si>
-    <t>Permission grants for roles and users.</t>
-  </si>
-  <si>
-    <t>RoleId-&gt;AbpRoles.Id, UserId-&gt;AbpUsers.Id. IsGranted=true for active permissions.</t>
-  </si>
-  <si>
-    <t>Projects</t>
-  </si>
-  <si>
-    <t>Stores all projects. Each project belongs to a client, office and organization. Work orders link to projects via ProjectId. Stores all projects. Each project belongs to a client, office and has an assigned Project Manager.</t>
-  </si>
-  <si>
-    <t>ProjectName</t>
-  </si>
-  <si>
-    <t>Use ProjectName for display. ProjectNumber is human-readable lookup. IsDeleted=false for active. PMUserId links to Project Manager in AbpUsers. CreatorUserId links to AbpUsers. For project-wise WO count: JOIN WorkOrders ON ProjectId=Projects.Id GROUP BY ProjectName. Use ProjectName for display. ProjectNumber is human-readable lookup ID. IsDeleted=false for active. PMUserId links to AbpUsers.Id. For project-wise WO count: JOIN WorkOrders ON WorkOrders.ProjectId=Projects.Id GROUP BY ProjectName. CreatorUserId and PMUserId are INTEGER FKs — NEVER filter by username directly, always JOIN AbpUsers.</t>
-  </si>
-  <si>
-    <t>ColumnName</t>
-  </si>
-  <si>
-    <t>Relationship</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Primary key INTEGER. Use in all JOINs. NOT same as WorkOrderNumber.</t>
-  </si>
-  <si>
     <t>Work order title/name. ALWAYS USE FOR DISPLAY.</t>
   </si>
   <si>
-    <t>WorkOrderNumber</t>
-  </si>
-  <si>
     <t>Human-readable TEXT ID e.g. 08.25001260. Use only for WHERE lookups by number — never as integer FK.</t>
   </si>
   <si>
@@ -291,7 +290,7 @@
     <t>OfficeId</t>
   </si>
   <si>
-    <t>NULL for all records — NEVER USE. Use OrganizationId for all location queries.</t>
+    <t>OfficeId is NULL for all records — NEVER USE OfficeId. Use OrganizationId -&gt; AbpOrganizationUnits for all location/office/branch queries.</t>
   </si>
   <si>
     <t>ClientId</t>
@@ -399,7 +398,7 @@
     <t>Linked client.</t>
   </si>
   <si>
-    <t>Linked office.</t>
+    <t>NULL for all records — NEVER USE. Use OrganizationId -&gt; AbpOrganizationUnits for all location queries.</t>
   </si>
   <si>
     <t>-&gt; Offices.Id</t>
@@ -930,7 +929,7 @@
     <t>project,projects</t>
   </si>
   <si>
-    <t>office,offices,branch,branches,fort,myers,charleston,location</t>
+    <t>organization,organizations,org,unit,units,branch,branches,location</t>
   </si>
   <si>
     <t>user,users,username,creator,created,technician,active</t>
@@ -940,9 +939,6 @@
   </si>
   <si>
     <t>phase,phases</t>
-  </si>
-  <si>
-    <t>organization,organizations,org,unit,units,branch,branches,location</t>
   </si>
   <si>
     <t>specimen,sample,test,tests</t>
@@ -1633,7 +1629,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1650,6 +1646,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="distributed" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="distributed"/>
@@ -2014,26 +2013,26 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="65" style="8" customWidth="1"/>
+    <col min="2" max="2" width="65" style="9" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="70" style="8" customWidth="1"/>
+    <col min="4" max="4" width="70" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:4">
+    <row r="2" s="10" customFormat="1" ht="144" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -2047,7 +2046,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:4">
+    <row r="3" ht="64" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -2225,7 +2224,7 @@
       <c r="C15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2275,10 +2274,10 @@
       <c r="A19" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2286,27 +2285,27 @@
       <c r="A20" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C20" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="21" ht="129.6" spans="1:4">
+    <row r="21" ht="158.4" spans="1:4">
       <c r="A21" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="9" t="s">
         <v>69</v>
       </c>
       <c r="C21" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="9" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2342,271 +2341,271 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:4">
+    <row r="2" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:4">
+    <row r="3" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="6" t="s">
         <v>76</v>
       </c>
+      <c r="C3" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="D3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" spans="1:4">
+    <row r="4" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" spans="1:4">
+    <row r="5" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" spans="1:4">
+    <row r="6" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:4">
+    <row r="7" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>85</v>
       </c>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" ht="30" customHeight="1" spans="1:4">
+    <row r="8" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" spans="1:4">
+    <row r="9" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" spans="1:4">
+    <row r="10" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>93</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" spans="1:4">
+    <row r="11" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" spans="1:4">
+    <row r="12" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="1:4">
+    <row r="13" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>100</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="1:4">
+    <row r="14" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="3" t="s">
         <v>103</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" spans="1:4">
+    <row r="15" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" spans="1:4">
+    <row r="16" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" spans="1:4">
+    <row r="17" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="3" t="s">
         <v>109</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" spans="1:4">
+    <row r="18" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="3" t="s">
         <v>111</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" spans="1:4">
+    <row r="19" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1" spans="1:4">
+    <row r="20" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="3" t="s">
         <v>115</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="21" ht="30" customHeight="1" spans="1:4">
       <c r="A21" s="2" t="s">
         <v>68</v>
       </c>
@@ -2620,7 +2619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="22" ht="30" customHeight="1" spans="1:4">
       <c r="A22" s="3" t="s">
         <v>68</v>
       </c>
@@ -2634,7 +2633,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="23" ht="30" customHeight="1" spans="1:4">
       <c r="A23" s="2" t="s">
         <v>68</v>
       </c>
@@ -2648,7 +2647,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="24" ht="30" customHeight="1" spans="1:4">
       <c r="A24" s="3" t="s">
         <v>68</v>
       </c>
@@ -2662,7 +2661,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="25" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="25" ht="30" customHeight="1" spans="1:4">
       <c r="A25" s="2" t="s">
         <v>68</v>
       </c>
@@ -2676,7 +2675,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="26" ht="30" customHeight="1" spans="1:4">
       <c r="A26" s="3" t="s">
         <v>68</v>
       </c>
@@ -2690,7 +2689,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="27" ht="30" customHeight="1" spans="1:4">
       <c r="A27" s="2" t="s">
         <v>68</v>
       </c>
@@ -2704,7 +2703,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="28" ht="30" customHeight="1" spans="1:4">
       <c r="A28" s="3" t="s">
         <v>68</v>
       </c>
@@ -2718,7 +2717,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="29" ht="30" customHeight="1" spans="1:4">
       <c r="A29" s="2" t="s">
         <v>68</v>
       </c>
@@ -2732,7 +2731,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="30" ht="30" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
         <v>68</v>
       </c>
@@ -3306,7 +3305,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" ht="30" customHeight="1" spans="1:4">
+    <row r="71" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -3316,7 +3315,7 @@
       <c r="C71" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D71" s="11" t="s">
+      <c r="D71" s="12" t="s">
         <v>125</v>
       </c>
     </row>
@@ -3327,7 +3326,7 @@
       <c r="B72" t="s">
         <v>18</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="8" t="s">
         <v>197</v>
       </c>
     </row>
@@ -3342,14 +3341,14 @@
         <v>198</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" hidden="1" spans="1:4">
       <c r="A74" t="s">
         <v>4</v>
       </c>
       <c r="B74" t="s">
         <v>199</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="9" t="s">
         <v>200</v>
       </c>
       <c r="D74" t="s">
@@ -3367,14 +3366,14 @@
         <v>202</v>
       </c>
     </row>
-    <row r="76" ht="28.8" hidden="1" spans="1:4">
+    <row r="76" hidden="1" spans="1:4">
       <c r="A76" t="s">
         <v>50</v>
       </c>
       <c r="B76" t="s">
         <v>52</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="9" t="s">
         <v>203</v>
       </c>
     </row>
@@ -3400,14 +3399,14 @@
         <v>205</v>
       </c>
     </row>
-    <row r="79" ht="28.8" hidden="1" spans="1:4">
+    <row r="79" hidden="1" spans="1:4">
       <c r="A79" t="s">
         <v>59</v>
       </c>
       <c r="B79" t="s">
         <v>18</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="9" t="s">
         <v>206</v>
       </c>
     </row>
@@ -3547,29 +3546,29 @@
         <v>91</v>
       </c>
     </row>
-    <row r="91" ht="115.2" spans="1:4">
+    <row r="91" ht="72" hidden="1" spans="1:4">
       <c r="A91" t="s">
         <v>4</v>
       </c>
       <c r="B91" t="s">
         <v>219</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="9" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" hidden="1" spans="1:4">
       <c r="A92" t="s">
         <v>4</v>
       </c>
       <c r="B92" t="s">
         <v>221</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="9" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="93" hidden="1" spans="1:4">
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
         <v>68</v>
       </c>
@@ -3580,7 +3579,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:4">
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
         <v>68</v>
       </c>
@@ -3591,7 +3590,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:4">
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
         <v>68</v>
       </c>
@@ -3602,7 +3601,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:4">
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
         <v>68</v>
       </c>
@@ -3613,7 +3612,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:4">
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
         <v>68</v>
       </c>
@@ -3624,7 +3623,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:4">
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
         <v>68</v>
       </c>
@@ -3635,7 +3634,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:4">
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
         <v>68</v>
       </c>
@@ -3649,35 +3648,35 @@
         <v>83</v>
       </c>
     </row>
-    <row r="100" ht="28.8" hidden="1" spans="1:4">
+    <row r="100" ht="28.8" spans="1:4">
       <c r="A100" t="s">
         <v>68</v>
       </c>
       <c r="B100" t="s">
         <v>126</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C100" s="9" t="s">
         <v>236</v>
       </c>
       <c r="D100" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="101" ht="28.8" hidden="1" spans="1:4">
+    <row r="101" ht="28.8" spans="1:4">
       <c r="A101" t="s">
         <v>68</v>
       </c>
       <c r="B101" t="s">
         <v>89</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="C101" s="9" t="s">
         <v>237</v>
       </c>
       <c r="D101" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="102" ht="28.8" hidden="1" spans="1:4">
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
         <v>68</v>
       </c>
@@ -3688,7 +3687,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="103" ht="28.8" spans="1:4">
+    <row r="103" hidden="1" spans="1:4">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -3699,7 +3698,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="104" ht="28.8" hidden="1" spans="1:4">
+    <row r="104" hidden="1" spans="1:4">
       <c r="A104" t="s">
         <v>12</v>
       </c>
@@ -3710,7 +3709,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="105" ht="28.8" hidden="1" spans="1:4">
+    <row r="105" hidden="1" spans="1:4">
       <c r="A105" t="s">
         <v>59</v>
       </c>
@@ -3721,7 +3720,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="106" ht="28.8" hidden="1" spans="1:4">
+    <row r="106" hidden="1" spans="1:4">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -3732,7 +3731,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="107" ht="28.8" hidden="1" spans="1:4">
+    <row r="107" hidden="1" spans="1:4">
       <c r="A107" t="s">
         <v>16</v>
       </c>
@@ -3754,7 +3753,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="109" ht="28.8" hidden="1" spans="1:4">
+    <row r="109" hidden="1" spans="1:4">
       <c r="A109" t="s">
         <v>50</v>
       </c>
@@ -3769,7 +3768,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D109" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
-        <filter val="WorkOrders"/>
+        <filter val="Projects"/>
       </filters>
     </filterColumn>
     <extLst/>
@@ -4563,7 +4562,7 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C9" t="s">
         <v>296</v>
@@ -4574,7 +4573,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C10" t="s">
         <v>296</v>
@@ -4585,7 +4584,7 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C11" t="s">
         <v>296</v>
@@ -4596,7 +4595,7 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C12" t="s">
         <v>296</v>
@@ -4607,7 +4606,7 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C13" t="s">
         <v>296</v>
@@ -4618,7 +4617,7 @@
         <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C14" t="s">
         <v>296</v>
@@ -4629,10 +4628,10 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
+        <v>307</v>
+      </c>
+      <c r="C15" t="s">
         <v>308</v>
-      </c>
-      <c r="C15" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4640,32 +4639,32 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B17" t="s">
         <v>311</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>312</v>
-      </c>
-      <c r="C17" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" t="s">
         <v>314</v>
       </c>
-      <c r="B18" t="s">
-        <v>315</v>
-      </c>
       <c r="C18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4673,10 +4672,10 @@
         <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4684,10 +4683,10 @@
         <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/python/table_metadata.xlsx
+++ b/python/table_metadata.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="316">
   <si>
     <t>TableName</t>
   </si>
@@ -263,10 +263,7 @@
     <t>Primary key INTEGER. Use in all JOINs. NOT same as WorkOrderNumber.</t>
   </si>
   <si>
-    <t>Subject</t>
-  </si>
-  <si>
-    <t>Work order title/name. ALWAYS USE FOR DISPLAY.</t>
+    <t>Primary display column for work orders. ALWAYS USE THIS for listing and display. Human-readable ID e.g. 08.25001260.</t>
   </si>
   <si>
     <t>Human-readable TEXT ID e.g. 08.25001260. Use only for WHERE lookups by number — never as integer FK.</t>
@@ -2341,7 +2338,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="2" ht="30" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -2355,21 +2352,21 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="3" ht="30" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="D3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="4" ht="30" customHeight="1" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -2377,235 +2374,235 @@
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="5" ht="30" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="6" ht="30" customHeight="1" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" ht="30" hidden="1" customHeight="1" spans="1:4">
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="8" ht="30" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" ht="30" hidden="1" customHeight="1" spans="1:4">
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:4">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" ht="30" hidden="1" customHeight="1" spans="1:4">
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:4">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" ht="30" hidden="1" customHeight="1" spans="1:4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:4">
       <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" ht="30" hidden="1" customHeight="1" spans="1:4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:4">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" ht="30" hidden="1" customHeight="1" spans="1:4">
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" ht="30" hidden="1" customHeight="1" spans="1:4">
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:4">
       <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="15" ht="30" customHeight="1" spans="1:4">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="D15" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="16" ht="30" customHeight="1" spans="1:4">
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="D16" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="17" ht="30" customHeight="1" spans="1:4">
       <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="D17" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="18" ht="30" customHeight="1" spans="1:4">
       <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="D18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="19" ht="30" customHeight="1" spans="1:4">
       <c r="A19" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="D19" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="20" ht="30" customHeight="1" spans="1:4">
       <c r="A20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="D20" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1" spans="1:4">
+    <row r="21" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A21" s="2" t="s">
         <v>68</v>
       </c>
@@ -2613,13 +2610,13 @@
         <v>74</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1" spans="1:4">
+    <row r="22" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A22" s="3" t="s">
         <v>68</v>
       </c>
@@ -2627,119 +2624,119 @@
         <v>70</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1" spans="1:4">
+    <row r="23" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A23" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="D23" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1" spans="1:4">
+    <row r="24" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A24" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1" spans="1:4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A25" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1" spans="1:4">
+    </row>
+    <row r="26" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A26" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="D26" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1" spans="1:4">
+    </row>
+    <row r="27" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A27" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>127</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1" spans="1:4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A28" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1" spans="1:4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A29" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>130</v>
-      </c>
       <c r="D29" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1" spans="1:4">
+    <row r="30" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A30" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>22</v>
@@ -2753,7 +2750,7 @@
         <v>74</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>22</v>
@@ -2767,7 +2764,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>22</v>
@@ -2781,7 +2778,7 @@
         <v>18</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>22</v>
@@ -2792,10 +2789,10 @@
         <v>8</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>22</v>
@@ -2806,10 +2803,10 @@
         <v>8</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>22</v>
@@ -2820,10 +2817,10 @@
         <v>8</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>22</v>
@@ -2834,10 +2831,10 @@
         <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>22</v>
@@ -2848,10 +2845,10 @@
         <v>8</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>22</v>
@@ -2862,13 +2859,13 @@
         <v>8</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="40" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -2876,10 +2873,10 @@
         <v>8</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>22</v>
@@ -2893,7 +2890,7 @@
         <v>74</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>22</v>
@@ -2907,7 +2904,7 @@
         <v>14</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>22</v>
@@ -2921,7 +2918,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>22</v>
@@ -2932,10 +2929,10 @@
         <v>12</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
@@ -2946,10 +2943,10 @@
         <v>12</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>156</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>22</v>
@@ -2960,10 +2957,10 @@
         <v>12</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>22</v>
@@ -2974,10 +2971,10 @@
         <v>12</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>22</v>
@@ -2988,10 +2985,10 @@
         <v>12</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>22</v>
@@ -3002,10 +2999,10 @@
         <v>12</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>22</v>
@@ -3019,7 +3016,7 @@
         <v>74</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>22</v>
@@ -3033,7 +3030,7 @@
         <v>18</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>22</v>
@@ -3047,7 +3044,7 @@
         <v>42</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>22</v>
@@ -3058,10 +3055,10 @@
         <v>16</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>22</v>
@@ -3075,7 +3072,7 @@
         <v>74</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>22</v>
@@ -3086,13 +3083,13 @@
         <v>20</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>170</v>
-      </c>
       <c r="D55" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3100,13 +3097,13 @@
         <v>20</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="D56" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="57" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3117,7 +3114,7 @@
         <v>74</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>22</v>
@@ -3128,13 +3125,13 @@
         <v>24</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="D58" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="59" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3142,13 +3139,13 @@
         <v>24</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="D59" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="60" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3156,13 +3153,13 @@
         <v>24</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="D60" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="61" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3170,13 +3167,13 @@
         <v>24</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3184,10 +3181,10 @@
         <v>24</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>22</v>
@@ -3198,10 +3195,10 @@
         <v>24</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>22</v>
@@ -3212,10 +3209,10 @@
         <v>24</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>22</v>
@@ -3229,7 +3226,7 @@
         <v>74</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>22</v>
@@ -3240,13 +3237,13 @@
         <v>33</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C66" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="D66" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="67" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3254,13 +3251,13 @@
         <v>33</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3271,7 +3268,7 @@
         <v>35</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>22</v>
@@ -3282,10 +3279,10 @@
         <v>33</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>22</v>
@@ -3296,27 +3293,27 @@
         <v>33</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="71" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="71" ht="30" customHeight="1" spans="1:4">
       <c r="A71" t="s">
         <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" ht="28.8" hidden="1" spans="1:4">
@@ -3327,7 +3324,7 @@
         <v>18</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" hidden="1" spans="1:4">
@@ -3335,24 +3332,24 @@
         <v>59</v>
       </c>
       <c r="B73" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="74" hidden="1" spans="1:4">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>4</v>
       </c>
       <c r="B74" t="s">
+        <v>198</v>
+      </c>
+      <c r="C74" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="D74" t="s">
         <v>200</v>
-      </c>
-      <c r="D74" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="75" hidden="1" spans="1:4">
@@ -3363,7 +3360,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="76" hidden="1" spans="1:4">
@@ -3374,7 +3371,7 @@
         <v>52</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" hidden="1" spans="1:4">
@@ -3382,10 +3379,10 @@
         <v>50</v>
       </c>
       <c r="B77" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="78" hidden="1" spans="1:4">
@@ -3396,7 +3393,7 @@
         <v>74</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" hidden="1" spans="1:4">
@@ -3407,7 +3404,7 @@
         <v>18</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="80" hidden="1" spans="1:4">
@@ -3415,13 +3412,13 @@
         <v>59</v>
       </c>
       <c r="B80" t="s">
+        <v>206</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C80" s="4" t="s">
-        <v>208</v>
-      </c>
       <c r="D80" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="81" hidden="1" spans="1:4">
@@ -3429,10 +3426,10 @@
         <v>59</v>
       </c>
       <c r="B81" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="82" hidden="1" spans="1:4">
@@ -3440,10 +3437,10 @@
         <v>59</v>
       </c>
       <c r="B82" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="83" hidden="1" spans="1:4">
@@ -3451,13 +3448,13 @@
         <v>62</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D83" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" hidden="1" spans="1:4">
@@ -3465,13 +3462,13 @@
         <v>62</v>
       </c>
       <c r="B84" t="s">
+        <v>211</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>213</v>
-      </c>
       <c r="D84" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="85" hidden="1" spans="1:4">
@@ -3479,10 +3476,10 @@
         <v>62</v>
       </c>
       <c r="B85" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="86" hidden="1" spans="1:4">
@@ -3493,7 +3490,7 @@
         <v>74</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="87" hidden="1" spans="1:4">
@@ -3504,7 +3501,7 @@
         <v>42</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="88" hidden="1" spans="1:4">
@@ -3512,10 +3509,10 @@
         <v>65</v>
       </c>
       <c r="B88" t="s">
+        <v>214</v>
+      </c>
+      <c r="C88" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="89" hidden="1" spans="1:4">
@@ -3523,13 +3520,13 @@
         <v>65</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D89" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="90" hidden="1" spans="1:4">
@@ -3537,165 +3534,165 @@
         <v>65</v>
       </c>
       <c r="B90" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D90" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="91" ht="72" hidden="1" spans="1:4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" ht="72" spans="1:4">
       <c r="A91" t="s">
         <v>4</v>
       </c>
       <c r="B91" t="s">
+        <v>218</v>
+      </c>
+      <c r="C91" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="C91" s="9" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="92" hidden="1" spans="1:4">
+    </row>
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
         <v>4</v>
       </c>
       <c r="B92" t="s">
+        <v>220</v>
+      </c>
+      <c r="C92" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="C92" s="9" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+    </row>
+    <row r="93" hidden="1" spans="1:4">
       <c r="A93" t="s">
         <v>68</v>
       </c>
       <c r="B93" t="s">
+        <v>222</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
+    </row>
+    <row r="94" hidden="1" spans="1:4">
       <c r="A94" t="s">
         <v>68</v>
       </c>
       <c r="B94" t="s">
+        <v>224</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C94" s="4" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+    </row>
+    <row r="95" hidden="1" spans="1:4">
       <c r="A95" t="s">
         <v>68</v>
       </c>
       <c r="B95" t="s">
+        <v>226</v>
+      </c>
+      <c r="C95" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C95" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+    </row>
+    <row r="96" hidden="1" spans="1:4">
       <c r="A96" t="s">
         <v>68</v>
       </c>
       <c r="B96" t="s">
+        <v>228</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="C96" s="4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
+    </row>
+    <row r="97" hidden="1" spans="1:4">
       <c r="A97" t="s">
         <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="98" hidden="1" spans="1:4">
       <c r="A98" t="s">
         <v>68</v>
       </c>
       <c r="B98" t="s">
+        <v>231</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
+    </row>
+    <row r="99" hidden="1" spans="1:4">
       <c r="A99" t="s">
         <v>68</v>
       </c>
       <c r="B99" t="s">
+        <v>233</v>
+      </c>
+      <c r="C99" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C99" s="4" t="s">
-        <v>235</v>
-      </c>
       <c r="D99" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="100" ht="28.8" spans="1:4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="100" ht="28.8" hidden="1" spans="1:4">
       <c r="A100" t="s">
         <v>68</v>
       </c>
       <c r="B100" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D100" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="101" ht="28.8" spans="1:4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="101" ht="28.8" hidden="1" spans="1:4">
       <c r="A101" t="s">
         <v>68</v>
       </c>
       <c r="B101" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D101" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="102" hidden="1" spans="1:4">
       <c r="A102" t="s">
         <v>68</v>
       </c>
       <c r="B102" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="103" hidden="1" spans="1:4">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
         <v>4</v>
       </c>
       <c r="B103" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="104" hidden="1" spans="1:4">
@@ -3703,10 +3700,10 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="105" hidden="1" spans="1:4">
@@ -3714,10 +3711,10 @@
         <v>59</v>
       </c>
       <c r="B105" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="106" hidden="1" spans="1:4">
@@ -3725,10 +3722,10 @@
         <v>8</v>
       </c>
       <c r="B106" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="107" hidden="1" spans="1:4">
@@ -3736,10 +3733,10 @@
         <v>16</v>
       </c>
       <c r="B107" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="108" hidden="1" spans="1:4">
@@ -3747,10 +3744,10 @@
         <v>40</v>
       </c>
       <c r="B108" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="109" hidden="1" spans="1:4">
@@ -3758,17 +3755,17 @@
         <v>50</v>
       </c>
       <c r="B109" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D109" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
-        <filter val="Projects"/>
+        <filter val="WorkOrders"/>
       </filters>
     </filterColumn>
     <extLst/>
@@ -3791,19 +3788,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5">
@@ -3811,7 +3808,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>68</v>
@@ -3820,7 +3817,7 @@
         <v>74</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5">
@@ -3828,7 +3825,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>40</v>
@@ -3837,7 +3834,7 @@
         <v>74</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5">
@@ -3845,7 +3842,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>59</v>
@@ -3854,7 +3851,7 @@
         <v>74</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5">
@@ -3862,7 +3859,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>12</v>
@@ -3871,7 +3868,7 @@
         <v>74</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5">
@@ -3879,7 +3876,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>12</v>
@@ -3888,7 +3885,7 @@
         <v>74</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5">
@@ -3896,7 +3893,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>12</v>
@@ -3905,7 +3902,7 @@
         <v>74</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5">
@@ -3913,7 +3910,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>50</v>
@@ -3922,7 +3919,7 @@
         <v>74</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5">
@@ -3930,16 +3927,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5">
@@ -3947,16 +3944,16 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5">
@@ -3964,16 +3961,16 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5">
@@ -3981,7 +3978,7 @@
         <v>68</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>12</v>
@@ -3990,7 +3987,7 @@
         <v>74</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5">
@@ -3998,7 +3995,7 @@
         <v>68</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>40</v>
@@ -4007,7 +4004,7 @@
         <v>74</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5">
@@ -4015,7 +4012,7 @@
         <v>68</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>12</v>
@@ -4024,7 +4021,7 @@
         <v>74</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5">
@@ -4032,7 +4029,7 @@
         <v>68</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>8</v>
@@ -4041,7 +4038,7 @@
         <v>74</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5">
@@ -4049,7 +4046,7 @@
         <v>68</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>59</v>
@@ -4058,7 +4055,7 @@
         <v>74</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5">
@@ -4066,7 +4063,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>12</v>
@@ -4075,7 +4072,7 @@
         <v>74</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:5">
@@ -4083,7 +4080,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>16</v>
@@ -4092,7 +4089,7 @@
         <v>74</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:5">
@@ -4100,7 +4097,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>4</v>
@@ -4109,7 +4106,7 @@
         <v>74</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:5">
@@ -4117,7 +4114,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>47</v>
@@ -4126,7 +4123,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:5">
@@ -4134,7 +4131,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>33</v>
@@ -4143,7 +4140,7 @@
         <v>74</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:5">
@@ -4151,7 +4148,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>12</v>
@@ -4160,7 +4157,7 @@
         <v>74</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:5">
@@ -4168,7 +4165,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>4</v>
@@ -4177,7 +4174,7 @@
         <v>74</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:5">
@@ -4185,7 +4182,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>12</v>
@@ -4194,7 +4191,7 @@
         <v>74</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:5">
@@ -4202,7 +4199,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>4</v>
@@ -4211,7 +4208,7 @@
         <v>74</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:5">
@@ -4219,7 +4216,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>44</v>
@@ -4228,7 +4225,7 @@
         <v>74</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:5">
@@ -4236,16 +4233,16 @@
         <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:5">
@@ -4253,7 +4250,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>68</v>
@@ -4262,7 +4259,7 @@
         <v>74</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:5">
@@ -4270,7 +4267,7 @@
         <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>4</v>
@@ -4279,7 +4276,7 @@
         <v>74</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:5">
@@ -4287,7 +4284,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>47</v>
@@ -4296,7 +4293,7 @@
         <v>74</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:5">
@@ -4304,7 +4301,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>12</v>
@@ -4313,7 +4310,7 @@
         <v>74</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:5">
@@ -4321,16 +4318,16 @@
         <v>8</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -4338,7 +4335,7 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
         <v>59</v>
@@ -4347,7 +4344,7 @@
         <v>74</v>
       </c>
       <c r="E33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -4355,16 +4352,16 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C34" t="s">
+        <v>285</v>
+      </c>
+      <c r="D34" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" t="s">
         <v>286</v>
-      </c>
-      <c r="D34" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -4372,7 +4369,7 @@
         <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
@@ -4381,7 +4378,7 @@
         <v>74</v>
       </c>
       <c r="E35" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -4389,7 +4386,7 @@
         <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C36" t="s">
         <v>59</v>
@@ -4398,7 +4395,7 @@
         <v>74</v>
       </c>
       <c r="E36" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -4406,7 +4403,7 @@
         <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C37" t="s">
         <v>16</v>
@@ -4415,7 +4412,7 @@
         <v>74</v>
       </c>
       <c r="E37" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -4423,7 +4420,7 @@
         <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -4432,7 +4429,7 @@
         <v>74</v>
       </c>
       <c r="E38" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -4440,7 +4437,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C39" t="s">
         <v>68</v>
@@ -4449,7 +4446,7 @@
         <v>74</v>
       </c>
       <c r="E39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -4474,10 +4471,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4485,10 +4482,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C2" t="s">
         <v>295</v>
-      </c>
-      <c r="C2" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4496,10 +4493,10 @@
         <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4507,10 +4504,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4518,10 +4515,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4529,10 +4526,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4540,10 +4537,10 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4551,10 +4548,10 @@
         <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4562,10 +4559,10 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4573,10 +4570,10 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4584,10 +4581,10 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4595,10 +4592,10 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4606,10 +4603,10 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4617,10 +4614,10 @@
         <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4628,10 +4625,10 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
+        <v>306</v>
+      </c>
+      <c r="C15" t="s">
         <v>307</v>
-      </c>
-      <c r="C15" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4639,32 +4636,32 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>309</v>
+      </c>
+      <c r="B17" t="s">
         <v>310</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>311</v>
-      </c>
-      <c r="C17" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>312</v>
+      </c>
+      <c r="B18" t="s">
         <v>313</v>
       </c>
-      <c r="B18" t="s">
-        <v>314</v>
-      </c>
       <c r="C18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4672,10 +4669,10 @@
         <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4683,10 +4680,10 @@
         <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/python/table_metadata.xlsx
+++ b/python/table_metadata.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Triggers" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$D$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$D$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="317">
   <si>
     <t>TableName</t>
   </si>
@@ -56,7 +56,8 @@
     <t>WorkOrderNumber</t>
   </si>
   <si>
-    <t>Id is INTEGER PK for JOINs. WorkOrderNumber is TEXT never use as integer. IsDeleted=false for active. OfficeId is NULL for all records — NEVER USE OfficeId. branches = AbpOrganizationUnits table. organizations = AbpOrganizationUnits table. For location/branch/office/fort myers queries always JOIN AbpOrganizationUnits ON OrganizationId=Id and filter by DisplayName ILIKE. For count by group always use COUNT(Id) with GROUP BY. For project-wise counts use ProjectId -&gt; Projects. For phase-wise counts use PhaseId -&gt; Phases. For day-wise/daily count queries use: COUNT("WorkOrders"."Id") GROUP BY "WorkOrders"."CreationTime"::date ORDER BY date. For per-day results always cast timestamp to date using ::date. Always SELECT WorkOrderNumber and Subject for display.</t>
+    <t>NEVER SELECT Subject column — always use WorkOrderNumber for display.
+ Id is INTEGER PK for JOINs. WorkOrderNumber is TEXT never use as integer. IsDeleted=false for active. OfficeId is NULL for all records — NEVER USE OfficeId. branches = AbpOrganizationUnits table. organizations = AbpOrganizationUnits table. For location/branch/office/fort myers queries always JOIN AbpOrganizationUnits ON OrganizationId=Id and filter by DisplayName ILIKE. For count by group always use COUNT(Id) with GROUP BY. For project-wise counts use ProjectId -&gt; Projects. For phase-wise counts use PhaseId -&gt; Phases. For day-wise/daily count queries use: COUNT("WorkOrders"."Id") GROUP BY "WorkOrders"."CreationTime"::date ORDER BY date. For per-day results always cast timestamp to date using ::date. Always SELECT WorkOrderNumber and Subject for display.</t>
   </si>
   <si>
     <t>Offices</t>
@@ -263,10 +264,7 @@
     <t>Primary key INTEGER. Use in all JOINs. NOT same as WorkOrderNumber.</t>
   </si>
   <si>
-    <t>Primary display column for work orders. ALWAYS USE THIS for listing and display. Human-readable ID e.g. 08.25001260.</t>
-  </si>
-  <si>
-    <t>Human-readable TEXT ID e.g. 08.25001260. Use only for WHERE lookups by number — never as integer FK.</t>
+    <t>ALWAYS USE THIS Primary display column for work orders. ALWAYS USE THIS for listing and display. Human-readable ID e.g. 08.25001260.</t>
   </si>
   <si>
     <t>Status</t>
@@ -768,6 +766,12 @@
   </si>
   <si>
     <t>Soft delete. Always write "Phases"."IsDeleted" = false — never bare "IsDeleted"</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>NEVER SELECT this column. Use WorkOrderNumber for display instead.</t>
   </si>
   <si>
     <t>FromTable</t>
@@ -2367,99 +2371,99 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:4">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>22</v>
+      <c r="C5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>82</v>
       </c>
+      <c r="C6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="3"/>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:4">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="C7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:4">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>90</v>
-      </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>90</v>
+      <c r="C10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:4">
@@ -2467,27 +2471,27 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>97</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4">
@@ -2495,26 +2499,26 @@
         <v>4</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="C14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2523,26 +2527,26 @@
         <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2551,804 +2555,801 @@
         <v>4</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:4">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="C18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:4">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1" spans="1:4">
-      <c r="A20" s="3" t="s">
+      <c r="C19" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A21" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A27" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A37" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A39" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A52" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A54" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="58" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="59" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="60" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="61" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A64" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A65" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="66" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A66" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A67" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A68" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A69" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1" spans="1:4">
+      <c r="A70" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A22" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A24" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="B70" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="26" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A26" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" s="6" t="s">
+      <c r="C70" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D70" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="27" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A28" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A30" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="2" t="s">
+    </row>
+    <row r="71" ht="28.8" hidden="1" spans="1:4">
+      <c r="A71" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A34" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A36" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A38" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="40" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A40" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A41" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A43" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A45" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A46" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A47" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A48" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A49" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A50" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A51" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A53" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A55" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A56" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="57" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A57" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="59" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A59" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="60" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="61" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A61" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="62" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A63" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A65" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A66" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="67" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A67" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="68" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A68" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A69" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A70" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="71" ht="30" customHeight="1" spans="1:4">
-      <c r="A71" t="s">
-        <v>4</v>
-      </c>
-      <c r="B71" t="s">
-        <v>122</v>
-      </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D71" s="12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="72" ht="28.8" hidden="1" spans="1:4">
+    </row>
+    <row r="72" hidden="1" spans="1:4">
       <c r="A72" t="s">
         <v>59</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
-      </c>
-      <c r="C72" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="73" hidden="1" spans="1:4">
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
-      </c>
-      <c r="C73" s="4" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="C73" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="D73" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="74" hidden="1" spans="1:4">
       <c r="A74" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="B74" t="s">
-        <v>198</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="D74" t="s">
+        <v>74</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>200</v>
       </c>
     </row>
@@ -3357,9 +3358,9 @@
         <v>50</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C75" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C75" s="9" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3368,18 +3369,18 @@
         <v>50</v>
       </c>
       <c r="B76" t="s">
-        <v>52</v>
-      </c>
-      <c r="C76" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C76" s="4" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="77" hidden="1" spans="1:4">
       <c r="A77" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B77" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>203</v>
@@ -3390,9 +3391,9 @@
         <v>59</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
-      </c>
-      <c r="C78" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="9" t="s">
         <v>204</v>
       </c>
     </row>
@@ -3401,10 +3402,13 @@
         <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>18</v>
-      </c>
-      <c r="C79" s="9" t="s">
         <v>205</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D79" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="80" hidden="1" spans="1:4">
@@ -3412,13 +3416,10 @@
         <v>59</v>
       </c>
       <c r="B80" t="s">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>207</v>
-      </c>
-      <c r="D80" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="81" hidden="1" spans="1:4">
@@ -3426,7 +3427,7 @@
         <v>59</v>
       </c>
       <c r="B81" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>208</v>
@@ -3434,13 +3435,16 @@
     </row>
     <row r="82" hidden="1" spans="1:4">
       <c r="A82" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B82" t="s">
-        <v>130</v>
+        <v>169</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>209</v>
+      </c>
+      <c r="D82" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="83" hidden="1" spans="1:4">
@@ -3448,13 +3452,13 @@
         <v>62</v>
       </c>
       <c r="B83" t="s">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D83" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
     </row>
     <row r="84" hidden="1" spans="1:4">
@@ -3462,24 +3466,21 @@
         <v>62</v>
       </c>
       <c r="B84" t="s">
-        <v>211</v>
+        <v>129</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="D84" t="s">
-        <v>124</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" hidden="1" spans="1:4">
       <c r="A85" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B85" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
     </row>
     <row r="86" hidden="1" spans="1:4">
@@ -3487,10 +3488,10 @@
         <v>65</v>
       </c>
       <c r="B86" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
     </row>
     <row r="87" hidden="1" spans="1:4">
@@ -3498,10 +3499,10 @@
         <v>65</v>
       </c>
       <c r="B87" t="s">
-        <v>42</v>
+        <v>213</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="88" hidden="1" spans="1:4">
@@ -3509,10 +3510,13 @@
         <v>65</v>
       </c>
       <c r="B88" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>215</v>
+      </c>
+      <c r="D88" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="89" hidden="1" spans="1:4">
@@ -3520,49 +3524,46 @@
         <v>65</v>
       </c>
       <c r="B89" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>216</v>
       </c>
       <c r="D89" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="90" hidden="1" spans="1:4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" ht="72" spans="1:4">
       <c r="A90" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>168</v>
-      </c>
-      <c r="C90" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="D90" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="91" ht="72" spans="1:4">
+      <c r="C90" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
         <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="92" hidden="1" spans="1:4">
       <c r="A92" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="B92" t="s">
-        <v>220</v>
-      </c>
-      <c r="C92" s="9" t="s">
         <v>221</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="93" hidden="1" spans="1:4">
@@ -3570,10 +3571,10 @@
         <v>68</v>
       </c>
       <c r="B93" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="94" hidden="1" spans="1:4">
@@ -3581,10 +3582,10 @@
         <v>68</v>
       </c>
       <c r="B94" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="95" hidden="1" spans="1:4">
@@ -3592,10 +3593,10 @@
         <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="96" hidden="1" spans="1:4">
@@ -3603,7 +3604,7 @@
         <v>68</v>
       </c>
       <c r="B96" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>229</v>
@@ -3614,10 +3615,10 @@
         <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="98" hidden="1" spans="1:4">
@@ -3625,24 +3626,27 @@
         <v>68</v>
       </c>
       <c r="B98" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="99" hidden="1" spans="1:4">
+        <v>233</v>
+      </c>
+      <c r="D98" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="99" ht="28.8" hidden="1" spans="1:4">
       <c r="A99" t="s">
         <v>68</v>
       </c>
       <c r="B99" t="s">
-        <v>233</v>
-      </c>
-      <c r="C99" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C99" s="9" t="s">
         <v>234</v>
       </c>
       <c r="D99" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="100" ht="28.8" hidden="1" spans="1:4">
@@ -3650,46 +3654,43 @@
         <v>68</v>
       </c>
       <c r="B100" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="C100" s="9" t="s">
         <v>235</v>
       </c>
       <c r="D100" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="101" ht="28.8" hidden="1" spans="1:4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="101" hidden="1" spans="1:4">
       <c r="A101" t="s">
         <v>68</v>
       </c>
       <c r="B101" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="C101" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="D101" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="102" hidden="1" spans="1:4">
+    </row>
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="B102" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C102" s="9" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" hidden="1" spans="1:4">
       <c r="A103" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C103" s="9" t="s">
         <v>238</v>
@@ -3697,10 +3698,10 @@
     </row>
     <row r="104" hidden="1" spans="1:4">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="B104" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C104" s="9" t="s">
         <v>239</v>
@@ -3708,10 +3709,10 @@
     </row>
     <row r="105" hidden="1" spans="1:4">
       <c r="A105" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C105" s="9" t="s">
         <v>240</v>
@@ -3719,10 +3720,10 @@
     </row>
     <row r="106" hidden="1" spans="1:4">
       <c r="A106" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B106" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C106" s="9" t="s">
         <v>241</v>
@@ -3730,10 +3731,10 @@
     </row>
     <row r="107" hidden="1" spans="1:4">
       <c r="A107" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B107" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C107" s="9" t="s">
         <v>242</v>
@@ -3741,28 +3742,28 @@
     </row>
     <row r="108" hidden="1" spans="1:4">
       <c r="A108" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B108" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C108" s="9" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:4">
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="B109" t="s">
-        <v>130</v>
-      </c>
-      <c r="C109" s="9" t="s">
         <v>244</v>
       </c>
+      <c r="C109" t="s">
+        <v>245</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D109" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D108" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
         <filter val="WorkOrders"/>
@@ -3788,19 +3789,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5">
@@ -3808,7 +3809,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>68</v>
@@ -3817,7 +3818,7 @@
         <v>74</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5">
@@ -3825,7 +3826,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>40</v>
@@ -3834,7 +3835,7 @@
         <v>74</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5">
@@ -3842,7 +3843,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>59</v>
@@ -3851,7 +3852,7 @@
         <v>74</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5">
@@ -3859,7 +3860,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>12</v>
@@ -3868,7 +3869,7 @@
         <v>74</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5">
@@ -3876,7 +3877,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>12</v>
@@ -3885,7 +3886,7 @@
         <v>74</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5">
@@ -3893,7 +3894,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>12</v>
@@ -3902,7 +3903,7 @@
         <v>74</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5">
@@ -3910,7 +3911,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>50</v>
@@ -3919,7 +3920,7 @@
         <v>74</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5">
@@ -3927,16 +3928,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5">
@@ -3944,16 +3945,16 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5">
@@ -3961,16 +3962,16 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5">
@@ -3978,7 +3979,7 @@
         <v>68</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>12</v>
@@ -3987,7 +3988,7 @@
         <v>74</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5">
@@ -3995,7 +3996,7 @@
         <v>68</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>40</v>
@@ -4004,7 +4005,7 @@
         <v>74</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5">
@@ -4012,7 +4013,7 @@
         <v>68</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>12</v>
@@ -4021,7 +4022,7 @@
         <v>74</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5">
@@ -4029,7 +4030,7 @@
         <v>68</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>8</v>
@@ -4038,7 +4039,7 @@
         <v>74</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5">
@@ -4046,7 +4047,7 @@
         <v>68</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>59</v>
@@ -4055,7 +4056,7 @@
         <v>74</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5">
@@ -4063,7 +4064,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>12</v>
@@ -4072,7 +4073,7 @@
         <v>74</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:5">
@@ -4080,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>16</v>
@@ -4089,7 +4090,7 @@
         <v>74</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:5">
@@ -4097,7 +4098,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>4</v>
@@ -4106,7 +4107,7 @@
         <v>74</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:5">
@@ -4114,7 +4115,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>47</v>
@@ -4123,7 +4124,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:5">
@@ -4131,7 +4132,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>33</v>
@@ -4140,7 +4141,7 @@
         <v>74</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:5">
@@ -4148,7 +4149,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>12</v>
@@ -4157,7 +4158,7 @@
         <v>74</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:5">
@@ -4165,7 +4166,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>4</v>
@@ -4174,7 +4175,7 @@
         <v>74</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:5">
@@ -4182,7 +4183,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>12</v>
@@ -4191,7 +4192,7 @@
         <v>74</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:5">
@@ -4199,7 +4200,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>4</v>
@@ -4208,7 +4209,7 @@
         <v>74</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:5">
@@ -4216,7 +4217,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>44</v>
@@ -4225,7 +4226,7 @@
         <v>74</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:5">
@@ -4233,16 +4234,16 @@
         <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>74</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:5">
@@ -4250,7 +4251,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>68</v>
@@ -4259,7 +4260,7 @@
         <v>74</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:5">
@@ -4267,7 +4268,7 @@
         <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>4</v>
@@ -4276,7 +4277,7 @@
         <v>74</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:5">
@@ -4284,7 +4285,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>47</v>
@@ -4293,7 +4294,7 @@
         <v>74</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:5">
@@ -4301,7 +4302,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>12</v>
@@ -4310,7 +4311,7 @@
         <v>74</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:5">
@@ -4318,16 +4319,16 @@
         <v>8</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -4335,7 +4336,7 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s">
         <v>59</v>
@@ -4344,7 +4345,7 @@
         <v>74</v>
       </c>
       <c r="E33" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -4352,16 +4353,16 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C34" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D34" t="s">
         <v>74</v>
       </c>
       <c r="E34" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -4369,7 +4370,7 @@
         <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
@@ -4378,7 +4379,7 @@
         <v>74</v>
       </c>
       <c r="E35" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -4386,7 +4387,7 @@
         <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C36" t="s">
         <v>59</v>
@@ -4395,7 +4396,7 @@
         <v>74</v>
       </c>
       <c r="E36" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -4403,7 +4404,7 @@
         <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C37" t="s">
         <v>16</v>
@@ -4412,7 +4413,7 @@
         <v>74</v>
       </c>
       <c r="E37" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -4420,7 +4421,7 @@
         <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -4429,7 +4430,7 @@
         <v>74</v>
       </c>
       <c r="E38" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -4437,7 +4438,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C39" t="s">
         <v>68</v>
@@ -4446,7 +4447,7 @@
         <v>74</v>
       </c>
       <c r="E39" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4471,10 +4472,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4482,10 +4483,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4493,10 +4494,10 @@
         <v>68</v>
       </c>
       <c r="B3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C3" t="s">
         <v>296</v>
-      </c>
-      <c r="C3" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4504,10 +4505,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4515,10 +4516,10 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4526,10 +4527,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4537,10 +4538,10 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4548,10 +4549,10 @@
         <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4559,10 +4560,10 @@
         <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4570,10 +4571,10 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4581,10 +4582,10 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4592,10 +4593,10 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4603,10 +4604,10 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4614,10 +4615,10 @@
         <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4625,10 +4626,10 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4636,32 +4637,32 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
+        <v>309</v>
+      </c>
+      <c r="C16" t="s">
         <v>308</v>
-      </c>
-      <c r="C16" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" t="s">
+        <v>314</v>
+      </c>
+      <c r="C18" t="s">
         <v>312</v>
-      </c>
-      <c r="B18" t="s">
-        <v>313</v>
-      </c>
-      <c r="C18" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4669,10 +4670,10 @@
         <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4680,10 +4681,10 @@
         <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/python/table_metadata.xlsx
+++ b/python/table_metadata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9840" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9840" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Triggers" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$D$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$D$109</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="318">
   <si>
     <t>TableName</t>
   </si>
@@ -57,7 +57,15 @@
   </si>
   <si>
     <t>NEVER SELECT Subject column — always use WorkOrderNumber for display.
- Id is INTEGER PK for JOINs. WorkOrderNumber is TEXT never use as integer. IsDeleted=false for active. OfficeId is NULL for all records — NEVER USE OfficeId. branches = AbpOrganizationUnits table. organizations = AbpOrganizationUnits table. For location/branch/office/fort myers queries always JOIN AbpOrganizationUnits ON OrganizationId=Id and filter by DisplayName ILIKE. For count by group always use COUNT(Id) with GROUP BY. For project-wise counts use ProjectId -&gt; Projects. For phase-wise counts use PhaseId -&gt; Phases. For day-wise/daily count queries use: COUNT("WorkOrders"."Id") GROUP BY "WorkOrders"."CreationTime"::date ORDER BY date. For per-day results always cast timestamp to date using ::date. Always SELECT WorkOrderNumber and Subject for display.</t>
+ Id is INTEGER PK for JOINs. WorkOrderNumber is TEXT never use as integer. IsDeleted=false for active. 
+ OfficeId is NULL for all records — NEVER USE OfficeId. branches = AbpOrganizationUnits table. 
+ organizations = AbpOrganizationUnits table. For location/branch/office/fort myers queries always 
+ JOIN AbpOrganizationUnits ON OrganizationId=Id and filter by DisplayName ILIKE. For count by group 
+ always use COUNT(Id) with GROUP BY. For project-wise counts use ProjectId -&gt; Projects. For phase-wise
+ counts use PhaseId -&gt; Phases. For day-wise/daily count queries use: COUNT("WorkOrders"."Id") GROUP
+ BY "WorkOrders"."CreationTime"::date ORDER BY date. For per-day results always cast timestamp to 
+ date using ::date. Always SELECT WorkOrderNumber for display — NEVER SELECT Subject. Office names come 
+ from AbpOrganizationUnits.DisplayName via OrganizationId — NOT from Offices table..</t>
   </si>
   <si>
     <t>Offices</t>
@@ -930,7 +938,7 @@
     <t>project,projects</t>
   </si>
   <si>
-    <t>organization,organizations,org,unit,units,branch,branches,location</t>
+    <t>office,offices</t>
   </si>
   <si>
     <t>user,users,username,creator,created,technician,active</t>
@@ -940,6 +948,9 @@
   </si>
   <si>
     <t>phase,phases</t>
+  </si>
+  <si>
+    <t>organization,organizations,org,unit,units,branch,branches,location,office,offices,officename</t>
   </si>
   <si>
     <t>specimen,sample,test,tests</t>
@@ -1635,6 +1646,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1653,9 +1667,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2014,9 +2025,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="65" style="9" customWidth="1"/>
+    <col min="2" max="2" width="65" style="10" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="70" style="9" customWidth="1"/>
+    <col min="4" max="4" width="70" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:4">
@@ -2034,240 +2045,240 @@
       </c>
     </row>
     <row r="2" s="10" customFormat="1" ht="144" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:4">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:4">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:4">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:4">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="C8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:4">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:4">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="C11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:4">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:4">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:4">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2275,10 +2286,10 @@
       <c r="A19" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="10" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2286,13 +2297,13 @@
       <c r="A20" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="10" t="s">
         <v>66</v>
       </c>
       <c r="C20" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="10" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2300,13 +2311,13 @@
       <c r="A21" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="10" t="s">
         <v>69</v>
       </c>
       <c r="C21" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="10" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2324,7 +2335,7 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="81.8888888888889" style="4" customWidth="1"/>
+    <col min="3" max="3" width="81.8888888888889" style="5" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2343,952 +2354,952 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:4">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:4">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:4">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:4">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:4">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:4">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:4">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:4">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:4">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:4">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:4">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:4">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:4">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:4">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:4">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:4">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="24" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="25" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="26" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="27" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="4" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="28" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="30" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="31" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="32" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="33" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="34" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="38" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="3" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="39" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="40" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="41" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="42" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="43" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="46" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="47" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="48" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C49" s="6" t="s">
+      <c r="B49" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="50" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="51" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="52" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="53" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C53" s="6" t="s">
+      <c r="B53" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="55" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="4" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="56" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C56" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="4" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="58" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="59" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="4" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="60" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="61" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="62" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="64" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C64" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="65" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="4" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="66" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="67" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="68" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D68" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="69" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3299,7 +3310,7 @@
       <c r="B70" t="s">
         <v>121</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="8" t="s">
         <v>194</v>
       </c>
       <c r="D70" s="12" t="s">
@@ -3313,7 +3324,7 @@
       <c r="B71" t="s">
         <v>18</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="9" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3324,7 +3335,7 @@
       <c r="B72" t="s">
         <v>136</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="5" t="s">
         <v>196</v>
       </c>
     </row>
@@ -3335,7 +3346,7 @@
       <c r="B73" t="s">
         <v>197</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="10" t="s">
         <v>198</v>
       </c>
       <c r="D73" t="s">
@@ -3349,7 +3360,7 @@
       <c r="B74" t="s">
         <v>74</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>200</v>
       </c>
     </row>
@@ -3360,7 +3371,7 @@
       <c r="B75" t="s">
         <v>52</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="10" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3371,7 +3382,7 @@
       <c r="B76" t="s">
         <v>129</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="5" t="s">
         <v>202</v>
       </c>
     </row>
@@ -3382,7 +3393,7 @@
       <c r="B77" t="s">
         <v>74</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="5" t="s">
         <v>203</v>
       </c>
     </row>
@@ -3393,7 +3404,7 @@
       <c r="B78" t="s">
         <v>18</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="10" t="s">
         <v>204</v>
       </c>
     </row>
@@ -3404,7 +3415,7 @@
       <c r="B79" t="s">
         <v>205</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="5" t="s">
         <v>206</v>
       </c>
       <c r="D79" t="s">
@@ -3418,7 +3429,7 @@
       <c r="B80" t="s">
         <v>136</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="5" t="s">
         <v>207</v>
       </c>
     </row>
@@ -3429,7 +3440,7 @@
       <c r="B81" t="s">
         <v>129</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="5" t="s">
         <v>208</v>
       </c>
     </row>
@@ -3440,7 +3451,7 @@
       <c r="B82" t="s">
         <v>169</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="5" t="s">
         <v>209</v>
       </c>
       <c r="D82" t="s">
@@ -3454,7 +3465,7 @@
       <c r="B83" t="s">
         <v>210</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="5" t="s">
         <v>211</v>
       </c>
       <c r="D83" t="s">
@@ -3468,7 +3479,7 @@
       <c r="B84" t="s">
         <v>129</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="5" t="s">
         <v>186</v>
       </c>
     </row>
@@ -3479,7 +3490,7 @@
       <c r="B85" t="s">
         <v>74</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="5" t="s">
         <v>166</v>
       </c>
     </row>
@@ -3490,7 +3501,7 @@
       <c r="B86" t="s">
         <v>42</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="5" t="s">
         <v>212</v>
       </c>
     </row>
@@ -3501,7 +3512,7 @@
       <c r="B87" t="s">
         <v>213</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="5" t="s">
         <v>214</v>
       </c>
     </row>
@@ -3512,7 +3523,7 @@
       <c r="B88" t="s">
         <v>169</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="5" t="s">
         <v>215</v>
       </c>
       <c r="D88" t="s">
@@ -3526,7 +3537,7 @@
       <c r="B89" t="s">
         <v>167</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="5" t="s">
         <v>216</v>
       </c>
       <c r="D89" t="s">
@@ -3540,7 +3551,7 @@
       <c r="B90" t="s">
         <v>217</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C90" s="10" t="s">
         <v>218</v>
       </c>
     </row>
@@ -3551,7 +3562,7 @@
       <c r="B91" t="s">
         <v>219</v>
       </c>
-      <c r="C91" s="9" t="s">
+      <c r="C91" s="10" t="s">
         <v>220</v>
       </c>
     </row>
@@ -3562,7 +3573,7 @@
       <c r="B92" t="s">
         <v>221</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="5" t="s">
         <v>222</v>
       </c>
     </row>
@@ -3573,7 +3584,7 @@
       <c r="B93" t="s">
         <v>223</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="5" t="s">
         <v>224</v>
       </c>
     </row>
@@ -3584,7 +3595,7 @@
       <c r="B94" t="s">
         <v>225</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="5" t="s">
         <v>226</v>
       </c>
     </row>
@@ -3595,7 +3606,7 @@
       <c r="B95" t="s">
         <v>227</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" s="5" t="s">
         <v>228</v>
       </c>
     </row>
@@ -3606,7 +3617,7 @@
       <c r="B96" t="s">
         <v>217</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="5" t="s">
         <v>229</v>
       </c>
     </row>
@@ -3617,7 +3628,7 @@
       <c r="B97" t="s">
         <v>230</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="5" t="s">
         <v>231</v>
       </c>
     </row>
@@ -3628,7 +3639,7 @@
       <c r="B98" t="s">
         <v>232</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="5" t="s">
         <v>233</v>
       </c>
       <c r="D98" t="s">
@@ -3642,7 +3653,7 @@
       <c r="B99" t="s">
         <v>124</v>
       </c>
-      <c r="C99" s="9" t="s">
+      <c r="C99" s="10" t="s">
         <v>234</v>
       </c>
       <c r="D99" t="s">
@@ -3656,7 +3667,7 @@
       <c r="B100" t="s">
         <v>87</v>
       </c>
-      <c r="C100" s="9" t="s">
+      <c r="C100" s="10" t="s">
         <v>235</v>
       </c>
       <c r="D100" t="s">
@@ -3670,7 +3681,7 @@
       <c r="B101" t="s">
         <v>129</v>
       </c>
-      <c r="C101" s="9" t="s">
+      <c r="C101" s="10" t="s">
         <v>236</v>
       </c>
     </row>
@@ -3681,7 +3692,7 @@
       <c r="B102" t="s">
         <v>129</v>
       </c>
-      <c r="C102" s="9" t="s">
+      <c r="C102" s="10" t="s">
         <v>237</v>
       </c>
     </row>
@@ -3692,7 +3703,7 @@
       <c r="B103" t="s">
         <v>129</v>
       </c>
-      <c r="C103" s="9" t="s">
+      <c r="C103" s="10" t="s">
         <v>238</v>
       </c>
     </row>
@@ -3703,7 +3714,7 @@
       <c r="B104" t="s">
         <v>129</v>
       </c>
-      <c r="C104" s="9" t="s">
+      <c r="C104" s="10" t="s">
         <v>239</v>
       </c>
     </row>
@@ -3714,7 +3725,7 @@
       <c r="B105" t="s">
         <v>129</v>
       </c>
-      <c r="C105" s="9" t="s">
+      <c r="C105" s="10" t="s">
         <v>240</v>
       </c>
     </row>
@@ -3725,7 +3736,7 @@
       <c r="B106" t="s">
         <v>129</v>
       </c>
-      <c r="C106" s="9" t="s">
+      <c r="C106" s="10" t="s">
         <v>241</v>
       </c>
     </row>
@@ -3736,7 +3747,7 @@
       <c r="B107" t="s">
         <v>129</v>
       </c>
-      <c r="C107" s="9" t="s">
+      <c r="C107" s="10" t="s">
         <v>242</v>
       </c>
     </row>
@@ -3747,7 +3758,7 @@
       <c r="B108" t="s">
         <v>129</v>
       </c>
-      <c r="C108" s="9" t="s">
+      <c r="C108" s="10" t="s">
         <v>243</v>
       </c>
     </row>
@@ -3763,11 +3774,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D108" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D109" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
-      <filters>
-        <filter val="WorkOrders"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="WorkOrders"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>
@@ -3805,529 +3816,529 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="D6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="D8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="D9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="3" t="s">
+      <c r="D10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="D12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="D13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="D15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="3" t="s">
+      <c r="D16" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="D17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="3" t="s">
+      <c r="D18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:5">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="D19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="D20" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:5">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="D21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="D22" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:5">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="D23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="3" t="s">
+      <c r="D24" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:5">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="D25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="3" t="s">
+      <c r="D26" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:5">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="D27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="3" t="s">
+      <c r="D28" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:5">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="D29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="D30" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:5">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="D31" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="3" t="s">
+      <c r="D32" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>284</v>
       </c>
     </row>
@@ -4482,7 +4493,7 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>295</v>
       </c>
       <c r="C2" t="s">
@@ -4493,7 +4504,7 @@
       <c r="A3" t="s">
         <v>68</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>297</v>
       </c>
       <c r="C3" t="s">
@@ -4504,7 +4515,7 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>298</v>
       </c>
       <c r="C4" t="s">
@@ -4515,7 +4526,7 @@
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C5" t="s">
@@ -4526,7 +4537,7 @@
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>300</v>
       </c>
       <c r="C6" t="s">
@@ -4537,7 +4548,7 @@
       <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>300</v>
       </c>
       <c r="C7" t="s">
@@ -4548,19 +4559,19 @@
       <c r="A8" t="s">
         <v>50</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>301</v>
       </c>
       <c r="C8" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" ht="28.8" spans="1:3">
       <c r="A9" t="s">
         <v>59</v>
       </c>
-      <c r="B9" t="s">
-        <v>298</v>
+      <c r="B9" s="2" t="s">
+        <v>302</v>
       </c>
       <c r="C9" t="s">
         <v>296</v>
@@ -4570,8 +4581,8 @@
       <c r="A10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
-        <v>302</v>
+      <c r="B10" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="C10" t="s">
         <v>296</v>
@@ -4581,8 +4592,8 @@
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
-        <v>303</v>
+      <c r="B11" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="C11" t="s">
         <v>296</v>
@@ -4592,8 +4603,8 @@
       <c r="A12" t="s">
         <v>47</v>
       </c>
-      <c r="B12" t="s">
-        <v>304</v>
+      <c r="B12" s="2" t="s">
+        <v>305</v>
       </c>
       <c r="C12" t="s">
         <v>296</v>
@@ -4603,8 +4614,8 @@
       <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="B13" t="s">
-        <v>305</v>
+      <c r="B13" s="2" t="s">
+        <v>306</v>
       </c>
       <c r="C13" t="s">
         <v>296</v>
@@ -4614,8 +4625,8 @@
       <c r="A14" t="s">
         <v>44</v>
       </c>
-      <c r="B14" t="s">
-        <v>306</v>
+      <c r="B14" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="C14" t="s">
         <v>296</v>
@@ -4625,66 +4636,66 @@
       <c r="A15" t="s">
         <v>27</v>
       </c>
-      <c r="B15" t="s">
-        <v>307</v>
+      <c r="B15" s="2" t="s">
+        <v>308</v>
       </c>
       <c r="C15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>37</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C16" t="s">
         <v>309</v>
-      </c>
-      <c r="C16" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>310</v>
-      </c>
-      <c r="B17" t="s">
         <v>311</v>
       </c>
+      <c r="B17" s="2" t="s">
+        <v>312</v>
+      </c>
       <c r="C17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>314</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C18" t="s">
         <v>313</v>
-      </c>
-      <c r="B18" t="s">
-        <v>314</v>
-      </c>
-      <c r="C18" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>62</v>
       </c>
-      <c r="B19" t="s">
-        <v>315</v>
+      <c r="B19" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="C19" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>65</v>
       </c>
-      <c r="B20" t="s">
-        <v>316</v>
+      <c r="B20" s="2" t="s">
+        <v>317</v>
       </c>
       <c r="C20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/python/table_metadata.xlsx
+++ b/python/table_metadata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9840" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="9840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -512,7 +512,7 @@
     <t>IsActive</t>
   </si>
   <si>
-    <t>Boolean — TRUE means user is active/enabled. USE = true TO FILTER ACTIVE USERS.</t>
+    <t>Boolean — TRUE means user is active. ALWAYS filter with BOTH: "AbpUsers"."IsActive" = true AND "AbpUsers"."IsDeleted" = false together — never use IsActive alone.</t>
   </si>
   <si>
     <t>Soft delete boolean. Use = false for non-deleted users.</t>
@@ -758,7 +758,7 @@
     <t>Soft delete. Always write "WorkOrders"."IsDeleted" = false — never bare "IsDeleted".</t>
   </si>
   <si>
-    <t>Soft delete. Always write "AbpUsers"."IsDeleted" = false — never bare "IsDeleted"</t>
+    <t>Soft delete. ALWAYS combine with IsActive: use "AbpUsers"."IsActive" = true AND "AbpUsers"."IsDeleted" = false together in every query involving users.</t>
   </si>
   <si>
     <t>Soft delete. Always write "AbpOrganizationUnits"."IsDeleted" = false — never bare "IsDeleted"</t>
@@ -2353,7 +2353,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:4">
+    <row r="2" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:4">
+    <row r="3" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" spans="1:4">
+    <row r="4" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" spans="1:4">
+    <row r="5" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" spans="1:4">
+    <row r="6" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:4">
+    <row r="7" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" spans="1:4">
+    <row r="8" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" spans="1:4">
+    <row r="9" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" spans="1:4">
+    <row r="10" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" spans="1:4">
+    <row r="11" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" spans="1:4">
+    <row r="12" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="1:4">
+    <row r="13" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A13" s="4" t="s">
         <v>4</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="1:4">
+    <row r="14" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" spans="1:4">
+    <row r="15" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A15" s="3" t="s">
         <v>4</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" spans="1:4">
+    <row r="16" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" spans="1:4">
+    <row r="17" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A17" s="4" t="s">
         <v>4</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1" spans="1:4">
+    <row r="18" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1" spans="1:4">
+    <row r="19" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="40" ht="30" customHeight="1" spans="1:4">
       <c r="A40" s="3" t="s">
         <v>12</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="41" ht="30" customHeight="1" spans="1:4">
       <c r="A41" s="4" t="s">
         <v>12</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="42" ht="30" customHeight="1" spans="1:4">
       <c r="A42" s="3" t="s">
         <v>12</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="43" ht="30" customHeight="1" spans="1:4">
       <c r="A43" s="4" t="s">
         <v>12</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="44" ht="30" customHeight="1" spans="1:4">
       <c r="A44" s="3" t="s">
         <v>12</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="45" ht="30" customHeight="1" spans="1:4">
       <c r="A45" s="4" t="s">
         <v>12</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="46" ht="30" customHeight="1" spans="1:4">
       <c r="A46" s="3" t="s">
         <v>12</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="47" ht="30" customHeight="1" spans="1:4">
       <c r="A47" s="4" t="s">
         <v>12</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" ht="30" hidden="1" customHeight="1" spans="1:4">
+    <row r="48" ht="30" customHeight="1" spans="1:4">
       <c r="A48" s="3" t="s">
         <v>12</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1" spans="1:4">
+    <row r="70" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A70" t="s">
         <v>4</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" hidden="1" spans="1:4">
       <c r="A73" t="s">
         <v>4</v>
       </c>
@@ -3544,7 +3544,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="90" ht="72" spans="1:4">
+    <row r="90" ht="72" hidden="1" spans="1:4">
       <c r="A90" t="s">
         <v>4</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" hidden="1" spans="1:4">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" hidden="1" spans="1:4">
       <c r="A102" t="s">
         <v>4</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:4">
+    <row r="103" ht="28.8" spans="1:4">
       <c r="A103" t="s">
         <v>12</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" hidden="1" spans="1:4">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -3776,9 +3776,9 @@
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D109" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
-      <customFilters>
-        <customFilter operator="equal" val="WorkOrders"/>
-      </customFilters>
+      <filters>
+        <filter val="AbpUsers"/>
+      </filters>
     </filterColumn>
     <extLst/>
   </autoFilter>

--- a/python/table_metadata.xlsx
+++ b/python/table_metadata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9840" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9840"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Triggers" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$D$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$D$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="317">
   <si>
     <t>TableName</t>
   </si>
@@ -89,7 +89,7 @@
     <t>UserName</t>
   </si>
   <si>
-    <t>IsActive=true for active users. Use UserName for filtering by login. Name+Surname for full name. To get users by role JOIN AbpUserRoles then AbpRoles.</t>
+    <t>ALWAYS filter users with BOTH conditions together: "AbpUsers"."IsActive" = true AND "AbpUsers"."IsDeleted" = false — never use IsActive alone without IsDeleted. Use UserName for filtering by login. Name+Surname for full name. To get users by role JOIN AbpUserRoles then AbpRoles.</t>
   </si>
   <si>
     <t>AbpRoles</t>
@@ -513,9 +513,6 @@
   </si>
   <si>
     <t>Boolean — TRUE means user is active. ALWAYS filter with BOTH: "AbpUsers"."IsActive" = true AND "AbpUsers"."IsDeleted" = false together — never use IsActive alone.</t>
-  </si>
-  <si>
-    <t>Soft delete boolean. Use = false for non-deleted users.</t>
   </si>
   <si>
     <t>DefaultRole</t>
@@ -2330,7 +2327,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -2968,388 +2965,385 @@
       </c>
     </row>
     <row r="46" ht="30" customHeight="1" spans="1:4">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1" spans="1:4">
+      <c r="A47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1" spans="1:4">
-      <c r="A47" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1" spans="1:4">
-      <c r="A48" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A49" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A50" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50" s="3" t="s">
+      <c r="C51" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A52" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="54" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A54" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="55" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A56" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="58" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A58" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="59" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A60" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A62" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A63" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A64" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="65" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A65" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A66" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A67" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A68" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A69" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" t="s">
+        <v>121</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="70" ht="28.8" hidden="1" spans="1:4">
+      <c r="A70" t="s">
+        <v>59</v>
+      </c>
+      <c r="B70" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A51" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A53" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="55" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A55" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="56" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="57" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A57" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="58" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="59" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A59" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="60" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="61" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A61" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A63" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A64" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A65" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="66" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A66" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="67" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A67" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="68" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A68" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A69" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" ht="30" hidden="1" customHeight="1" spans="1:4">
-      <c r="A70" t="s">
-        <v>4</v>
-      </c>
-      <c r="B70" t="s">
-        <v>121</v>
-      </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="D70" s="12" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="71" ht="28.8" hidden="1" spans="1:4">
+    </row>
+    <row r="71" hidden="1" spans="1:4">
       <c r="A71" t="s">
         <v>59</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
-      </c>
-      <c r="C71" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="72" hidden="1" spans="1:4">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>136</v>
-      </c>
-      <c r="C72" s="5" t="s">
         <v>196</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="D72" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="73" hidden="1" spans="1:4">
       <c r="A73" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="B73" t="s">
-        <v>197</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="D73" t="s">
+        <v>74</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>199</v>
       </c>
     </row>
@@ -3358,9 +3352,9 @@
         <v>50</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
-      </c>
-      <c r="C74" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C74" s="10" t="s">
         <v>200</v>
       </c>
     </row>
@@ -3369,18 +3363,18 @@
         <v>50</v>
       </c>
       <c r="B75" t="s">
-        <v>52</v>
-      </c>
-      <c r="C75" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="76" hidden="1" spans="1:4">
       <c r="A76" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B76" t="s">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>202</v>
@@ -3391,9 +3385,9 @@
         <v>59</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
-      </c>
-      <c r="C77" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C77" s="10" t="s">
         <v>203</v>
       </c>
     </row>
@@ -3402,10 +3396,13 @@
         <v>59</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
-      </c>
-      <c r="C78" s="10" t="s">
         <v>204</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D78" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="79" hidden="1" spans="1:4">
@@ -3413,13 +3410,10 @@
         <v>59</v>
       </c>
       <c r="B79" t="s">
-        <v>205</v>
+        <v>136</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="D79" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="80" hidden="1" spans="1:4">
@@ -3427,7 +3421,7 @@
         <v>59</v>
       </c>
       <c r="B80" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>207</v>
@@ -3435,13 +3429,16 @@
     </row>
     <row r="81" hidden="1" spans="1:4">
       <c r="A81" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B81" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>208</v>
+      </c>
+      <c r="D81" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="82" hidden="1" spans="1:4">
@@ -3449,13 +3446,13 @@
         <v>62</v>
       </c>
       <c r="B82" t="s">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D82" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
     </row>
     <row r="83" hidden="1" spans="1:4">
@@ -3463,24 +3460,21 @@
         <v>62</v>
       </c>
       <c r="B83" t="s">
-        <v>210</v>
+        <v>129</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D83" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" hidden="1" spans="1:4">
       <c r="A84" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B84" t="s">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
     </row>
     <row r="85" hidden="1" spans="1:4">
@@ -3488,10 +3482,10 @@
         <v>65</v>
       </c>
       <c r="B85" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>166</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" hidden="1" spans="1:4">
@@ -3499,10 +3493,10 @@
         <v>65</v>
       </c>
       <c r="B86" t="s">
-        <v>42</v>
+        <v>212</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="87" hidden="1" spans="1:4">
@@ -3510,10 +3504,13 @@
         <v>65</v>
       </c>
       <c r="B87" t="s">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>214</v>
+      </c>
+      <c r="D87" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="88" hidden="1" spans="1:4">
@@ -3521,49 +3518,46 @@
         <v>65</v>
       </c>
       <c r="B88" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>215</v>
       </c>
       <c r="D88" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="89" hidden="1" spans="1:4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="89" ht="72" hidden="1" spans="1:4">
       <c r="A89" t="s">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="B89" t="s">
-        <v>167</v>
-      </c>
-      <c r="C89" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="D89" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="90" ht="72" hidden="1" spans="1:4">
+      <c r="C89" s="10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="90" hidden="1" spans="1:4">
       <c r="A90" t="s">
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="91" hidden="1" spans="1:4">
       <c r="A91" t="s">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="B91" t="s">
-        <v>219</v>
-      </c>
-      <c r="C91" s="10" t="s">
         <v>220</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="92" hidden="1" spans="1:4">
@@ -3571,10 +3565,10 @@
         <v>68</v>
       </c>
       <c r="B92" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="93" hidden="1" spans="1:4">
@@ -3582,10 +3576,10 @@
         <v>68</v>
       </c>
       <c r="B93" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="94" hidden="1" spans="1:4">
@@ -3593,10 +3587,10 @@
         <v>68</v>
       </c>
       <c r="B94" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="95" hidden="1" spans="1:4">
@@ -3604,7 +3598,7 @@
         <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>228</v>
@@ -3615,10 +3609,10 @@
         <v>68</v>
       </c>
       <c r="B96" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="97" hidden="1" spans="1:4">
@@ -3626,24 +3620,27 @@
         <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="98" hidden="1" spans="1:4">
+        <v>232</v>
+      </c>
+      <c r="D97" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="98" ht="28.8" hidden="1" spans="1:4">
       <c r="A98" t="s">
         <v>68</v>
       </c>
       <c r="B98" t="s">
-        <v>232</v>
-      </c>
-      <c r="C98" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C98" s="10" t="s">
         <v>233</v>
       </c>
       <c r="D98" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="99" ht="28.8" hidden="1" spans="1:4">
@@ -3651,7 +3648,7 @@
         <v>68</v>
       </c>
       <c r="B99" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="C99" s="10" t="s">
         <v>234</v>
@@ -3660,23 +3657,20 @@
         <v>89</v>
       </c>
     </row>
-    <row r="100" ht="28.8" hidden="1" spans="1:4">
+    <row r="100" hidden="1" spans="1:4">
       <c r="A100" t="s">
         <v>68</v>
       </c>
       <c r="B100" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="D100" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="101" hidden="1" spans="1:4">
       <c r="A101" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="B101" t="s">
         <v>129</v>
@@ -3685,9 +3679,9 @@
         <v>236</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:4">
+    <row r="102" ht="28.8" spans="1:4">
       <c r="A102" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
         <v>129</v>
@@ -3696,9 +3690,9 @@
         <v>237</v>
       </c>
     </row>
-    <row r="103" ht="28.8" spans="1:4">
+    <row r="103" hidden="1" spans="1:4">
       <c r="A103" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="B103" t="s">
         <v>129</v>
@@ -3709,7 +3703,7 @@
     </row>
     <row r="104" hidden="1" spans="1:4">
       <c r="A104" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="B104" t="s">
         <v>129</v>
@@ -3720,7 +3714,7 @@
     </row>
     <row r="105" hidden="1" spans="1:4">
       <c r="A105" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B105" t="s">
         <v>129</v>
@@ -3731,7 +3725,7 @@
     </row>
     <row r="106" hidden="1" spans="1:4">
       <c r="A106" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B106" t="s">
         <v>129</v>
@@ -3742,7 +3736,7 @@
     </row>
     <row r="107" hidden="1" spans="1:4">
       <c r="A107" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B107" t="s">
         <v>129</v>
@@ -3753,28 +3747,17 @@
     </row>
     <row r="108" hidden="1" spans="1:4">
       <c r="A108" t="s">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="B108" t="s">
-        <v>129</v>
-      </c>
-      <c r="C108" s="10" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="109" hidden="1" spans="1:4">
-      <c r="A109" t="s">
-        <v>4</v>
-      </c>
-      <c r="B109" t="s">
+      <c r="C108" t="s">
         <v>244</v>
       </c>
-      <c r="C109" t="s">
-        <v>245</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D109" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D108" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
         <filter val="AbpUsers"/>
@@ -3800,19 +3783,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5">
@@ -3829,7 +3812,7 @@
         <v>74</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5">
@@ -3846,7 +3829,7 @@
         <v>74</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5">
@@ -3863,7 +3846,7 @@
         <v>74</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5">
@@ -3880,7 +3863,7 @@
         <v>74</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5">
@@ -3897,7 +3880,7 @@
         <v>74</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5">
@@ -3914,7 +3897,7 @@
         <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5">
@@ -3922,7 +3905,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>50</v>
@@ -3931,7 +3914,7 @@
         <v>74</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5">
@@ -3939,16 +3922,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5">
@@ -3959,13 +3942,13 @@
         <v>94</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>261</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5">
@@ -3976,13 +3959,13 @@
         <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5">
@@ -3999,7 +3982,7 @@
         <v>74</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5">
@@ -4016,7 +3999,7 @@
         <v>74</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5">
@@ -4033,7 +4016,7 @@
         <v>74</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5">
@@ -4050,7 +4033,7 @@
         <v>74</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5">
@@ -4067,7 +4050,7 @@
         <v>74</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5">
@@ -4075,7 +4058,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>12</v>
@@ -4084,7 +4067,7 @@
         <v>74</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:5">
@@ -4092,7 +4075,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>16</v>
@@ -4101,7 +4084,7 @@
         <v>74</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:5">
@@ -4109,7 +4092,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>4</v>
@@ -4118,7 +4101,7 @@
         <v>74</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:5">
@@ -4126,7 +4109,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>47</v>
@@ -4135,7 +4118,7 @@
         <v>74</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:5">
@@ -4143,7 +4126,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>33</v>
@@ -4152,7 +4135,7 @@
         <v>74</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:5">
@@ -4160,7 +4143,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>12</v>
@@ -4169,7 +4152,7 @@
         <v>74</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:5">
@@ -4177,7 +4160,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>4</v>
@@ -4186,7 +4169,7 @@
         <v>74</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:5">
@@ -4194,7 +4177,7 @@
         <v>27</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>12</v>
@@ -4203,7 +4186,7 @@
         <v>74</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:5">
@@ -4211,7 +4194,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>4</v>
@@ -4220,7 +4203,7 @@
         <v>74</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:5">
@@ -4228,7 +4211,7 @@
         <v>30</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>44</v>
@@ -4237,7 +4220,7 @@
         <v>74</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:5">
@@ -4245,16 +4228,16 @@
         <v>33</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:5">
@@ -4271,7 +4254,7 @@
         <v>74</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:5">
@@ -4279,7 +4262,7 @@
         <v>37</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>4</v>
@@ -4288,7 +4271,7 @@
         <v>74</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:5">
@@ -4296,7 +4279,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>47</v>
@@ -4305,7 +4288,7 @@
         <v>74</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="1:5">
@@ -4313,7 +4296,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>12</v>
@@ -4322,7 +4305,7 @@
         <v>74</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:5">
@@ -4333,13 +4316,13 @@
         <v>144</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -4356,7 +4339,7 @@
         <v>74</v>
       </c>
       <c r="E33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -4364,16 +4347,16 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C34" t="s">
+        <v>285</v>
+      </c>
+      <c r="D34" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" t="s">
         <v>286</v>
-      </c>
-      <c r="D34" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -4381,7 +4364,7 @@
         <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
@@ -4390,7 +4373,7 @@
         <v>74</v>
       </c>
       <c r="E35" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -4398,7 +4381,7 @@
         <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C36" t="s">
         <v>59</v>
@@ -4407,7 +4390,7 @@
         <v>74</v>
       </c>
       <c r="E36" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -4415,7 +4398,7 @@
         <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C37" t="s">
         <v>16</v>
@@ -4424,7 +4407,7 @@
         <v>74</v>
       </c>
       <c r="E37" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -4432,7 +4415,7 @@
         <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -4441,7 +4424,7 @@
         <v>74</v>
       </c>
       <c r="E38" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -4449,7 +4432,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C39" t="s">
         <v>68</v>
@@ -4458,7 +4441,7 @@
         <v>74</v>
       </c>
       <c r="E39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -4483,10 +4466,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4494,10 +4477,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C2" t="s">
         <v>295</v>
-      </c>
-      <c r="C2" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4505,10 +4488,10 @@
         <v>68</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4516,10 +4499,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4527,10 +4510,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4538,10 +4521,10 @@
         <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4549,10 +4532,10 @@
         <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4560,10 +4543,10 @@
         <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" ht="28.8" spans="1:3">
@@ -4571,10 +4554,10 @@
         <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4582,10 +4565,10 @@
         <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4593,10 +4576,10 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -4604,10 +4587,10 @@
         <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4615,10 +4598,10 @@
         <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4626,10 +4609,10 @@
         <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -4637,10 +4620,10 @@
         <v>27</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C15" t="s">
         <v>308</v>
-      </c>
-      <c r="C15" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -4648,32 +4631,32 @@
         <v>37</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" t="s">
         <v>312</v>
-      </c>
-      <c r="C17" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="C18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4681,10 +4664,10 @@
         <v>62</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -4692,10 +4675,10 @@
         <v>65</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/python/table_metadata.xlsx
+++ b/python/table_metadata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9840"/>
+    <workbookView windowWidth="23040" windowHeight="9840" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,10 @@
     <sheet name="Triggers" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$D$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tables!$A$1:$D$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Columns!$A$1:$D$215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Relationships!$A$1:$E$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Triggers!$A$1:$C$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="546">
   <si>
     <t>TableName</t>
   </si>
@@ -167,21 +170,24 @@
     <t>Clients</t>
   </si>
   <si>
-    <t>Client companies that own projects.</t>
+    <t>Client companies that own projects and work orders. Each project and WO links to a client via ClientId.</t>
+  </si>
+  <si>
+    <t>ClientName</t>
+  </si>
+  <si>
+    <t>Use ClientName for display. IsDeleted=false for active clients. ClientId in WorkOrders and Projects links here. CompanyId links to Companies table. StateName is the readable state name. Use ClientName for display. IsDeleted=false for active. When listing clients always SELECT Id, ClientName, Address1, City, StateName, Zipcode, Phonenumber, website, Status, CompanyId — skip Faxnumber, Code, OldClientId, State, ClientNotes as they are NULL for most records.</t>
+  </si>
+  <si>
+    <t>Equipments</t>
+  </si>
+  <si>
+    <t>Equipment items used in field work orders.</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>IsDeleted=false for active. ClientId in Projects and WorkOrders links here.</t>
-  </si>
-  <si>
-    <t>Equipments</t>
-  </si>
-  <si>
-    <t>Equipment items used in field work orders.</t>
-  </si>
-  <si>
     <t>Referenced by WorkOrderEquipments.EquipmentId</t>
   </si>
   <si>
@@ -260,6 +266,78 @@
     <t>OfficeId is NULL for all records — NEVER USE OfficeId. For location/office/branch queries always JOIN AbpOrganizationUnits ON Projects.OrganizationId=AbpOrganizationUnits.Id and filter by DisplayName ILIKE.Use ProjectName for display. ProjectNumber is human-readable lookup. IsDeleted=false for active. PMUserId links to Project Manager in AbpUsers. CreatorUserId links to AbpUsers. For project-wise WO count: JOIN WorkOrders ON ProjectId=Projects.Id GROUP BY ProjectName. Use ProjectName for display. ProjectNumber is human-readable lookup ID. IsDeleted=false for active. PMUserId links to AbpUsers.Id. For project-wise WO count: JOIN WorkOrders ON WorkOrders.ProjectId=Projects.Id GROUP BY ProjectName. CreatorUserId and PMUserId are INTEGER FKs — NEVER filter by username directly, always JOIN AbpUsers.</t>
   </si>
   <si>
+    <t>Companies</t>
+  </si>
+  <si>
+    <t>Parent companies that own clients. Clients.CompanyId links here.</t>
+  </si>
+  <si>
+    <t>CompanyName</t>
+  </si>
+  <si>
+    <t>Use CompanyName for display. IsDeleted=false for active. When listing companies always SELECT Id, CompanyName, CompanyCode, Status, CorporateId, CreationTime — skip Address, City, State, Zipcode, Phonenumber, Website, CompanyNotes as they are NULL for most records.</t>
+  </si>
+  <si>
+    <t>Contacts</t>
+  </si>
+  <si>
+    <t>Contact persons linked to clients. Each contact belongs to a client via ClientId.</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>Full name = FirstName + LastName. IsDeleted=false for active. ClientId links to Clients. Skip Code, MiddleName, Prefix, Suffix, Pager, HomeNumber, FaxNumber, Type, Firm, Version as they are NULL for most records.</t>
+  </si>
+  <si>
+    <t>Corporates</t>
+  </si>
+  <si>
+    <t>Top-level corporate entities. Companies.CorporateId links here.</t>
+  </si>
+  <si>
+    <t>CorporateName</t>
+  </si>
+  <si>
+    <t>Use CorporateName for display. Active=true for active corporates. IsDeleted=false for active. No FK to other tables — top of hierarchy: Corporate → Company → Client.</t>
+  </si>
+  <si>
+    <t>Departments within offices. OfficeId links to Offices table.</t>
+  </si>
+  <si>
+    <t>Use Name for display. Active=true and IsDeleted=false for active departments. OfficeId links to Offices. Skip VP_Department_Code, PluralLabel, SingularLabel, FBPERegistryNumber as rarely used.</t>
+  </si>
+  <si>
+    <t>Samples</t>
+  </si>
+  <si>
+    <t>Physical samples collected in field. SampleSpecimens are created from Samples for lab testing. SampleSpecimens table is the main specimens table — Specimens table is empty.</t>
+  </si>
+  <si>
+    <t>SampleNumber</t>
+  </si>
+  <si>
+    <t>Use SampleNumber for display. IsDeleted=false for active. ProjectId links to Projects. OrganizationId links to AbpOrganizationUnits. SamplePickedupBy, SampleCheckinBy, SampleReceivedBy link to AbpUsers.Id. Skip soil test columns (SoilAbrasion, SoilGradation etc) as they are integer codes not readable values.</t>
+  </si>
+  <si>
+    <t>Specimens created from samples for lab testing. THIS is the main specimens table — the Specimens table is empty, always use SampleSpecimens. Path from WorkOrders: WorkOrders → WorkOrderTests.RecordId → SampleSpecimens.Id.</t>
+  </si>
+  <si>
+    <t>Use SpecimenNumber for display e.g. 05.24000003.S1-A. IsDeleted=false for active. SampleId links to parent Sample. ProjectId links to Projects. OrganizationId links to AbpOrganizationUnits. CheckedInBy and PickedupBy link to AbpUsers.Id.</t>
+  </si>
+  <si>
+    <t>LimsTests</t>
+  </si>
+  <si>
+    <t>Lab tests performed on sample specimens. Each test links to a SampleSpecimen and a Sample.</t>
+  </si>
+  <si>
+    <t>TestDate</t>
+  </si>
+  <si>
+    <t>IsDeleted=false for active. SampleSpecimenId links to SampleSpecimens. SampleId links to Samples. LabTechnician, TestBrokenBy, TestSignedBy, TestReviewedBy, TestApprovedBy all link to AbpUsers.Id. TestFinalized=true for completed tests. IsBilled=true for billed tests.</t>
+  </si>
+  <si>
     <t>ColumnName</t>
   </si>
   <si>
@@ -767,7 +845,7 @@
     <t>Soft delete. Always write "AbpRoles"."IsDeleted" = false — never bare "IsDeleted"</t>
   </si>
   <si>
-    <t>Soft delete. Always write "Clients"."IsDeleted" = false — never bare "IsDeleted"</t>
+    <t>Soft delete. Always write "Clients"."IsDeleted" = false — never bare "IsDeleted".</t>
   </si>
   <si>
     <t>Soft delete. Always write "Phases"."IsDeleted" = false — never bare "IsDeleted"</t>
@@ -779,6 +857,531 @@
     <t>NEVER SELECT this column. Use WorkOrderNumber for display instead.</t>
   </si>
   <si>
+    <t>Primary key integer. Referenced by WorkOrders.ClientId and Projects.ClientId.</t>
+  </si>
+  <si>
+    <t>Human-readable client name. ALWAYS USE FOR DISPLAY AND FILTERING. Use ILIKE for search.</t>
+  </si>
+  <si>
+    <t>CompanyId</t>
+  </si>
+  <si>
+    <t>Parent company this client belongs to.</t>
+  </si>
+  <si>
+    <t>-&gt; Companies.Id</t>
+  </si>
+  <si>
+    <t>User who created this client record — INTEGER FK</t>
+  </si>
+  <si>
+    <t>Address1</t>
+  </si>
+  <si>
+    <t>Street address line 1.</t>
+  </si>
+  <si>
+    <t>Address2</t>
+  </si>
+  <si>
+    <t>Street address line 2 e.g. Suite number.</t>
+  </si>
+  <si>
+    <t>Client city.</t>
+  </si>
+  <si>
+    <t>StateName</t>
+  </si>
+  <si>
+    <t>Readable state name e.g. FL, TX. Use this for state filtering not State column.</t>
+  </si>
+  <si>
+    <t>Zipcode</t>
+  </si>
+  <si>
+    <t>Zip code.</t>
+  </si>
+  <si>
+    <t>Phonenumber</t>
+  </si>
+  <si>
+    <t>Client phone number</t>
+  </si>
+  <si>
+    <t>website</t>
+  </si>
+  <si>
+    <t>Client website URL.</t>
+  </si>
+  <si>
+    <t>NULL for most records — skip in SELECT.</t>
+  </si>
+  <si>
+    <t>Client status integer code</t>
+  </si>
+  <si>
+    <t>Date client record was created</t>
+  </si>
+  <si>
+    <t>Faxnumber</t>
+  </si>
+  <si>
+    <t>OldClientId</t>
+  </si>
+  <si>
+    <t>NULL for most records — use StateName instead.</t>
+  </si>
+  <si>
+    <t>ClientNotes</t>
+  </si>
+  <si>
+    <t>Primary key integer. Referenced by Clients.CompanyId.</t>
+  </si>
+  <si>
+    <t>Human-readable company name. ALWAYS USE FOR DISPLAY AND FILTERING. Use ILIKE for search.</t>
+  </si>
+  <si>
+    <t>CompanyCode</t>
+  </si>
+  <si>
+    <t>Short company code. Has data.</t>
+  </si>
+  <si>
+    <t>CorporateId</t>
+  </si>
+  <si>
+    <t>Parent corporate entity — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>-&gt; Corporates.Id</t>
+  </si>
+  <si>
+    <t>Company status integer code. Has data.</t>
+  </si>
+  <si>
+    <t>Date company record was created in DB.</t>
+  </si>
+  <si>
+    <t>User who created — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>Soft delete. Always write "Companies"."IsDeleted" = false — never bare "IsDeleted".</t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>CompanyNotes</t>
+  </si>
+  <si>
+    <t>Contact first name. Use FirstName + LastName for full name display.</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Contact last name. Use FirstName + LastName for full name display.</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Contact email address. Has data.</t>
+  </si>
+  <si>
+    <t>Contact phone number. Has data.</t>
+  </si>
+  <si>
+    <t>MobileNumber</t>
+  </si>
+  <si>
+    <t>Contact mobile number.</t>
+  </si>
+  <si>
+    <t>Client this contact belongs to — INTEGER FK. JOIN Clients ON ClientId=Id.</t>
+  </si>
+  <si>
+    <t>Date contact record was created.</t>
+  </si>
+  <si>
+    <t>Soft delete. Always write "Contacts"."IsDeleted" = false — never bare "IsDeleted".</t>
+  </si>
+  <si>
+    <t>Primary key. Referenced by Companies.CorporateId.</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Boolean — true means active corporate. Use = true to filter active.</t>
+  </si>
+  <si>
+    <t>Corporate name. ALWAYS USE FOR DISPLAY.</t>
+  </si>
+  <si>
+    <t>Soft delete. Always write "Corporates"."IsDeleted" = false.</t>
+  </si>
+  <si>
+    <t>Status integer code.</t>
+  </si>
+  <si>
+    <t>Date record was created.</t>
+  </si>
+  <si>
+    <t>Department name. ALWAYS USE FOR DISPLAY AND FILTERING.</t>
+  </si>
+  <si>
+    <t>Boolean — true means active department. Use = true to filter active.</t>
+  </si>
+  <si>
+    <t>Office this department belongs to — INTEGER FK. JOIN Offices ON OfficeId=Id.</t>
+  </si>
+  <si>
+    <t>Short department code e.g. 10. Has data.</t>
+  </si>
+  <si>
+    <t>Soft delete. Always write "Departments"."IsDeleted" = false.</t>
+  </si>
+  <si>
+    <t>Primary key. Referenced by SampleSpecimens.SampleId.</t>
+  </si>
+  <si>
+    <t>Human-readable sample number e.g. 05.24000003.S1. ALWAYS USE FOR DISPLAY.</t>
+  </si>
+  <si>
+    <t>SampleType</t>
+  </si>
+  <si>
+    <t>Type of sample e.g. Soil, Concrete. Has data.</t>
+  </si>
+  <si>
+    <t>Sample status e.g. S. Has data.</t>
+  </si>
+  <si>
+    <t>SampleDate</t>
+  </si>
+  <si>
+    <t>Date sample was collected. Has data.</t>
+  </si>
+  <si>
+    <t>SampleLocation</t>
+  </si>
+  <si>
+    <t>Location description where sample was collected e.g. NW CORNER OF PAD. Has data.</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Sample color description e.g. Dark Brown. Has data.</t>
+  </si>
+  <si>
+    <t>Project this sample belongs to — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>Organization unit — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>SamplePickedupBy</t>
+  </si>
+  <si>
+    <t>User who picked up the sample — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>SampleCheckinBy</t>
+  </si>
+  <si>
+    <t>User who checked in the sample — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>SampleReceivedBy</t>
+  </si>
+  <si>
+    <t>User who received the sample — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>SamplePickedupDate</t>
+  </si>
+  <si>
+    <t>Date sample was picked up.</t>
+  </si>
+  <si>
+    <t>SampleCheckinDate</t>
+  </si>
+  <si>
+    <t>Date sample was checked in.</t>
+  </si>
+  <si>
+    <t>SampleReceivedDate</t>
+  </si>
+  <si>
+    <t>Date sample was received at lab.</t>
+  </si>
+  <si>
+    <t>Soft delete. Always write "Samples"."IsDeleted" = false — never bare "IsDeleted".</t>
+  </si>
+  <si>
+    <t>AlternateSampleNumber</t>
+  </si>
+  <si>
+    <t>Alternate sample identifier.</t>
+  </si>
+  <si>
+    <t>GroupSymbol</t>
+  </si>
+  <si>
+    <t>Soil classification symbol e.g. SC. Has data.</t>
+  </si>
+  <si>
+    <t>SampleComments</t>
+  </si>
+  <si>
+    <t>Comments about the sample.</t>
+  </si>
+  <si>
+    <t>Primary key. Referenced by WorkOrderTests.RecordId — this is how specimens link to work orders.</t>
+  </si>
+  <si>
+    <t>Human-readable specimen number e.g. 05.24000003.S1-A. ALWAYS USE FOR DISPLAY.</t>
+  </si>
+  <si>
+    <t>Parent sample — INTEGER FK. JOIN Samples ON SampleId=Id</t>
+  </si>
+  <si>
+    <t>Human-readable sample number this specimen belongs to. Has data.</t>
+  </si>
+  <si>
+    <t>Specimen status e.g. S. Has data.</t>
+  </si>
+  <si>
+    <t>Sample type integer code. Has data.</t>
+  </si>
+  <si>
+    <t>SpecimenDate</t>
+  </si>
+  <si>
+    <t>Date specimen was created.</t>
+  </si>
+  <si>
+    <t>CheckInDate</t>
+  </si>
+  <si>
+    <t>Date specimen was checked in to lab. Has data.</t>
+  </si>
+  <si>
+    <t>CheckedInBy</t>
+  </si>
+  <si>
+    <t>User who checked in — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>PickedupBy</t>
+  </si>
+  <si>
+    <t>User who picked up specimen — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>RecievedBy</t>
+  </si>
+  <si>
+    <t>User who received specimen — INTEGER FK. Note: column name is misspelled as RecievedBy not ReceivedBy.</t>
+  </si>
+  <si>
+    <t>RecievedDate</t>
+  </si>
+  <si>
+    <t>Date specimen was received. Note: column name is misspelled as RecievedDate.</t>
+  </si>
+  <si>
+    <t>Lab</t>
+  </si>
+  <si>
+    <t>Lab integer code. Has data.</t>
+  </si>
+  <si>
+    <t>Project this specimen belongs to — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Location description.</t>
+  </si>
+  <si>
+    <t>TestAge</t>
+  </si>
+  <si>
+    <t>Test age value.</t>
+  </si>
+  <si>
+    <t>SpecimenSize</t>
+  </si>
+  <si>
+    <t>Specimen size integer code. Has data.</t>
+  </si>
+  <si>
+    <t>FieldCure</t>
+  </si>
+  <si>
+    <t>Boolean — true if field cured.</t>
+  </si>
+  <si>
+    <t>Hold</t>
+  </si>
+  <si>
+    <t>Boolean — true if specimen is on hold.</t>
+  </si>
+  <si>
+    <t>HoldComments</t>
+  </si>
+  <si>
+    <t>Comments when specimen is on hold.</t>
+  </si>
+  <si>
+    <t>IsOutsourced</t>
+  </si>
+  <si>
+    <t>Boolean — true if outsourced to third party lab.</t>
+  </si>
+  <si>
+    <t>Soft delete. Always write "SampleSpecimens"."IsDeleted" = false — never bare "IsDeleted".</t>
+  </si>
+  <si>
+    <t>SampleSpecimenId</t>
+  </si>
+  <si>
+    <t>Specimen this test belongs to — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>Sample this test belongs to — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Test type integer code. Has data.</t>
+  </si>
+  <si>
+    <t>Date test was performed. Has data.</t>
+  </si>
+  <si>
+    <t>TestBreakDate</t>
+  </si>
+  <si>
+    <t>Date test was broken/completed. Has data.</t>
+  </si>
+  <si>
+    <t>Test age value e.g. 9, 29 days. Has data.</t>
+  </si>
+  <si>
+    <t>TestRecord</t>
+  </si>
+  <si>
+    <t>Test record integer reference. Has data.</t>
+  </si>
+  <si>
+    <t>TestFinalized</t>
+  </si>
+  <si>
+    <t>Boolean — true if test is finalized/completed.</t>
+  </si>
+  <si>
+    <t>Boolean — true if test has been billed.</t>
+  </si>
+  <si>
+    <t>BilledDate</t>
+  </si>
+  <si>
+    <t>Date test was billed.</t>
+  </si>
+  <si>
+    <t>LabTechnician</t>
+  </si>
+  <si>
+    <t>Lab technician who performed test — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>TestBrokenBy</t>
+  </si>
+  <si>
+    <t>User who broke/completed test — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>TestSignedBy</t>
+  </si>
+  <si>
+    <t>User who signed the test — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>TestSignedDate</t>
+  </si>
+  <si>
+    <t>Date test was signed. Has data.</t>
+  </si>
+  <si>
+    <t>TestReviewedBy</t>
+  </si>
+  <si>
+    <t>User who reviewed the test — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>TestReviewedDate</t>
+  </si>
+  <si>
+    <t>Date test was reviewed. Has data.</t>
+  </si>
+  <si>
+    <t>TestApprovedBy</t>
+  </si>
+  <si>
+    <t>User who approved the test — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>TestApprovedDate</t>
+  </si>
+  <si>
+    <t>Date test was approved. Has data.</t>
+  </si>
+  <si>
+    <t>SendToEor</t>
+  </si>
+  <si>
+    <t>Boolean — true if sent to Engineer of Record.</t>
+  </si>
+  <si>
+    <t>SendToPm</t>
+  </si>
+  <si>
+    <t>Boolean — true if sent to Project Manager.</t>
+  </si>
+  <si>
+    <t>AttentionRequired</t>
+  </si>
+  <si>
+    <t>Boolean — true if attention is required.</t>
+  </si>
+  <si>
+    <t>TestNotes</t>
+  </si>
+  <si>
+    <t>Notes about the test.</t>
+  </si>
+  <si>
+    <t>TestBillingCode</t>
+  </si>
+  <si>
+    <t>Billing code for the test.</t>
+  </si>
+  <si>
+    <t>TestCost</t>
+  </si>
+  <si>
+    <t>Cost of the test.</t>
+  </si>
+  <si>
+    <t>Soft delete. Always write "LimsTests"."IsDeleted" = false — never bare "IsDeleted".</t>
+  </si>
+  <si>
     <t>FromTable</t>
   </si>
   <si>
@@ -875,9 +1478,6 @@
     <t>Equipment item</t>
   </si>
   <si>
-    <t>Samples</t>
-  </si>
-  <si>
     <t>Parent sample</t>
   </si>
   <si>
@@ -920,6 +1520,78 @@
     <t>Parent project for hierarchy</t>
   </si>
   <si>
+    <t>Each client belongs to one company</t>
+  </si>
+  <si>
+    <t>User who created this client</t>
+  </si>
+  <si>
+    <t>Parent corporate entity</t>
+  </si>
+  <si>
+    <t>User who created this company</t>
+  </si>
+  <si>
+    <t>Each contact belongs to one client</t>
+  </si>
+  <si>
+    <t>User who created this corporate</t>
+  </si>
+  <si>
+    <t>Project this sample belongs to</t>
+  </si>
+  <si>
+    <t>User who created the sample</t>
+  </si>
+  <si>
+    <t>User who picked up the sample</t>
+  </si>
+  <si>
+    <t>User who checked in the sample</t>
+  </si>
+  <si>
+    <t>User who received at lab</t>
+  </si>
+  <si>
+    <t>Parent sample this specimen belongs to</t>
+  </si>
+  <si>
+    <t>User who created</t>
+  </si>
+  <si>
+    <t>User who checked in the specimen</t>
+  </si>
+  <si>
+    <t>User who picked up the specimen</t>
+  </si>
+  <si>
+    <t>User who received the specimen</t>
+  </si>
+  <si>
+    <t>Specimen this test belongs to</t>
+  </si>
+  <si>
+    <t>Sample this test belongs to</t>
+  </si>
+  <si>
+    <t>Lab technician who performed the test</t>
+  </si>
+  <si>
+    <t>User who broke/completed the test</t>
+  </si>
+  <si>
+    <t>User who signed the test</t>
+  </si>
+  <si>
+    <t>User who reviewed the test</t>
+  </si>
+  <si>
+    <t>User who approved the test</t>
+  </si>
+  <si>
+    <t>User who created this record</t>
+  </si>
+  <si>
     <t>TriggerWords</t>
   </si>
   <si>
@@ -959,9 +1631,6 @@
     <t>form,forms</t>
   </si>
   <si>
-    <t>client,clients</t>
-  </si>
-  <si>
     <t>equipment,equipments</t>
   </si>
   <si>
@@ -993,6 +1662,27 @@
   </si>
   <si>
     <t>permission,permissions,granted</t>
+  </si>
+  <si>
+    <t>client,clients,clientname</t>
+  </si>
+  <si>
+    <t>contact,contacts,contactname</t>
+  </si>
+  <si>
+    <t>corporate,corporates,corporatename</t>
+  </si>
+  <si>
+    <t>department,departments</t>
+  </si>
+  <si>
+    <t>sample,samples,samplenumber</t>
+  </si>
+  <si>
+    <t>specimen,specimens,samplespecimen,specimenumber</t>
+  </si>
+  <si>
+    <t>limstest,limstests,labtest,labtests,test,tests,lims,lab,labs,laboratory,result,results,labresult</t>
   </si>
 </sst>
 </file>
@@ -2017,8 +2707,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D21"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2041,7 +2731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="10" customFormat="1" ht="144" customHeight="1" spans="1:4">
+    <row r="2" s="10" customFormat="1" ht="144" hidden="1" customHeight="1" spans="1:4">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2055,7 +2745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="64" customHeight="1" spans="1:4">
+    <row r="3" ht="64" hidden="1" customHeight="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -2069,7 +2759,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1" spans="1:4">
+    <row r="4" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
@@ -2083,7 +2773,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1" spans="1:4">
+    <row r="5" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -2097,7 +2787,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1" spans="1:4">
+    <row r="6" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
@@ -2111,7 +2801,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:4">
+    <row r="7" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -2125,7 +2815,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" spans="1:4">
+    <row r="8" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
@@ -2139,7 +2829,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" spans="1:4">
+    <row r="9" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
@@ -2153,7 +2843,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" spans="1:4">
+    <row r="10" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A10" s="4" t="s">
         <v>33</v>
       </c>
@@ -2167,7 +2857,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" spans="1:4">
+    <row r="11" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A11" s="3" t="s">
         <v>37</v>
       </c>
@@ -2195,7 +2885,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="1:4">
+    <row r="13" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A13" s="3" t="s">
         <v>44</v>
       </c>
@@ -2203,122 +2893,228 @@
         <v>45</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" ht="30" hidden="1" customHeight="1" spans="1:4">
+      <c r="A14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="1:4">
-      <c r="A14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A15" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" spans="1:4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A16" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1" spans="1:4">
+    <row r="17" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" spans="1:4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A18" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" hidden="1" spans="1:4">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" hidden="1" spans="1:4">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" ht="158.4" spans="1:4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" ht="158.4" hidden="1" spans="1:4">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" ht="57.6" hidden="1" spans="1:4">
+      <c r="A22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" ht="43.2" spans="1:4">
+      <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" ht="28.8" spans="1:4">
+      <c r="A24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" ht="43.2" spans="1:4">
+      <c r="A25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" ht="57.6" spans="1:4">
+      <c r="A26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" ht="57.6" spans="1:4">
+      <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" ht="57.6" spans="1:4">
+      <c r="A28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D22" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Clients"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -2327,7 +3123,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D242"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -2341,13 +3137,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -2355,10 +3151,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>22</v>
@@ -2372,7 +3168,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -2383,10 +3179,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -2397,13 +3193,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -2411,10 +3207,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D6" s="4"/>
     </row>
@@ -2423,13 +3219,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -2437,13 +3233,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -2451,13 +3247,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -2465,13 +3261,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -2479,13 +3275,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -2493,13 +3289,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -2507,10 +3303,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>22</v>
@@ -2521,10 +3317,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>22</v>
@@ -2535,10 +3331,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>22</v>
@@ -2549,10 +3345,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>22</v>
@@ -2563,10 +3359,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>22</v>
@@ -2577,10 +3373,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>22</v>
@@ -2591,10 +3387,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>22</v>
@@ -2602,13 +3398,13 @@
     </row>
     <row r="20" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>22</v>
@@ -2616,13 +3412,13 @@
     </row>
     <row r="21" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>22</v>
@@ -2630,13 +3426,13 @@
     </row>
     <row r="22" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>22</v>
@@ -2644,83 +3440,83 @@
     </row>
     <row r="23" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A24" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A26" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A28" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>22</v>
@@ -2728,13 +3524,13 @@
     </row>
     <row r="29" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>22</v>
@@ -2745,10 +3541,10 @@
         <v>8</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>22</v>
@@ -2762,7 +3558,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>22</v>
@@ -2776,7 +3572,7 @@
         <v>18</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>22</v>
@@ -2787,10 +3583,10 @@
         <v>8</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>22</v>
@@ -2801,10 +3597,10 @@
         <v>8</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>22</v>
@@ -2815,10 +3611,10 @@
         <v>8</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>22</v>
@@ -2829,10 +3625,10 @@
         <v>8</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>22</v>
@@ -2843,10 +3639,10 @@
         <v>8</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>22</v>
@@ -2857,13 +3653,13 @@
         <v>8</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -2871,30 +3667,30 @@
         <v>8</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1" spans="1:4">
+    <row r="40" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A40" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1" spans="1:4">
+    <row r="41" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A41" s="4" t="s">
         <v>12</v>
       </c>
@@ -2902,91 +3698,91 @@
         <v>14</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1" spans="1:4">
+    <row r="42" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A42" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1" spans="1:4">
+    <row r="43" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A43" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1" spans="1:4">
+    <row r="44" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A44" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1" spans="1:4">
+    <row r="45" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A45" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1" spans="1:4">
+    <row r="46" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A46" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1" spans="1:4">
+    <row r="47" ht="30" hidden="1" customHeight="1" spans="1:4">
       <c r="A47" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>22</v>
@@ -2997,10 +3793,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>22</v>
@@ -3014,7 +3810,7 @@
         <v>18</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>22</v>
@@ -3025,10 +3821,10 @@
         <v>16</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>22</v>
@@ -3039,10 +3835,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>22</v>
@@ -3053,10 +3849,10 @@
         <v>20</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>22</v>
@@ -3067,13 +3863,13 @@
         <v>20</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3081,13 +3877,13 @@
         <v>20</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3095,10 +3891,10 @@
         <v>24</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>22</v>
@@ -3109,13 +3905,13 @@
         <v>24</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3123,13 +3919,13 @@
         <v>24</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3137,13 +3933,13 @@
         <v>24</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
     </row>
     <row r="59" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3151,13 +3947,13 @@
         <v>24</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3165,10 +3961,10 @@
         <v>24</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>22</v>
@@ -3179,10 +3975,10 @@
         <v>24</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>22</v>
@@ -3193,10 +3989,10 @@
         <v>24</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>22</v>
@@ -3207,10 +4003,10 @@
         <v>33</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>22</v>
@@ -3221,13 +4017,13 @@
         <v>33</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3235,13 +4031,13 @@
         <v>33</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3252,7 +4048,7 @@
         <v>35</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>22</v>
@@ -3263,10 +4059,10 @@
         <v>33</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>22</v>
@@ -3277,10 +4073,10 @@
         <v>33</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>22</v>
@@ -3291,35 +4087,35 @@
         <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70" ht="28.8" hidden="1" spans="1:4">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B70" t="s">
         <v>18</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71" hidden="1" spans="1:4">
       <c r="A71" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B71" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
     </row>
     <row r="72" hidden="1" spans="1:4">
@@ -3327,204 +4123,204 @@
         <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="D72" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" hidden="1" spans="1:4">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" hidden="1" spans="1:4">
       <c r="A74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
     </row>
     <row r="75" hidden="1" spans="1:4">
       <c r="A75" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" hidden="1" spans="1:4">
       <c r="A76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" hidden="1" spans="1:4">
       <c r="A77" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B77" t="s">
         <v>18</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78" hidden="1" spans="1:4">
       <c r="A78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B78" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="D78" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
     </row>
     <row r="79" hidden="1" spans="1:4">
       <c r="A79" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B79" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
     </row>
     <row r="80" hidden="1" spans="1:4">
       <c r="A80" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B80" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
     </row>
     <row r="81" hidden="1" spans="1:4">
       <c r="A81" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B81" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="D81" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
     </row>
     <row r="82" hidden="1" spans="1:4">
       <c r="A82" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B82" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="D82" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
     </row>
     <row r="83" hidden="1" spans="1:4">
       <c r="A83" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B83" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
     </row>
     <row r="84" hidden="1" spans="1:4">
       <c r="A84" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" hidden="1" spans="1:4">
       <c r="A85" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B85" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86" hidden="1" spans="1:4">
       <c r="A86" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B86" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
     </row>
     <row r="87" hidden="1" spans="1:4">
       <c r="A87" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B87" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="D87" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
     </row>
     <row r="88" hidden="1" spans="1:4">
       <c r="A88" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B88" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="D88" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="89" ht="72" hidden="1" spans="1:4">
@@ -3532,10 +4328,10 @@
         <v>4</v>
       </c>
       <c r="B89" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
     </row>
     <row r="90" hidden="1" spans="1:4">
@@ -3543,129 +4339,129 @@
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" hidden="1" spans="1:4">
       <c r="A91" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B91" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
     </row>
     <row r="92" hidden="1" spans="1:4">
       <c r="A92" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B92" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
     </row>
     <row r="93" hidden="1" spans="1:4">
       <c r="A93" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B93" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
     </row>
     <row r="94" hidden="1" spans="1:4">
       <c r="A94" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B94" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
     </row>
     <row r="95" hidden="1" spans="1:4">
       <c r="A95" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B95" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
     </row>
     <row r="96" hidden="1" spans="1:4">
       <c r="A96" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B96" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
     </row>
     <row r="97" hidden="1" spans="1:4">
       <c r="A97" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B97" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="D97" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="98" ht="28.8" hidden="1" spans="1:4">
       <c r="A98" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="D98" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="99" ht="28.8" hidden="1" spans="1:4">
       <c r="A99" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B99" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="100" hidden="1" spans="1:4">
       <c r="A100" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B100" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
     </row>
     <row r="101" hidden="1" spans="1:4">
@@ -3673,32 +4469,32 @@
         <v>4</v>
       </c>
       <c r="B101" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="102" ht="28.8" spans="1:4">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="102" ht="28.8" hidden="1" spans="1:4">
       <c r="A102" t="s">
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
     </row>
     <row r="103" hidden="1" spans="1:4">
       <c r="A103" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B103" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
     </row>
     <row r="104" hidden="1" spans="1:4">
@@ -3706,10 +4502,10 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
     </row>
     <row r="105" hidden="1" spans="1:4">
@@ -3717,10 +4513,10 @@
         <v>16</v>
       </c>
       <c r="B105" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106" hidden="1" spans="1:4">
@@ -3728,21 +4524,21 @@
         <v>40</v>
       </c>
       <c r="B106" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" hidden="1" spans="1:4">
       <c r="A107" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B107" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
     </row>
     <row r="108" hidden="1" spans="1:4">
@@ -3750,17 +4546,1497 @@
         <v>4</v>
       </c>
       <c r="B108" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C108" t="s">
-        <v>244</v>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="109" hidden="1" spans="1:4">
+      <c r="A109" t="s">
+        <v>40</v>
+      </c>
+      <c r="B109" t="s">
+        <v>99</v>
+      </c>
+      <c r="C109" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="110" hidden="1" spans="1:4">
+      <c r="A110" t="s">
+        <v>40</v>
+      </c>
+      <c r="B110" t="s">
+        <v>42</v>
+      </c>
+      <c r="C110" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="111" hidden="1" spans="1:4">
+      <c r="A111" t="s">
+        <v>40</v>
+      </c>
+      <c r="B111" t="s">
+        <v>272</v>
+      </c>
+      <c r="C111" t="s">
+        <v>273</v>
+      </c>
+      <c r="D111" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="112" hidden="1" spans="1:4">
+      <c r="A112" t="s">
+        <v>40</v>
+      </c>
+      <c r="B112" t="s">
+        <v>112</v>
+      </c>
+      <c r="C112" t="s">
+        <v>275</v>
+      </c>
+      <c r="D112" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="113" hidden="1" spans="1:3">
+      <c r="A113" t="s">
+        <v>40</v>
+      </c>
+      <c r="B113" t="s">
+        <v>276</v>
+      </c>
+      <c r="C113" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="114" hidden="1" spans="1:3">
+      <c r="A114" t="s">
+        <v>40</v>
+      </c>
+      <c r="B114" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="115" hidden="1" spans="1:3">
+      <c r="A115" t="s">
+        <v>40</v>
+      </c>
+      <c r="B115" t="s">
+        <v>163</v>
+      </c>
+      <c r="C115" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="116" hidden="1" spans="1:3">
+      <c r="A116" t="s">
+        <v>40</v>
+      </c>
+      <c r="B116" t="s">
+        <v>281</v>
+      </c>
+      <c r="C116" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="117" hidden="1" spans="1:3">
+      <c r="A117" t="s">
+        <v>40</v>
+      </c>
+      <c r="B117" t="s">
+        <v>283</v>
+      </c>
+      <c r="C117" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="118" hidden="1" spans="1:3">
+      <c r="A118" t="s">
+        <v>40</v>
+      </c>
+      <c r="B118" t="s">
+        <v>285</v>
+      </c>
+      <c r="C118" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="119" hidden="1" spans="1:3">
+      <c r="A119" t="s">
+        <v>40</v>
+      </c>
+      <c r="B119" t="s">
+        <v>287</v>
+      </c>
+      <c r="C119" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="120" hidden="1" spans="1:3">
+      <c r="A120" t="s">
+        <v>40</v>
+      </c>
+      <c r="B120" t="s">
+        <v>161</v>
+      </c>
+      <c r="C120" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="121" hidden="1" spans="1:3">
+      <c r="A121" t="s">
+        <v>40</v>
+      </c>
+      <c r="B121" t="s">
+        <v>102</v>
+      </c>
+      <c r="C121" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="122" hidden="1" spans="1:3">
+      <c r="A122" t="s">
+        <v>40</v>
+      </c>
+      <c r="B122" t="s">
+        <v>241</v>
+      </c>
+      <c r="C122" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="123" hidden="1" spans="1:3">
+      <c r="A123" t="s">
+        <v>40</v>
+      </c>
+      <c r="B123" t="s">
+        <v>292</v>
+      </c>
+      <c r="C123" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="124" hidden="1" spans="1:3">
+      <c r="A124" t="s">
+        <v>40</v>
+      </c>
+      <c r="B124" t="s">
+        <v>293</v>
+      </c>
+      <c r="C124" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="125" hidden="1" spans="1:3">
+      <c r="A125" t="s">
+        <v>40</v>
+      </c>
+      <c r="B125" t="s">
+        <v>165</v>
+      </c>
+      <c r="C125" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="126" hidden="1" spans="1:3">
+      <c r="A126" t="s">
+        <v>40</v>
+      </c>
+      <c r="B126" t="s">
+        <v>295</v>
+      </c>
+      <c r="C126" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="127" hidden="1" spans="1:3">
+      <c r="A127" t="s">
+        <v>73</v>
+      </c>
+      <c r="B127" t="s">
+        <v>99</v>
+      </c>
+      <c r="C127" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="128" hidden="1" spans="1:3">
+      <c r="A128" t="s">
+        <v>73</v>
+      </c>
+      <c r="B128" t="s">
+        <v>75</v>
+      </c>
+      <c r="C128" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="129" hidden="1" spans="1:4">
+      <c r="A129" t="s">
+        <v>73</v>
+      </c>
+      <c r="B129" t="s">
+        <v>298</v>
+      </c>
+      <c r="C129" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="130" hidden="1" spans="1:4">
+      <c r="A130" t="s">
+        <v>73</v>
+      </c>
+      <c r="B130" t="s">
+        <v>300</v>
+      </c>
+      <c r="C130" t="s">
+        <v>301</v>
+      </c>
+      <c r="D130" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="131" hidden="1" spans="1:4">
+      <c r="A131" t="s">
+        <v>73</v>
+      </c>
+      <c r="B131" t="s">
+        <v>102</v>
+      </c>
+      <c r="C131" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="132" hidden="1" spans="1:4">
+      <c r="A132" t="s">
+        <v>73</v>
+      </c>
+      <c r="B132" t="s">
+        <v>241</v>
+      </c>
+      <c r="C132" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="133" hidden="1" spans="1:4">
+      <c r="A133" t="s">
+        <v>73</v>
+      </c>
+      <c r="B133" t="s">
+        <v>112</v>
+      </c>
+      <c r="C133" t="s">
+        <v>305</v>
+      </c>
+      <c r="D133" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="134" hidden="1" spans="1:4">
+      <c r="A134" t="s">
+        <v>73</v>
+      </c>
+      <c r="B134" t="s">
+        <v>154</v>
+      </c>
+      <c r="C134" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="135" hidden="1" spans="1:4">
+      <c r="A135" t="s">
+        <v>73</v>
+      </c>
+      <c r="B135" t="s">
+        <v>167</v>
+      </c>
+      <c r="C135" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="136" hidden="1" spans="1:4">
+      <c r="A136" t="s">
+        <v>73</v>
+      </c>
+      <c r="B136" t="s">
+        <v>163</v>
+      </c>
+      <c r="C136" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="137" hidden="1" spans="1:4">
+      <c r="A137" t="s">
+        <v>73</v>
+      </c>
+      <c r="B137" t="s">
+        <v>165</v>
+      </c>
+      <c r="C137" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="138" hidden="1" spans="1:4">
+      <c r="A138" t="s">
+        <v>73</v>
+      </c>
+      <c r="B138" t="s">
+        <v>283</v>
+      </c>
+      <c r="C138" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="139" hidden="1" spans="1:4">
+      <c r="A139" t="s">
+        <v>73</v>
+      </c>
+      <c r="B139" t="s">
+        <v>285</v>
+      </c>
+      <c r="C139" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="140" hidden="1" spans="1:4">
+      <c r="A140" t="s">
+        <v>73</v>
+      </c>
+      <c r="B140" t="s">
+        <v>307</v>
+      </c>
+      <c r="C140" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="141" hidden="1" spans="1:4">
+      <c r="A141" t="s">
+        <v>73</v>
+      </c>
+      <c r="B141" t="s">
+        <v>308</v>
+      </c>
+      <c r="C141" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="142" hidden="1" spans="1:4">
+      <c r="A142" t="s">
+        <v>77</v>
+      </c>
+      <c r="B142" t="s">
+        <v>99</v>
+      </c>
+      <c r="C142" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="143" hidden="1" spans="1:4">
+      <c r="A143" t="s">
+        <v>77</v>
+      </c>
+      <c r="B143" t="s">
+        <v>79</v>
+      </c>
+      <c r="C143" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="144" hidden="1" spans="1:4">
+      <c r="A144" t="s">
+        <v>77</v>
+      </c>
+      <c r="B144" t="s">
+        <v>310</v>
+      </c>
+      <c r="C144" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="145" hidden="1" spans="1:4">
+      <c r="A145" t="s">
+        <v>77</v>
+      </c>
+      <c r="B145" t="s">
+        <v>312</v>
+      </c>
+      <c r="C145" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="146" hidden="1" spans="1:4">
+      <c r="A146" t="s">
+        <v>77</v>
+      </c>
+      <c r="B146" t="s">
+        <v>184</v>
+      </c>
+      <c r="C146" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="147" hidden="1" spans="1:4">
+      <c r="A147" t="s">
+        <v>77</v>
+      </c>
+      <c r="B147" t="s">
+        <v>315</v>
+      </c>
+      <c r="C147" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="148" hidden="1" spans="1:4">
+      <c r="A148" t="s">
+        <v>77</v>
+      </c>
+      <c r="B148" t="s">
+        <v>109</v>
+      </c>
+      <c r="C148" t="s">
+        <v>317</v>
+      </c>
+      <c r="D148" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="149" hidden="1" spans="1:4">
+      <c r="A149" t="s">
+        <v>77</v>
+      </c>
+      <c r="B149" t="s">
+        <v>112</v>
+      </c>
+      <c r="C149" t="s">
+        <v>305</v>
+      </c>
+      <c r="D149" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="150" hidden="1" spans="1:4">
+      <c r="A150" t="s">
+        <v>77</v>
+      </c>
+      <c r="B150" t="s">
+        <v>102</v>
+      </c>
+      <c r="C150" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="151" hidden="1" spans="1:4">
+      <c r="A151" t="s">
+        <v>77</v>
+      </c>
+      <c r="B151" t="s">
+        <v>241</v>
+      </c>
+      <c r="C151" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="152" hidden="1" spans="1:4">
+      <c r="A152" t="s">
+        <v>77</v>
+      </c>
+      <c r="B152" t="s">
+        <v>154</v>
+      </c>
+      <c r="C152" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="153" hidden="1" spans="1:4">
+      <c r="A153" t="s">
+        <v>81</v>
+      </c>
+      <c r="B153" t="s">
+        <v>99</v>
+      </c>
+      <c r="C153" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="154" hidden="1" spans="1:4">
+      <c r="A154" t="s">
+        <v>81</v>
+      </c>
+      <c r="B154" t="s">
+        <v>321</v>
+      </c>
+      <c r="C154" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="155" hidden="1" spans="1:4">
+      <c r="A155" t="s">
+        <v>81</v>
+      </c>
+      <c r="B155" t="s">
+        <v>83</v>
+      </c>
+      <c r="C155" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="156" hidden="1" spans="1:4">
+      <c r="A156" t="s">
+        <v>81</v>
+      </c>
+      <c r="B156" t="s">
+        <v>154</v>
+      </c>
+      <c r="C156" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="157" hidden="1" spans="1:4">
+      <c r="A157" t="s">
+        <v>81</v>
+      </c>
+      <c r="B157" t="s">
+        <v>102</v>
+      </c>
+      <c r="C157" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="158" hidden="1" spans="1:4">
+      <c r="A158" t="s">
+        <v>81</v>
+      </c>
+      <c r="B158" t="s">
+        <v>241</v>
+      </c>
+      <c r="C158" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="159" hidden="1" spans="1:4">
+      <c r="A159" t="s">
+        <v>57</v>
+      </c>
+      <c r="B159" t="s">
+        <v>99</v>
+      </c>
+      <c r="C159" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="160" hidden="1" spans="1:4">
+      <c r="A160" t="s">
+        <v>57</v>
+      </c>
+      <c r="B160" t="s">
+        <v>46</v>
+      </c>
+      <c r="C160" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="161" hidden="1" spans="1:4">
+      <c r="A161" t="s">
+        <v>57</v>
+      </c>
+      <c r="B161" t="s">
+        <v>321</v>
+      </c>
+      <c r="C161" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="162" hidden="1" spans="1:4">
+      <c r="A162" t="s">
+        <v>57</v>
+      </c>
+      <c r="B162" t="s">
+        <v>107</v>
+      </c>
+      <c r="C162" t="s">
+        <v>329</v>
+      </c>
+      <c r="D162" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="163" hidden="1" spans="1:4">
+      <c r="A163" t="s">
+        <v>57</v>
+      </c>
+      <c r="B163" t="s">
+        <v>112</v>
+      </c>
+      <c r="C163" t="s">
+        <v>305</v>
+      </c>
+      <c r="D163" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="164" hidden="1" spans="1:4">
+      <c r="A164" t="s">
+        <v>57</v>
+      </c>
+      <c r="B164" t="s">
+        <v>161</v>
+      </c>
+      <c r="C164" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="165" hidden="1" spans="1:4">
+      <c r="A165" t="s">
+        <v>57</v>
+      </c>
+      <c r="B165" t="s">
+        <v>102</v>
+      </c>
+      <c r="C165" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="166" hidden="1" spans="1:4">
+      <c r="A166" t="s">
+        <v>57</v>
+      </c>
+      <c r="B166" t="s">
+        <v>154</v>
+      </c>
+      <c r="C166" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="167" hidden="1" spans="1:4">
+      <c r="A167" t="s">
+        <v>57</v>
+      </c>
+      <c r="B167" t="s">
+        <v>241</v>
+      </c>
+      <c r="C167" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="168" hidden="1" spans="1:4">
+      <c r="A168" t="s">
+        <v>87</v>
+      </c>
+      <c r="B168" t="s">
+        <v>99</v>
+      </c>
+      <c r="C168" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="169" hidden="1" spans="1:4">
+      <c r="A169" t="s">
+        <v>87</v>
+      </c>
+      <c r="B169" t="s">
+        <v>89</v>
+      </c>
+      <c r="C169" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="170" hidden="1" spans="1:4">
+      <c r="A170" t="s">
+        <v>87</v>
+      </c>
+      <c r="B170" t="s">
+        <v>334</v>
+      </c>
+      <c r="C170" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="171" hidden="1" spans="1:4">
+      <c r="A171" t="s">
+        <v>87</v>
+      </c>
+      <c r="B171" t="s">
+        <v>102</v>
+      </c>
+      <c r="C171" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="172" hidden="1" spans="1:4">
+      <c r="A172" t="s">
+        <v>87</v>
+      </c>
+      <c r="B172" t="s">
+        <v>337</v>
+      </c>
+      <c r="C172" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="173" hidden="1" spans="1:4">
+      <c r="A173" t="s">
+        <v>87</v>
+      </c>
+      <c r="B173" t="s">
+        <v>339</v>
+      </c>
+      <c r="C173" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="174" hidden="1" spans="1:4">
+      <c r="A174" t="s">
+        <v>87</v>
+      </c>
+      <c r="B174" t="s">
+        <v>341</v>
+      </c>
+      <c r="C174" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="175" hidden="1" spans="1:4">
+      <c r="A175" t="s">
+        <v>87</v>
+      </c>
+      <c r="B175" t="s">
+        <v>104</v>
+      </c>
+      <c r="C175" t="s">
+        <v>343</v>
+      </c>
+      <c r="D175" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="176" hidden="1" spans="1:4">
+      <c r="A176" t="s">
+        <v>87</v>
+      </c>
+      <c r="B176" t="s">
+        <v>146</v>
+      </c>
+      <c r="C176" t="s">
+        <v>344</v>
+      </c>
+      <c r="D176" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="177" hidden="1" spans="1:4">
+      <c r="A177" t="s">
+        <v>87</v>
+      </c>
+      <c r="B177" t="s">
+        <v>112</v>
+      </c>
+      <c r="C177" t="s">
+        <v>305</v>
+      </c>
+      <c r="D177" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="178" hidden="1" spans="1:4">
+      <c r="A178" t="s">
+        <v>87</v>
+      </c>
+      <c r="B178" t="s">
+        <v>345</v>
+      </c>
+      <c r="C178" t="s">
+        <v>346</v>
+      </c>
+      <c r="D178" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="179" hidden="1" spans="1:4">
+      <c r="A179" t="s">
+        <v>87</v>
+      </c>
+      <c r="B179" t="s">
+        <v>347</v>
+      </c>
+      <c r="C179" t="s">
+        <v>348</v>
+      </c>
+      <c r="D179" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="180" hidden="1" spans="1:4">
+      <c r="A180" t="s">
+        <v>87</v>
+      </c>
+      <c r="B180" t="s">
+        <v>349</v>
+      </c>
+      <c r="C180" t="s">
+        <v>350</v>
+      </c>
+      <c r="D180" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="181" hidden="1" spans="1:4">
+      <c r="A181" t="s">
+        <v>87</v>
+      </c>
+      <c r="B181" t="s">
+        <v>351</v>
+      </c>
+      <c r="C181" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="182" hidden="1" spans="1:4">
+      <c r="A182" t="s">
+        <v>87</v>
+      </c>
+      <c r="B182" t="s">
+        <v>353</v>
+      </c>
+      <c r="C182" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="183" hidden="1" spans="1:4">
+      <c r="A183" t="s">
+        <v>87</v>
+      </c>
+      <c r="B183" t="s">
+        <v>355</v>
+      </c>
+      <c r="C183" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="184" hidden="1" spans="1:4">
+      <c r="A184" t="s">
+        <v>87</v>
+      </c>
+      <c r="B184" t="s">
+        <v>241</v>
+      </c>
+      <c r="C184" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="185" hidden="1" spans="1:4">
+      <c r="A185" t="s">
+        <v>87</v>
+      </c>
+      <c r="B185" t="s">
+        <v>154</v>
+      </c>
+      <c r="C185" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="186" hidden="1" spans="1:4">
+      <c r="A186" t="s">
+        <v>87</v>
+      </c>
+      <c r="B186" t="s">
+        <v>358</v>
+      </c>
+      <c r="C186" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="187" hidden="1" spans="1:4">
+      <c r="A187" t="s">
+        <v>87</v>
+      </c>
+      <c r="B187" t="s">
+        <v>360</v>
+      </c>
+      <c r="C187" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="188" hidden="1" spans="1:4">
+      <c r="A188" t="s">
+        <v>87</v>
+      </c>
+      <c r="B188" t="s">
+        <v>362</v>
+      </c>
+      <c r="C188" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="189" hidden="1" spans="1:4">
+      <c r="A189" t="s">
+        <v>33</v>
+      </c>
+      <c r="B189" t="s">
+        <v>99</v>
+      </c>
+      <c r="C189" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="190" hidden="1" spans="1:4">
+      <c r="A190" t="s">
+        <v>33</v>
+      </c>
+      <c r="B190" t="s">
+        <v>35</v>
+      </c>
+      <c r="C190" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="191" hidden="1" spans="1:4">
+      <c r="A191" t="s">
+        <v>33</v>
+      </c>
+      <c r="B191" t="s">
+        <v>212</v>
+      </c>
+      <c r="C191" t="s">
+        <v>366</v>
+      </c>
+      <c r="D191" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="192" hidden="1" spans="1:4">
+      <c r="A192" t="s">
+        <v>33</v>
+      </c>
+      <c r="B192" t="s">
+        <v>89</v>
+      </c>
+      <c r="C192" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="193" hidden="1" spans="1:4">
+      <c r="A193" t="s">
+        <v>33</v>
+      </c>
+      <c r="B193" t="s">
+        <v>102</v>
+      </c>
+      <c r="C193" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="194" hidden="1" spans="1:4">
+      <c r="A194" t="s">
+        <v>33</v>
+      </c>
+      <c r="B194" t="s">
+        <v>334</v>
+      </c>
+      <c r="C194" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="195" hidden="1" spans="1:4">
+      <c r="A195" t="s">
+        <v>33</v>
+      </c>
+      <c r="B195" t="s">
+        <v>370</v>
+      </c>
+      <c r="C195" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="196" hidden="1" spans="1:4">
+      <c r="A196" t="s">
+        <v>33</v>
+      </c>
+      <c r="B196" t="s">
+        <v>337</v>
+      </c>
+      <c r="C196" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="197" hidden="1" spans="1:4">
+      <c r="A197" t="s">
+        <v>33</v>
+      </c>
+      <c r="B197" t="s">
+        <v>372</v>
+      </c>
+      <c r="C197" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="198" hidden="1" spans="1:4">
+      <c r="A198" t="s">
+        <v>33</v>
+      </c>
+      <c r="B198" t="s">
+        <v>374</v>
+      </c>
+      <c r="C198" t="s">
+        <v>375</v>
+      </c>
+      <c r="D198" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="199" hidden="1" spans="1:4">
+      <c r="A199" t="s">
+        <v>33</v>
+      </c>
+      <c r="B199" t="s">
+        <v>376</v>
+      </c>
+      <c r="C199" t="s">
+        <v>377</v>
+      </c>
+      <c r="D199" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="200" hidden="1" spans="1:4">
+      <c r="A200" t="s">
+        <v>33</v>
+      </c>
+      <c r="B200" t="s">
+        <v>378</v>
+      </c>
+      <c r="C200" t="s">
+        <v>379</v>
+      </c>
+      <c r="D200" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="201" hidden="1" spans="1:4">
+      <c r="A201" t="s">
+        <v>33</v>
+      </c>
+      <c r="B201" t="s">
+        <v>380</v>
+      </c>
+      <c r="C201" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="202" hidden="1" spans="1:4">
+      <c r="A202" t="s">
+        <v>33</v>
+      </c>
+      <c r="B202" t="s">
+        <v>382</v>
+      </c>
+      <c r="C202" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="203" hidden="1" spans="1:4">
+      <c r="A203" t="s">
+        <v>33</v>
+      </c>
+      <c r="B203" t="s">
+        <v>146</v>
+      </c>
+      <c r="C203" t="s">
+        <v>344</v>
+      </c>
+      <c r="D203" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="204" hidden="1" spans="1:4">
+      <c r="A204" t="s">
+        <v>33</v>
+      </c>
+      <c r="B204" t="s">
+        <v>104</v>
+      </c>
+      <c r="C204" t="s">
+        <v>384</v>
+      </c>
+      <c r="D204" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="205" hidden="1" spans="1:4">
+      <c r="A205" t="s">
+        <v>33</v>
+      </c>
+      <c r="B205" t="s">
+        <v>385</v>
+      </c>
+      <c r="C205" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="206" hidden="1" spans="1:4">
+      <c r="A206" t="s">
+        <v>33</v>
+      </c>
+      <c r="B206" t="s">
+        <v>387</v>
+      </c>
+      <c r="C206" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="207" hidden="1" spans="1:4">
+      <c r="A207" t="s">
+        <v>33</v>
+      </c>
+      <c r="B207" t="s">
+        <v>389</v>
+      </c>
+      <c r="C207" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="208" hidden="1" spans="1:4">
+      <c r="A208" t="s">
+        <v>33</v>
+      </c>
+      <c r="B208" t="s">
+        <v>391</v>
+      </c>
+      <c r="C208" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="209" hidden="1" spans="1:4">
+      <c r="A209" t="s">
+        <v>33</v>
+      </c>
+      <c r="B209" t="s">
+        <v>393</v>
+      </c>
+      <c r="C209" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="210" hidden="1" spans="1:4">
+      <c r="A210" t="s">
+        <v>33</v>
+      </c>
+      <c r="B210" t="s">
+        <v>395</v>
+      </c>
+      <c r="C210" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="211" hidden="1" spans="1:4">
+      <c r="A211" t="s">
+        <v>33</v>
+      </c>
+      <c r="B211" t="s">
+        <v>397</v>
+      </c>
+      <c r="C211" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="212" hidden="1" spans="1:4">
+      <c r="A212" t="s">
+        <v>33</v>
+      </c>
+      <c r="B212" t="s">
+        <v>241</v>
+      </c>
+      <c r="C212" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="213" hidden="1" spans="1:4">
+      <c r="A213" t="s">
+        <v>33</v>
+      </c>
+      <c r="B213" t="s">
+        <v>154</v>
+      </c>
+      <c r="C213" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="214" hidden="1" spans="1:4">
+      <c r="A214" t="s">
+        <v>33</v>
+      </c>
+      <c r="B214" t="s">
+        <v>112</v>
+      </c>
+      <c r="C214" t="s">
+        <v>305</v>
+      </c>
+      <c r="D214" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
+      <c r="A215" t="s">
+        <v>93</v>
+      </c>
+      <c r="B215" t="s">
+        <v>99</v>
+      </c>
+      <c r="C215" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="B216" t="s">
+        <v>400</v>
+      </c>
+      <c r="C216" t="s">
+        <v>401</v>
+      </c>
+      <c r="D216" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
+      <c r="B217" t="s">
+        <v>212</v>
+      </c>
+      <c r="C217" t="s">
+        <v>402</v>
+      </c>
+      <c r="D217" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
+      <c r="B218" t="s">
+        <v>403</v>
+      </c>
+      <c r="C218" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
+      <c r="B219" t="s">
+        <v>95</v>
+      </c>
+      <c r="C219" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="B220" t="s">
+        <v>406</v>
+      </c>
+      <c r="C220" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
+      <c r="B221" t="s">
+        <v>387</v>
+      </c>
+      <c r="C221" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
+      <c r="B222" t="s">
+        <v>409</v>
+      </c>
+      <c r="C222" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
+      <c r="B223" t="s">
+        <v>411</v>
+      </c>
+      <c r="C223" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="B224" t="s">
+        <v>208</v>
+      </c>
+      <c r="C224" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4">
+      <c r="B225" t="s">
+        <v>414</v>
+      </c>
+      <c r="C225" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4">
+      <c r="B226" t="s">
+        <v>416</v>
+      </c>
+      <c r="C226" t="s">
+        <v>417</v>
+      </c>
+      <c r="D226" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4">
+      <c r="B227" t="s">
+        <v>418</v>
+      </c>
+      <c r="C227" t="s">
+        <v>419</v>
+      </c>
+      <c r="D227" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4">
+      <c r="B228" t="s">
+        <v>420</v>
+      </c>
+      <c r="C228" t="s">
+        <v>421</v>
+      </c>
+      <c r="D228" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4">
+      <c r="B229" t="s">
+        <v>422</v>
+      </c>
+      <c r="C229" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4">
+      <c r="B230" t="s">
+        <v>424</v>
+      </c>
+      <c r="C230" t="s">
+        <v>425</v>
+      </c>
+      <c r="D230" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4">
+      <c r="B231" t="s">
+        <v>426</v>
+      </c>
+      <c r="C231" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4">
+      <c r="B232" t="s">
+        <v>428</v>
+      </c>
+      <c r="C232" t="s">
+        <v>429</v>
+      </c>
+      <c r="D232" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4">
+      <c r="B233" t="s">
+        <v>430</v>
+      </c>
+      <c r="C233" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4">
+      <c r="B234" t="s">
+        <v>432</v>
+      </c>
+      <c r="C234" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="235" spans="2:4">
+      <c r="B235" t="s">
+        <v>434</v>
+      </c>
+      <c r="C235" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4">
+      <c r="B236" t="s">
+        <v>436</v>
+      </c>
+      <c r="C236" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4">
+      <c r="B237" t="s">
+        <v>438</v>
+      </c>
+      <c r="C237" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="238" spans="2:4">
+      <c r="B238" t="s">
+        <v>440</v>
+      </c>
+      <c r="C238" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="239" spans="2:4">
+      <c r="B239" t="s">
+        <v>442</v>
+      </c>
+      <c r="C239" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4">
+      <c r="B240" t="s">
+        <v>241</v>
+      </c>
+      <c r="C240" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="241" spans="2:4">
+      <c r="B241" t="s">
+        <v>154</v>
+      </c>
+      <c r="C241" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="242" spans="2:4">
+      <c r="B242" t="s">
+        <v>112</v>
+      </c>
+      <c r="C242" t="s">
+        <v>305</v>
+      </c>
+      <c r="D242" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D108" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D215" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
-        <filter val="AbpUsers"/>
+        <filter val="LimsTests"/>
       </filters>
     </filterColumn>
     <extLst/>
@@ -3772,8 +6048,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E39"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="22" customWidth="1"/>
@@ -3783,444 +6059,444 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>445</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>446</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>247</v>
+        <v>447</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>248</v>
+        <v>448</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="2" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="3" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="4" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="5" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="6" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:5">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="7" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:5">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="8" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:5">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="9" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>257</v>
+        <v>457</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>258</v>
+        <v>458</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:5">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>260</v>
+        <v>460</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:5">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="11" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>262</v>
+        <v>462</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="12" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" spans="1:5">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="13" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="1:5">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="14" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="1:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="15" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" spans="1:5">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="16" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" spans="1:5">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="17" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" spans="1:5">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="18" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" spans="1:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="19" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1" spans="1:5">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="20" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A20" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1" spans="1:5">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="21" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1" spans="1:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="22" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A22" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1" spans="1:5">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="23" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A23" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1" spans="1:5">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="24" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A24" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1" spans="1:5">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="25" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1" spans="1:5">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="26" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A26" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>275</v>
+        <v>475</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>276</v>
+        <v>476</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:5">
@@ -4228,16 +6504,16 @@
         <v>33</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>277</v>
+        <v>87</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>278</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:5">
@@ -4245,206 +6521,741 @@
         <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1" spans="1:5">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="29" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A29" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1" spans="1:5">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A30" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1" spans="1:5">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="31" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1" spans="1:5">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="32" ht="30" hidden="1" customHeight="1" spans="1:5">
       <c r="A32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>282</v>
+        <v>481</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="33" hidden="1" spans="1:5">
       <c r="A33" t="s">
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D33" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E33" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="34" hidden="1" spans="1:5">
       <c r="A34" t="s">
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="C34" t="s">
-        <v>285</v>
+        <v>484</v>
       </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E34" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="35" hidden="1" spans="1:5">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E35" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="36" hidden="1" spans="1:5">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E36" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="37" hidden="1" spans="1:5">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C37" t="s">
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E37" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="38" hidden="1" spans="1:5">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E38" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="39" hidden="1" spans="1:5">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="C39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E39" t="s">
-        <v>291</v>
+        <v>490</v>
+      </c>
+    </row>
+    <row r="40" hidden="1" spans="1:5">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" t="s">
+        <v>272</v>
+      </c>
+      <c r="C40" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="41" hidden="1" spans="1:5">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
+        <v>99</v>
+      </c>
+      <c r="E41" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="42" hidden="1" spans="1:5">
+      <c r="A42" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" t="s">
+        <v>300</v>
+      </c>
+      <c r="C42" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42" t="s">
+        <v>99</v>
+      </c>
+      <c r="E42" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="43" hidden="1" spans="1:5">
+      <c r="A43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>99</v>
+      </c>
+      <c r="E43" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="44" hidden="1" spans="1:5">
+      <c r="A44" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" t="s">
+        <v>99</v>
+      </c>
+      <c r="E44" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="45" hidden="1" spans="1:5">
+      <c r="A45" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="s">
+        <v>99</v>
+      </c>
+      <c r="E45" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="46" hidden="1" spans="1:5">
+      <c r="A46" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="47" hidden="1" spans="1:5">
+      <c r="A47" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" t="s">
+        <v>99</v>
+      </c>
+      <c r="E47" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="48" hidden="1" spans="1:5">
+      <c r="A48" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>99</v>
+      </c>
+      <c r="E48" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="49" hidden="1" spans="1:5">
+      <c r="A49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" t="s">
+        <v>300</v>
+      </c>
+      <c r="C49" t="s">
+        <v>81</v>
+      </c>
+      <c r="D49" t="s">
+        <v>99</v>
+      </c>
+      <c r="E49" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" spans="1:5">
+      <c r="A50" t="s">
+        <v>87</v>
+      </c>
+      <c r="B50" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D50" t="s">
+        <v>99</v>
+      </c>
+      <c r="E50" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="51" hidden="1" spans="1:5">
+      <c r="A51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B51" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" t="s">
+        <v>99</v>
+      </c>
+      <c r="E51" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="52" hidden="1" spans="1:5">
+      <c r="A52" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>99</v>
+      </c>
+      <c r="E52" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="53" hidden="1" spans="1:5">
+      <c r="A53" t="s">
+        <v>87</v>
+      </c>
+      <c r="B53" t="s">
+        <v>345</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="s">
+        <v>99</v>
+      </c>
+      <c r="E53" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="54" hidden="1" spans="1:5">
+      <c r="A54" t="s">
+        <v>87</v>
+      </c>
+      <c r="B54" t="s">
+        <v>347</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="s">
+        <v>99</v>
+      </c>
+      <c r="E54" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="55" hidden="1" spans="1:5">
+      <c r="A55" t="s">
+        <v>87</v>
+      </c>
+      <c r="B55" t="s">
+        <v>349</v>
+      </c>
+      <c r="C55" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" t="s">
+        <v>99</v>
+      </c>
+      <c r="E55" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" t="s">
+        <v>212</v>
+      </c>
+      <c r="C56" t="s">
+        <v>87</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E56" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>33</v>
+      </c>
+      <c r="B57" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" t="s">
+        <v>69</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E57" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" t="s">
+        <v>146</v>
+      </c>
+      <c r="C58" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E58" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" t="s">
+        <v>112</v>
+      </c>
+      <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E59" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" t="s">
+        <v>374</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E60" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>33</v>
+      </c>
+      <c r="B61" t="s">
+        <v>376</v>
+      </c>
+      <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E61" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>33</v>
+      </c>
+      <c r="B62" t="s">
+        <v>378</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E62" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B63" t="s">
+        <v>400</v>
+      </c>
+      <c r="C63" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E63" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" t="s">
+        <v>212</v>
+      </c>
+      <c r="C64" t="s">
+        <v>87</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E64" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>93</v>
+      </c>
+      <c r="B65" t="s">
+        <v>416</v>
+      </c>
+      <c r="C65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E65" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>93</v>
+      </c>
+      <c r="B66" t="s">
+        <v>418</v>
+      </c>
+      <c r="C66" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E66" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>93</v>
+      </c>
+      <c r="B67" t="s">
+        <v>420</v>
+      </c>
+      <c r="C67" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E67" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>93</v>
+      </c>
+      <c r="B68" t="s">
+        <v>424</v>
+      </c>
+      <c r="C68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E68" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>93</v>
+      </c>
+      <c r="B69" t="s">
+        <v>428</v>
+      </c>
+      <c r="C69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E69" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>93</v>
+      </c>
+      <c r="B70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E70" t="s">
+        <v>514</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E56" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="SampleSpecimens"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -4453,7 +7264,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="34.6666666666667" customWidth="1"/>
@@ -4466,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>292</v>
+        <v>515</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>293</v>
+        <v>516</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4477,21 +7288,21 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>294</v>
+        <v>517</v>
       </c>
       <c r="C2" t="s">
-        <v>295</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>296</v>
+        <v>519</v>
       </c>
       <c r="C3" t="s">
-        <v>295</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4499,10 +7310,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>297</v>
+        <v>520</v>
       </c>
       <c r="C4" t="s">
-        <v>295</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4510,10 +7321,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>298</v>
+        <v>521</v>
       </c>
       <c r="C5" t="s">
-        <v>295</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -4521,10 +7332,10 @@
         <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>299</v>
+        <v>522</v>
       </c>
       <c r="C6" t="s">
-        <v>295</v>
+        <v>518</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4532,32 +7343,32 @@
         <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>299</v>
+        <v>522</v>
       </c>
       <c r="C7" t="s">
-        <v>295</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>300</v>
+        <v>523</v>
       </c>
       <c r="C8" t="s">
-        <v>295</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9" ht="28.8" spans="1:3">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>301</v>
+        <v>524</v>
       </c>
       <c r="C9" t="s">
-        <v>295</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -4565,10 +7376,10 @@
         <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>302</v>
+        <v>525</v>
       </c>
       <c r="C10" t="s">
-        <v>295</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4576,112 +7387,181 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>303</v>
+        <v>526</v>
       </c>
       <c r="C11" t="s">
-        <v>295</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>304</v>
+        <v>527</v>
       </c>
       <c r="C12" t="s">
-        <v>295</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>305</v>
+        <v>528</v>
       </c>
       <c r="C13" t="s">
-        <v>295</v>
+        <v>518</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>306</v>
+        <v>529</v>
       </c>
       <c r="C14" t="s">
-        <v>295</v>
+        <v>530</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>307</v>
+        <v>531</v>
       </c>
       <c r="C15" t="s">
-        <v>308</v>
+        <v>530</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>532</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>309</v>
+        <v>533</v>
       </c>
       <c r="C16" t="s">
-        <v>308</v>
+        <v>534</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>310</v>
+        <v>535</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>311</v>
+        <v>536</v>
       </c>
       <c r="C17" t="s">
-        <v>312</v>
+        <v>534</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>313</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>314</v>
+        <v>537</v>
       </c>
       <c r="C18" t="s">
-        <v>312</v>
+        <v>530</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>315</v>
+        <v>538</v>
       </c>
       <c r="C19" t="s">
-        <v>308</v>
+        <v>530</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>316</v>
+        <v>40</v>
+      </c>
+      <c r="B20" t="s">
+        <v>539</v>
       </c>
       <c r="C20" t="s">
-        <v>308</v>
+        <v>518</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" t="s">
+        <v>540</v>
+      </c>
+      <c r="C21" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" t="s">
+        <v>541</v>
+      </c>
+      <c r="C22" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
+        <v>542</v>
+      </c>
+      <c r="C23" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" t="s">
+        <v>543</v>
+      </c>
+      <c r="C24" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>544</v>
+      </c>
+      <c r="C25" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" t="s">
+        <v>545</v>
+      </c>
+      <c r="C26" t="s">
+        <v>518</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:C20" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/python/table_metadata.xlsx
+++ b/python/table_metadata.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9840" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="9840"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="577">
   <si>
     <t>TableName</t>
   </si>
@@ -338,6 +338,27 @@
     <t>IsDeleted=false for active. SampleSpecimenId links to SampleSpecimens. SampleId links to Samples. LabTechnician, TestBrokenBy, TestSignedBy, TestReviewedBy, TestApprovedBy all link to AbpUsers.Id. TestFinalized=true for completed tests. IsBilled=true for billed tests.</t>
   </si>
   <si>
+    <t>Lookups</t>
+  </si>
+  <si>
+    <t>Master lookup groups. Each group has multiple detail values in LookupDetails. Examples: Hierarchy Type, TimeZone, Status codes.</t>
+  </si>
+  <si>
+    <t>GroupName</t>
+  </si>
+  <si>
+    <t>Use GroupName for display. IsDeleted=false for active. LookupDetails.LookupId links here. Use this table to find what group a lookup belongs to.</t>
+  </si>
+  <si>
+    <t>LookupDetails</t>
+  </si>
+  <si>
+    <t>Lookup detail values for dropdowns and code fields. Many integer columns in other tables (Status, SampleType, SpecimenSize etc) reference LookupDetails.Id for their readable names.</t>
+  </si>
+  <si>
+    <t>Use Name for display — this is the human-readable label. Value is the code. LookupId links to parent Lookups group. IsDeleted=false for active. To get readable name for any integer code field: JOIN LookupDetails ON integer_column = LookupDetails.Id.</t>
+  </si>
+  <si>
     <t>ColumnName</t>
   </si>
   <si>
@@ -1382,6 +1403,69 @@
     <t>Soft delete. Always write "LimsTests"."IsDeleted" = false — never bare "IsDeleted".</t>
   </si>
   <si>
+    <t>Primary key. Referenced by LookupDetails.LookupId.</t>
+  </si>
+  <si>
+    <t>Lookup group name e.g. Hierarchy Type, TimeZone, Status. ALWAYS USE FOR DISPLAY.</t>
+  </si>
+  <si>
+    <t>Description of the lookup group.</t>
+  </si>
+  <si>
+    <t>Soft delete. Always write "Lookups"."IsDeleted" = false.</t>
+  </si>
+  <si>
+    <t>Primary key. Referenced by many tables as integer code columns e.g. Status, SampleType, SpecimenSize.</t>
+  </si>
+  <si>
+    <t>Human-readable label for this lookup value e.g. Organization, Region. ALWAYS USE FOR DISPLAY.</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Code value for this lookup detail.</t>
+  </si>
+  <si>
+    <t>Description of this lookup value.</t>
+  </si>
+  <si>
+    <t>LookupId</t>
+  </si>
+  <si>
+    <t>Parent lookup group — INTEGER FK.</t>
+  </si>
+  <si>
+    <t>-&gt; Lookups.Id</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Category of this lookup detail.</t>
+  </si>
+  <si>
+    <t>DetailType</t>
+  </si>
+  <si>
+    <t>Type of this lookup detail.</t>
+  </si>
+  <si>
+    <t>OrderNumber</t>
+  </si>
+  <si>
+    <t>Display order number.</t>
+  </si>
+  <si>
+    <t>ColorCode</t>
+  </si>
+  <si>
+    <t>Color code for UI display.</t>
+  </si>
+  <si>
+    <t>Soft delete. Always write "LookupDetails"."IsDeleted" = false.</t>
+  </si>
+  <si>
     <t>FromTable</t>
   </si>
   <si>
@@ -1592,6 +1676,9 @@
     <t>User who created this record</t>
   </si>
   <si>
+    <t>Each detail belongs to one lookup group</t>
+  </si>
+  <si>
     <t>TriggerWords</t>
   </si>
   <si>
@@ -1683,6 +1770,12 @@
   </si>
   <si>
     <t>limstest,limstests,labtest,labtests,test,tests,lims,lab,labs,laboratory,result,results,labresult</t>
+  </si>
+  <si>
+    <t>lookup,lookups,lookupgroup</t>
+  </si>
+  <si>
+    <t>lookupdetail,lookupdetails,lookup,dropdown,code</t>
   </si>
 </sst>
 </file>
@@ -2708,7 +2801,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -3104,6 +3197,34 @@
       </c>
       <c r="D28" s="2" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="29" ht="28.8" spans="1:4">
+      <c r="A29" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" ht="43.2" spans="1:4">
+      <c r="A30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -3123,7 +3244,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D242"/>
+  <dimension ref="A1:D258"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -3137,13 +3258,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3151,10 +3272,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>22</v>
@@ -3168,7 +3289,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -3179,10 +3300,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
@@ -3193,13 +3314,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3207,10 +3328,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D6" s="4"/>
     </row>
@@ -3219,13 +3340,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3233,13 +3354,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3247,13 +3368,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3261,13 +3382,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3275,13 +3396,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3289,13 +3410,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3303,10 +3424,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>22</v>
@@ -3317,10 +3438,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>22</v>
@@ -3331,10 +3452,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>22</v>
@@ -3345,10 +3466,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>22</v>
@@ -3359,10 +3480,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>22</v>
@@ -3373,10 +3494,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>22</v>
@@ -3387,10 +3508,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>22</v>
@@ -3401,10 +3522,10 @@
         <v>69</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>22</v>
@@ -3418,7 +3539,7 @@
         <v>71</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>22</v>
@@ -3429,10 +3550,10 @@
         <v>69</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>22</v>
@@ -3443,13 +3564,13 @@
         <v>69</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3457,13 +3578,13 @@
         <v>69</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3471,13 +3592,13 @@
         <v>69</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3485,13 +3606,13 @@
         <v>69</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3499,13 +3620,13 @@
         <v>69</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3513,10 +3634,10 @@
         <v>69</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>22</v>
@@ -3527,10 +3648,10 @@
         <v>69</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>22</v>
@@ -3541,10 +3662,10 @@
         <v>8</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>22</v>
@@ -3558,7 +3679,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>22</v>
@@ -3572,7 +3693,7 @@
         <v>18</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>22</v>
@@ -3583,10 +3704,10 @@
         <v>8</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>22</v>
@@ -3597,10 +3718,10 @@
         <v>8</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>22</v>
@@ -3611,10 +3732,10 @@
         <v>8</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>22</v>
@@ -3625,10 +3746,10 @@
         <v>8</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>22</v>
@@ -3639,10 +3760,10 @@
         <v>8</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>22</v>
@@ -3653,13 +3774,13 @@
         <v>8</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3667,10 +3788,10 @@
         <v>8</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>22</v>
@@ -3681,10 +3802,10 @@
         <v>12</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>22</v>
@@ -3698,7 +3819,7 @@
         <v>14</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>22</v>
@@ -3712,7 +3833,7 @@
         <v>46</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>22</v>
@@ -3723,10 +3844,10 @@
         <v>12</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>22</v>
@@ -3737,10 +3858,10 @@
         <v>12</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
@@ -3751,10 +3872,10 @@
         <v>12</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>22</v>
@@ -3765,10 +3886,10 @@
         <v>12</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>22</v>
@@ -3779,10 +3900,10 @@
         <v>12</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>22</v>
@@ -3793,10 +3914,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>22</v>
@@ -3810,7 +3931,7 @@
         <v>18</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>22</v>
@@ -3824,7 +3945,7 @@
         <v>46</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>22</v>
@@ -3835,10 +3956,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>22</v>
@@ -3849,10 +3970,10 @@
         <v>20</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>22</v>
@@ -3863,13 +3984,13 @@
         <v>20</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3877,13 +3998,13 @@
         <v>20</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="55" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3891,10 +4012,10 @@
         <v>24</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>22</v>
@@ -3905,13 +4026,13 @@
         <v>24</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="57" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3919,13 +4040,13 @@
         <v>24</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="58" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3933,13 +4054,13 @@
         <v>24</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="59" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3947,13 +4068,13 @@
         <v>24</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -3961,10 +4082,10 @@
         <v>24</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>22</v>
@@ -3975,10 +4096,10 @@
         <v>24</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>22</v>
@@ -3989,10 +4110,10 @@
         <v>24</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>22</v>
@@ -4003,10 +4124,10 @@
         <v>33</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>22</v>
@@ -4017,13 +4138,13 @@
         <v>33</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="65" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -4031,13 +4152,13 @@
         <v>33</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="66" ht="30" hidden="1" customHeight="1" spans="1:4">
@@ -4048,7 +4169,7 @@
         <v>35</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>22</v>
@@ -4059,10 +4180,10 @@
         <v>33</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>22</v>
@@ -4073,10 +4194,10 @@
         <v>33</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>22</v>
@@ -4087,13 +4208,13 @@
         <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="70" ht="28.8" hidden="1" spans="1:4">
@@ -4104,7 +4225,7 @@
         <v>18</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="71" hidden="1" spans="1:4">
@@ -4112,10 +4233,10 @@
         <v>60</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="72" hidden="1" spans="1:4">
@@ -4123,13 +4244,13 @@
         <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D72" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="73" hidden="1" spans="1:4">
@@ -4137,10 +4258,10 @@
         <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="74" hidden="1" spans="1:4">
@@ -4151,7 +4272,7 @@
         <v>53</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="75" hidden="1" spans="1:4">
@@ -4159,10 +4280,10 @@
         <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" hidden="1" spans="1:4">
@@ -4170,10 +4291,10 @@
         <v>60</v>
       </c>
       <c r="B76" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" hidden="1" spans="1:4">
@@ -4184,7 +4305,7 @@
         <v>18</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="78" hidden="1" spans="1:4">
@@ -4192,13 +4313,13 @@
         <v>60</v>
       </c>
       <c r="B78" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D78" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="79" hidden="1" spans="1:4">
@@ -4206,10 +4327,10 @@
         <v>60</v>
       </c>
       <c r="B79" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="80" hidden="1" spans="1:4">
@@ -4217,10 +4338,10 @@
         <v>60</v>
       </c>
       <c r="B80" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" hidden="1" spans="1:4">
@@ -4228,13 +4349,13 @@
         <v>63</v>
       </c>
       <c r="B81" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="D81" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="82" hidden="1" spans="1:4">
@@ -4242,13 +4363,13 @@
         <v>63</v>
       </c>
       <c r="B82" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D82" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="83" hidden="1" spans="1:4">
@@ -4256,10 +4377,10 @@
         <v>63</v>
       </c>
       <c r="B83" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="84" hidden="1" spans="1:4">
@@ -4267,10 +4388,10 @@
         <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="85" hidden="1" spans="1:4">
@@ -4281,7 +4402,7 @@
         <v>46</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="86" hidden="1" spans="1:4">
@@ -4289,10 +4410,10 @@
         <v>66</v>
       </c>
       <c r="B86" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="87" hidden="1" spans="1:4">
@@ -4300,13 +4421,13 @@
         <v>66</v>
       </c>
       <c r="B87" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D87" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="88" hidden="1" spans="1:4">
@@ -4314,13 +4435,13 @@
         <v>66</v>
       </c>
       <c r="B88" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D88" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="89" ht="72" hidden="1" spans="1:4">
@@ -4328,10 +4449,10 @@
         <v>4</v>
       </c>
       <c r="B89" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="90" hidden="1" spans="1:4">
@@ -4339,10 +4460,10 @@
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="91" hidden="1" spans="1:4">
@@ -4350,10 +4471,10 @@
         <v>69</v>
       </c>
       <c r="B91" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="92" hidden="1" spans="1:4">
@@ -4361,10 +4482,10 @@
         <v>69</v>
       </c>
       <c r="B92" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="93" hidden="1" spans="1:4">
@@ -4372,10 +4493,10 @@
         <v>69</v>
       </c>
       <c r="B93" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
     </row>
     <row r="94" hidden="1" spans="1:4">
@@ -4383,10 +4504,10 @@
         <v>69</v>
       </c>
       <c r="B94" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="95" hidden="1" spans="1:4">
@@ -4394,10 +4515,10 @@
         <v>69</v>
       </c>
       <c r="B95" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="96" hidden="1" spans="1:4">
@@ -4405,10 +4526,10 @@
         <v>69</v>
       </c>
       <c r="B96" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="97" hidden="1" spans="1:4">
@@ -4416,13 +4537,13 @@
         <v>69</v>
       </c>
       <c r="B97" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="98" ht="28.8" hidden="1" spans="1:4">
@@ -4430,13 +4551,13 @@
         <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="D98" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="99" ht="28.8" hidden="1" spans="1:4">
@@ -4444,13 +4565,13 @@
         <v>69</v>
       </c>
       <c r="B99" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D99" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="100" hidden="1" spans="1:4">
@@ -4458,10 +4579,10 @@
         <v>69</v>
       </c>
       <c r="B100" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="101" hidden="1" spans="1:4">
@@ -4469,10 +4590,10 @@
         <v>4</v>
       </c>
       <c r="B101" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="102" ht="28.8" hidden="1" spans="1:4">
@@ -4480,10 +4601,10 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="103" hidden="1" spans="1:4">
@@ -4491,10 +4612,10 @@
         <v>60</v>
       </c>
       <c r="B103" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" hidden="1" spans="1:4">
@@ -4502,10 +4623,10 @@
         <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" hidden="1" spans="1:4">
@@ -4513,10 +4634,10 @@
         <v>16</v>
       </c>
       <c r="B105" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="106" hidden="1" spans="1:4">
@@ -4524,10 +4645,10 @@
         <v>40</v>
       </c>
       <c r="B106" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="107" hidden="1" spans="1:4">
@@ -4535,10 +4656,10 @@
         <v>51</v>
       </c>
       <c r="B107" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="108" hidden="1" spans="1:4">
@@ -4546,10 +4667,10 @@
         <v>4</v>
       </c>
       <c r="B108" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C108" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
     </row>
     <row r="109" hidden="1" spans="1:4">
@@ -4557,10 +4678,10 @@
         <v>40</v>
       </c>
       <c r="B109" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C109" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="110" hidden="1" spans="1:4">
@@ -4571,7 +4692,7 @@
         <v>42</v>
       </c>
       <c r="C110" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="111" hidden="1" spans="1:4">
@@ -4579,13 +4700,13 @@
         <v>40</v>
       </c>
       <c r="B111" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C111" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D111" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="112" hidden="1" spans="1:4">
@@ -4593,13 +4714,13 @@
         <v>40</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C112" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D112" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="113" hidden="1" spans="1:3">
@@ -4607,10 +4728,10 @@
         <v>40</v>
       </c>
       <c r="B113" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C113" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="114" hidden="1" spans="1:3">
@@ -4618,10 +4739,10 @@
         <v>40</v>
       </c>
       <c r="B114" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C114" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="115" hidden="1" spans="1:3">
@@ -4629,10 +4750,10 @@
         <v>40</v>
       </c>
       <c r="B115" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C115" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="116" hidden="1" spans="1:3">
@@ -4640,10 +4761,10 @@
         <v>40</v>
       </c>
       <c r="B116" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C116" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="117" hidden="1" spans="1:3">
@@ -4651,10 +4772,10 @@
         <v>40</v>
       </c>
       <c r="B117" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C117" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="118" hidden="1" spans="1:3">
@@ -4662,10 +4783,10 @@
         <v>40</v>
       </c>
       <c r="B118" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C118" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
     <row r="119" hidden="1" spans="1:3">
@@ -4673,10 +4794,10 @@
         <v>40</v>
       </c>
       <c r="B119" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C119" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="120" hidden="1" spans="1:3">
@@ -4684,10 +4805,10 @@
         <v>40</v>
       </c>
       <c r="B120" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C120" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="121" hidden="1" spans="1:3">
@@ -4695,10 +4816,10 @@
         <v>40</v>
       </c>
       <c r="B121" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C121" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
     </row>
     <row r="122" hidden="1" spans="1:3">
@@ -4706,10 +4827,10 @@
         <v>40</v>
       </c>
       <c r="B122" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C122" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="123" hidden="1" spans="1:3">
@@ -4717,10 +4838,10 @@
         <v>40</v>
       </c>
       <c r="B123" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C123" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="124" hidden="1" spans="1:3">
@@ -4728,10 +4849,10 @@
         <v>40</v>
       </c>
       <c r="B124" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C124" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="125" hidden="1" spans="1:3">
@@ -4739,10 +4860,10 @@
         <v>40</v>
       </c>
       <c r="B125" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C125" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
     </row>
     <row r="126" hidden="1" spans="1:3">
@@ -4750,10 +4871,10 @@
         <v>40</v>
       </c>
       <c r="B126" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C126" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="127" hidden="1" spans="1:3">
@@ -4761,10 +4882,10 @@
         <v>73</v>
       </c>
       <c r="B127" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C127" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="128" hidden="1" spans="1:3">
@@ -4775,7 +4896,7 @@
         <v>75</v>
       </c>
       <c r="C128" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="129" hidden="1" spans="1:4">
@@ -4783,10 +4904,10 @@
         <v>73</v>
       </c>
       <c r="B129" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C129" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="130" hidden="1" spans="1:4">
@@ -4794,13 +4915,13 @@
         <v>73</v>
       </c>
       <c r="B130" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C130" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="D130" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="131" hidden="1" spans="1:4">
@@ -4808,10 +4929,10 @@
         <v>73</v>
       </c>
       <c r="B131" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C131" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="132" hidden="1" spans="1:4">
@@ -4819,10 +4940,10 @@
         <v>73</v>
       </c>
       <c r="B132" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C132" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="133" hidden="1" spans="1:4">
@@ -4830,13 +4951,13 @@
         <v>73</v>
       </c>
       <c r="B133" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C133" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D133" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="134" hidden="1" spans="1:4">
@@ -4844,10 +4965,10 @@
         <v>73</v>
       </c>
       <c r="B134" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C134" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="135" hidden="1" spans="1:4">
@@ -4855,10 +4976,10 @@
         <v>73</v>
       </c>
       <c r="B135" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C135" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="136" hidden="1" spans="1:4">
@@ -4866,10 +4987,10 @@
         <v>73</v>
       </c>
       <c r="B136" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C136" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="137" hidden="1" spans="1:4">
@@ -4877,10 +4998,10 @@
         <v>73</v>
       </c>
       <c r="B137" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C137" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="138" hidden="1" spans="1:4">
@@ -4888,10 +5009,10 @@
         <v>73</v>
       </c>
       <c r="B138" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C138" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="139" hidden="1" spans="1:4">
@@ -4899,10 +5020,10 @@
         <v>73</v>
       </c>
       <c r="B139" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C139" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="140" hidden="1" spans="1:4">
@@ -4910,10 +5031,10 @@
         <v>73</v>
       </c>
       <c r="B140" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="C140" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="141" hidden="1" spans="1:4">
@@ -4921,10 +5042,10 @@
         <v>73</v>
       </c>
       <c r="B141" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C141" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="142" hidden="1" spans="1:4">
@@ -4932,10 +5053,10 @@
         <v>77</v>
       </c>
       <c r="B142" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C142" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="143" hidden="1" spans="1:4">
@@ -4946,7 +5067,7 @@
         <v>79</v>
       </c>
       <c r="C143" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="144" hidden="1" spans="1:4">
@@ -4954,10 +5075,10 @@
         <v>77</v>
       </c>
       <c r="B144" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C144" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="145" hidden="1" spans="1:4">
@@ -4965,10 +5086,10 @@
         <v>77</v>
       </c>
       <c r="B145" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C145" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="146" hidden="1" spans="1:4">
@@ -4976,10 +5097,10 @@
         <v>77</v>
       </c>
       <c r="B146" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C146" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
     </row>
     <row r="147" hidden="1" spans="1:4">
@@ -4987,10 +5108,10 @@
         <v>77</v>
       </c>
       <c r="B147" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C147" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="148" hidden="1" spans="1:4">
@@ -4998,13 +5119,13 @@
         <v>77</v>
       </c>
       <c r="B148" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C148" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="149" hidden="1" spans="1:4">
@@ -5012,13 +5133,13 @@
         <v>77</v>
       </c>
       <c r="B149" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C149" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D149" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="150" hidden="1" spans="1:4">
@@ -5026,10 +5147,10 @@
         <v>77</v>
       </c>
       <c r="B150" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C150" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="151" hidden="1" spans="1:4">
@@ -5037,10 +5158,10 @@
         <v>77</v>
       </c>
       <c r="B151" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C151" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
     </row>
     <row r="152" hidden="1" spans="1:4">
@@ -5048,10 +5169,10 @@
         <v>77</v>
       </c>
       <c r="B152" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C152" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="153" hidden="1" spans="1:4">
@@ -5059,10 +5180,10 @@
         <v>81</v>
       </c>
       <c r="B153" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C153" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="154" hidden="1" spans="1:4">
@@ -5070,10 +5191,10 @@
         <v>81</v>
       </c>
       <c r="B154" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C154" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="155" hidden="1" spans="1:4">
@@ -5084,7 +5205,7 @@
         <v>83</v>
       </c>
       <c r="C155" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="156" hidden="1" spans="1:4">
@@ -5092,10 +5213,10 @@
         <v>81</v>
       </c>
       <c r="B156" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C156" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
     </row>
     <row r="157" hidden="1" spans="1:4">
@@ -5103,10 +5224,10 @@
         <v>81</v>
       </c>
       <c r="B157" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C157" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
     <row r="158" hidden="1" spans="1:4">
@@ -5114,10 +5235,10 @@
         <v>81</v>
       </c>
       <c r="B158" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C158" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="159" hidden="1" spans="1:4">
@@ -5125,10 +5246,10 @@
         <v>57</v>
       </c>
       <c r="B159" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C159" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="160" hidden="1" spans="1:4">
@@ -5139,7 +5260,7 @@
         <v>46</v>
       </c>
       <c r="C160" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="161" hidden="1" spans="1:4">
@@ -5147,10 +5268,10 @@
         <v>57</v>
       </c>
       <c r="B161" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C161" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="162" hidden="1" spans="1:4">
@@ -5158,13 +5279,13 @@
         <v>57</v>
       </c>
       <c r="B162" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C162" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="D162" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="163" hidden="1" spans="1:4">
@@ -5172,13 +5293,13 @@
         <v>57</v>
       </c>
       <c r="B163" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C163" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D163" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="164" hidden="1" spans="1:4">
@@ -5186,10 +5307,10 @@
         <v>57</v>
       </c>
       <c r="B164" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C164" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="165" hidden="1" spans="1:4">
@@ -5197,10 +5318,10 @@
         <v>57</v>
       </c>
       <c r="B165" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C165" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
     </row>
     <row r="166" hidden="1" spans="1:4">
@@ -5208,10 +5329,10 @@
         <v>57</v>
       </c>
       <c r="B166" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C166" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="167" hidden="1" spans="1:4">
@@ -5219,10 +5340,10 @@
         <v>57</v>
       </c>
       <c r="B167" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C167" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="168" hidden="1" spans="1:4">
@@ -5230,10 +5351,10 @@
         <v>87</v>
       </c>
       <c r="B168" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C168" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="169" hidden="1" spans="1:4">
@@ -5244,7 +5365,7 @@
         <v>89</v>
       </c>
       <c r="C169" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="170" hidden="1" spans="1:4">
@@ -5252,10 +5373,10 @@
         <v>87</v>
       </c>
       <c r="B170" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C170" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="171" hidden="1" spans="1:4">
@@ -5263,10 +5384,10 @@
         <v>87</v>
       </c>
       <c r="B171" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C171" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
     </row>
     <row r="172" hidden="1" spans="1:4">
@@ -5274,10 +5395,10 @@
         <v>87</v>
       </c>
       <c r="B172" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C172" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="173" hidden="1" spans="1:4">
@@ -5285,10 +5406,10 @@
         <v>87</v>
       </c>
       <c r="B173" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C173" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="174" hidden="1" spans="1:4">
@@ -5296,10 +5417,10 @@
         <v>87</v>
       </c>
       <c r="B174" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C174" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="175" hidden="1" spans="1:4">
@@ -5307,13 +5428,13 @@
         <v>87</v>
       </c>
       <c r="B175" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C175" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="D175" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="176" hidden="1" spans="1:4">
@@ -5321,13 +5442,13 @@
         <v>87</v>
       </c>
       <c r="B176" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C176" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D176" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="177" hidden="1" spans="1:4">
@@ -5335,13 +5456,13 @@
         <v>87</v>
       </c>
       <c r="B177" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C177" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D177" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="178" hidden="1" spans="1:4">
@@ -5349,13 +5470,13 @@
         <v>87</v>
       </c>
       <c r="B178" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C178" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="D178" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="179" hidden="1" spans="1:4">
@@ -5363,13 +5484,13 @@
         <v>87</v>
       </c>
       <c r="B179" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C179" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D179" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="180" hidden="1" spans="1:4">
@@ -5377,13 +5498,13 @@
         <v>87</v>
       </c>
       <c r="B180" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C180" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D180" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="181" hidden="1" spans="1:4">
@@ -5391,10 +5512,10 @@
         <v>87</v>
       </c>
       <c r="B181" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C181" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="182" hidden="1" spans="1:4">
@@ -5402,10 +5523,10 @@
         <v>87</v>
       </c>
       <c r="B182" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C182" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="183" hidden="1" spans="1:4">
@@ -5413,10 +5534,10 @@
         <v>87</v>
       </c>
       <c r="B183" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C183" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="184" hidden="1" spans="1:4">
@@ -5424,10 +5545,10 @@
         <v>87</v>
       </c>
       <c r="B184" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C184" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="185" hidden="1" spans="1:4">
@@ -5435,10 +5556,10 @@
         <v>87</v>
       </c>
       <c r="B185" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C185" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="186" hidden="1" spans="1:4">
@@ -5446,10 +5567,10 @@
         <v>87</v>
       </c>
       <c r="B186" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C186" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="187" hidden="1" spans="1:4">
@@ -5457,10 +5578,10 @@
         <v>87</v>
       </c>
       <c r="B187" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C187" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="188" hidden="1" spans="1:4">
@@ -5468,10 +5589,10 @@
         <v>87</v>
       </c>
       <c r="B188" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C188" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="189" hidden="1" spans="1:4">
@@ -5479,10 +5600,10 @@
         <v>33</v>
       </c>
       <c r="B189" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C189" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="190" hidden="1" spans="1:4">
@@ -5493,7 +5614,7 @@
         <v>35</v>
       </c>
       <c r="C190" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="191" hidden="1" spans="1:4">
@@ -5501,13 +5622,13 @@
         <v>33</v>
       </c>
       <c r="B191" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C191" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="D191" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="192" hidden="1" spans="1:4">
@@ -5518,7 +5639,7 @@
         <v>89</v>
       </c>
       <c r="C192" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="193" hidden="1" spans="1:4">
@@ -5526,10 +5647,10 @@
         <v>33</v>
       </c>
       <c r="B193" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C193" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="194" hidden="1" spans="1:4">
@@ -5537,10 +5658,10 @@
         <v>33</v>
       </c>
       <c r="B194" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C194" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="195" hidden="1" spans="1:4">
@@ -5548,10 +5669,10 @@
         <v>33</v>
       </c>
       <c r="B195" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="C195" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="196" hidden="1" spans="1:4">
@@ -5559,10 +5680,10 @@
         <v>33</v>
       </c>
       <c r="B196" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C196" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
     </row>
     <row r="197" hidden="1" spans="1:4">
@@ -5570,10 +5691,10 @@
         <v>33</v>
       </c>
       <c r="B197" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C197" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="198" hidden="1" spans="1:4">
@@ -5581,13 +5702,13 @@
         <v>33</v>
       </c>
       <c r="B198" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C198" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="D198" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="199" hidden="1" spans="1:4">
@@ -5595,13 +5716,13 @@
         <v>33</v>
       </c>
       <c r="B199" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="C199" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="D199" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="200" hidden="1" spans="1:4">
@@ -5609,13 +5730,13 @@
         <v>33</v>
       </c>
       <c r="B200" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C200" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="D200" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="201" hidden="1" spans="1:4">
@@ -5623,10 +5744,10 @@
         <v>33</v>
       </c>
       <c r="B201" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C201" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="202" hidden="1" spans="1:4">
@@ -5634,10 +5755,10 @@
         <v>33</v>
       </c>
       <c r="B202" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C202" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="203" hidden="1" spans="1:4">
@@ -5645,13 +5766,13 @@
         <v>33</v>
       </c>
       <c r="B203" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C203" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D203" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="204" hidden="1" spans="1:4">
@@ -5659,13 +5780,13 @@
         <v>33</v>
       </c>
       <c r="B204" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C204" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D204" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="205" hidden="1" spans="1:4">
@@ -5673,10 +5794,10 @@
         <v>33</v>
       </c>
       <c r="B205" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C205" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="206" hidden="1" spans="1:4">
@@ -5684,10 +5805,10 @@
         <v>33</v>
       </c>
       <c r="B206" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C206" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="207" hidden="1" spans="1:4">
@@ -5695,10 +5816,10 @@
         <v>33</v>
       </c>
       <c r="B207" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C207" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="208" hidden="1" spans="1:4">
@@ -5706,10 +5827,10 @@
         <v>33</v>
       </c>
       <c r="B208" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C208" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="209" hidden="1" spans="1:4">
@@ -5717,10 +5838,10 @@
         <v>33</v>
       </c>
       <c r="B209" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C209" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="210" hidden="1" spans="1:4">
@@ -5728,10 +5849,10 @@
         <v>33</v>
       </c>
       <c r="B210" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="C210" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="211" hidden="1" spans="1:4">
@@ -5739,10 +5860,10 @@
         <v>33</v>
       </c>
       <c r="B211" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C211" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="212" hidden="1" spans="1:4">
@@ -5750,10 +5871,10 @@
         <v>33</v>
       </c>
       <c r="B212" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C212" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="213" hidden="1" spans="1:4">
@@ -5761,10 +5882,10 @@
         <v>33</v>
       </c>
       <c r="B213" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C213" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="214" hidden="1" spans="1:4">
@@ -5772,13 +5893,13 @@
         <v>33</v>
       </c>
       <c r="B214" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C214" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D214" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5786,250 +5907,510 @@
         <v>93</v>
       </c>
       <c r="B215" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C215" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="216" spans="1:4">
+      <c r="A216" t="s">
+        <v>93</v>
+      </c>
       <c r="B216" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C216" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="D216" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="217" spans="1:4">
+      <c r="A217" t="s">
+        <v>93</v>
+      </c>
       <c r="B217" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C217" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D217" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="218" spans="1:4">
+      <c r="A218" t="s">
+        <v>93</v>
+      </c>
       <c r="B218" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C218" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="219" spans="1:4">
+      <c r="A219" t="s">
+        <v>93</v>
+      </c>
       <c r="B219" t="s">
         <v>95</v>
       </c>
       <c r="C219" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="220" spans="1:4">
+      <c r="A220" t="s">
+        <v>93</v>
+      </c>
       <c r="B220" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C220" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="221" spans="1:4">
+      <c r="A221" t="s">
+        <v>93</v>
+      </c>
       <c r="B221" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C221" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
     <row r="222" spans="1:4">
+      <c r="A222" t="s">
+        <v>93</v>
+      </c>
       <c r="B222" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C222" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="223" spans="1:4">
+      <c r="A223" t="s">
+        <v>93</v>
+      </c>
       <c r="B223" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C223" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="224" spans="1:4">
+      <c r="A224" t="s">
+        <v>93</v>
+      </c>
       <c r="B224" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C224" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="225" spans="2:4">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" t="s">
+        <v>93</v>
+      </c>
       <c r="B225" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C225" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="226" spans="2:4">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" t="s">
+        <v>93</v>
+      </c>
       <c r="B226" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C226" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="D226" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="227" spans="2:4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" t="s">
+        <v>93</v>
+      </c>
       <c r="B227" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C227" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="D227" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="228" spans="2:4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" t="s">
+        <v>93</v>
+      </c>
       <c r="B228" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C228" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="D228" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="229" spans="2:4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" t="s">
+        <v>93</v>
+      </c>
       <c r="B229" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C229" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="230" spans="2:4">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" t="s">
+        <v>93</v>
+      </c>
       <c r="B230" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C230" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="D230" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="231" spans="2:4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" t="s">
+        <v>93</v>
+      </c>
       <c r="B231" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C231" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="232" spans="2:4">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" t="s">
+        <v>93</v>
+      </c>
       <c r="B232" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C232" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D232" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="233" spans="2:4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" t="s">
+        <v>93</v>
+      </c>
       <c r="B233" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C233" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="234" spans="2:4">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" t="s">
+        <v>93</v>
+      </c>
       <c r="B234" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C234" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="235" spans="2:4">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" t="s">
+        <v>93</v>
+      </c>
       <c r="B235" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C235" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="236" spans="2:4">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" t="s">
+        <v>93</v>
+      </c>
       <c r="B236" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="C236" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="237" spans="2:4">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" t="s">
+        <v>93</v>
+      </c>
       <c r="B237" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="C237" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="238" spans="2:4">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" t="s">
+        <v>93</v>
+      </c>
       <c r="B238" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C238" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="239" spans="2:4">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
+        <v>93</v>
+      </c>
       <c r="B239" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="C239" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="240" spans="2:4">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
+        <v>93</v>
+      </c>
       <c r="B240" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C240" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="241" spans="2:4">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
+        <v>93</v>
+      </c>
       <c r="B241" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C241" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="242" spans="2:4">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
+        <v>93</v>
+      </c>
       <c r="B242" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C242" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="D242" t="s">
-        <v>114</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" t="s">
+        <v>97</v>
+      </c>
+      <c r="B243" t="s">
+        <v>106</v>
+      </c>
+      <c r="C243" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" t="s">
+        <v>97</v>
+      </c>
+      <c r="B244" t="s">
+        <v>99</v>
+      </c>
+      <c r="C244" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" t="s">
+        <v>97</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1</v>
+      </c>
+      <c r="C245" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" t="s">
+        <v>97</v>
+      </c>
+      <c r="B246" t="s">
+        <v>109</v>
+      </c>
+      <c r="C246" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" t="s">
+        <v>97</v>
+      </c>
+      <c r="B247" t="s">
+        <v>161</v>
+      </c>
+      <c r="C247" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" t="s">
+        <v>101</v>
+      </c>
+      <c r="B248" t="s">
+        <v>106</v>
+      </c>
+      <c r="C248" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
+      <c r="A249" t="s">
+        <v>101</v>
+      </c>
+      <c r="B249" t="s">
+        <v>46</v>
+      </c>
+      <c r="C249" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4">
+      <c r="A250" t="s">
+        <v>101</v>
+      </c>
+      <c r="B250" t="s">
+        <v>458</v>
+      </c>
+      <c r="C250" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
+      <c r="A251" t="s">
+        <v>101</v>
+      </c>
+      <c r="B251" t="s">
+        <v>1</v>
+      </c>
+      <c r="C251" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
+      <c r="A252" t="s">
+        <v>101</v>
+      </c>
+      <c r="B252" t="s">
+        <v>461</v>
+      </c>
+      <c r="C252" t="s">
+        <v>462</v>
+      </c>
+      <c r="D252" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4">
+      <c r="A253" t="s">
+        <v>101</v>
+      </c>
+      <c r="B253" t="s">
+        <v>464</v>
+      </c>
+      <c r="C253" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
+      <c r="A254" t="s">
+        <v>101</v>
+      </c>
+      <c r="B254" t="s">
+        <v>466</v>
+      </c>
+      <c r="C254" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
+      <c r="A255" t="s">
+        <v>101</v>
+      </c>
+      <c r="B255" t="s">
+        <v>468</v>
+      </c>
+      <c r="C255" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
+      <c r="A256" t="s">
+        <v>101</v>
+      </c>
+      <c r="B256" t="s">
+        <v>109</v>
+      </c>
+      <c r="C256" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3">
+      <c r="A257" t="s">
+        <v>101</v>
+      </c>
+      <c r="B257" t="s">
+        <v>470</v>
+      </c>
+      <c r="C257" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258" t="s">
+        <v>101</v>
+      </c>
+      <c r="B258" t="s">
+        <v>161</v>
+      </c>
+      <c r="C258" t="s">
+        <v>472</v>
       </c>
     </row>
   </sheetData>
@@ -6049,7 +6430,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="22" customWidth="1"/>
@@ -6059,19 +6440,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>449</v>
+        <v>477</v>
       </c>
     </row>
     <row r="2" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6079,16 +6460,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>450</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6096,16 +6477,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6113,16 +6494,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6130,16 +6511,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6147,16 +6528,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6164,16 +6545,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>455</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6181,16 +6562,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>51</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>456</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6198,16 +6579,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>459</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6215,16 +6596,16 @@
         <v>4</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>461</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6232,16 +6613,16 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>462</v>
+        <v>490</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6249,16 +6630,16 @@
         <v>69</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6266,16 +6647,16 @@
         <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
     </row>
     <row r="14" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6283,16 +6664,16 @@
         <v>69</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>466</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6300,16 +6681,16 @@
         <v>69</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>467</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6317,16 +6698,16 @@
         <v>69</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
     </row>
     <row r="17" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6334,16 +6715,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>468</v>
+        <v>496</v>
       </c>
     </row>
     <row r="18" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6351,16 +6732,16 @@
         <v>20</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>469</v>
+        <v>497</v>
       </c>
     </row>
     <row r="19" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6368,16 +6749,16 @@
         <v>24</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6385,16 +6766,16 @@
         <v>24</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>471</v>
+        <v>499</v>
       </c>
     </row>
     <row r="21" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6402,16 +6783,16 @@
         <v>24</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>472</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6419,16 +6800,16 @@
         <v>24</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>473</v>
+        <v>501</v>
       </c>
     </row>
     <row r="23" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6436,16 +6817,16 @@
         <v>27</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
     </row>
     <row r="24" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6453,16 +6834,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>474</v>
+        <v>502</v>
       </c>
     </row>
     <row r="25" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6470,16 +6851,16 @@
         <v>30</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6487,16 +6868,16 @@
         <v>30</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>475</v>
+        <v>503</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>476</v>
+        <v>504</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:5">
@@ -6504,16 +6885,16 @@
         <v>33</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>87</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>477</v>
+        <v>505</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:5">
@@ -6521,16 +6902,16 @@
         <v>33</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>69</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>478</v>
+        <v>506</v>
       </c>
     </row>
     <row r="29" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6538,16 +6919,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
     </row>
     <row r="30" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6555,16 +6936,16 @@
         <v>37</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>479</v>
+        <v>507</v>
       </c>
     </row>
     <row r="31" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6572,16 +6953,16 @@
         <v>37</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>480</v>
+        <v>508</v>
       </c>
     </row>
     <row r="32" ht="30" hidden="1" customHeight="1" spans="1:5">
@@ -6589,16 +6970,16 @@
         <v>8</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>481</v>
+        <v>509</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>482</v>
+        <v>510</v>
       </c>
     </row>
     <row r="33" hidden="1" spans="1:5">
@@ -6606,16 +6987,16 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s">
         <v>60</v>
       </c>
       <c r="D33" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E33" t="s">
-        <v>483</v>
+        <v>511</v>
       </c>
     </row>
     <row r="34" hidden="1" spans="1:5">
@@ -6623,16 +7004,16 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C34" t="s">
-        <v>484</v>
+        <v>512</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E34" t="s">
-        <v>485</v>
+        <v>513</v>
       </c>
     </row>
     <row r="35" hidden="1" spans="1:5">
@@ -6640,16 +7021,16 @@
         <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E35" t="s">
-        <v>486</v>
+        <v>514</v>
       </c>
     </row>
     <row r="36" hidden="1" spans="1:5">
@@ -6657,16 +7038,16 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C36" t="s">
         <v>60</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E36" t="s">
-        <v>487</v>
+        <v>515</v>
       </c>
     </row>
     <row r="37" hidden="1" spans="1:5">
@@ -6674,16 +7055,16 @@
         <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C37" t="s">
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E37" t="s">
-        <v>488</v>
+        <v>516</v>
       </c>
     </row>
     <row r="38" hidden="1" spans="1:5">
@@ -6691,16 +7072,16 @@
         <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E38" t="s">
-        <v>489</v>
+        <v>517</v>
       </c>
     </row>
     <row r="39" hidden="1" spans="1:5">
@@ -6708,16 +7089,16 @@
         <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C39" t="s">
         <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>490</v>
+        <v>518</v>
       </c>
     </row>
     <row r="40" hidden="1" spans="1:5">
@@ -6725,16 +7106,16 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C40" t="s">
         <v>73</v>
       </c>
       <c r="D40" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E40" t="s">
-        <v>491</v>
+        <v>519</v>
       </c>
     </row>
     <row r="41" hidden="1" spans="1:5">
@@ -6742,16 +7123,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E41" t="s">
-        <v>492</v>
+        <v>520</v>
       </c>
     </row>
     <row r="42" hidden="1" spans="1:5">
@@ -6759,16 +7140,16 @@
         <v>73</v>
       </c>
       <c r="B42" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
       </c>
       <c r="D42" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E42" t="s">
-        <v>493</v>
+        <v>521</v>
       </c>
     </row>
     <row r="43" hidden="1" spans="1:5">
@@ -6776,16 +7157,16 @@
         <v>73</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E43" t="s">
-        <v>494</v>
+        <v>522</v>
       </c>
     </row>
     <row r="44" hidden="1" spans="1:5">
@@ -6793,16 +7174,16 @@
         <v>77</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C44" t="s">
         <v>40</v>
       </c>
       <c r="D44" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E44" t="s">
-        <v>495</v>
+        <v>523</v>
       </c>
     </row>
     <row r="45" hidden="1" spans="1:5">
@@ -6810,16 +7191,16 @@
         <v>77</v>
       </c>
       <c r="B45" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C45" t="s">
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E45" t="s">
-        <v>495</v>
+        <v>523</v>
       </c>
     </row>
     <row r="46" hidden="1" spans="1:5">
@@ -6827,16 +7208,16 @@
         <v>81</v>
       </c>
       <c r="B46" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E46" t="s">
-        <v>496</v>
+        <v>524</v>
       </c>
     </row>
     <row r="47" hidden="1" spans="1:5">
@@ -6844,16 +7225,16 @@
         <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C47" t="s">
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E47" t="s">
-        <v>496</v>
+        <v>524</v>
       </c>
     </row>
     <row r="48" hidden="1" spans="1:5">
@@ -6861,16 +7242,16 @@
         <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C48" t="s">
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E48" t="s">
-        <v>496</v>
+        <v>524</v>
       </c>
     </row>
     <row r="49" hidden="1" spans="1:5">
@@ -6878,16 +7259,16 @@
         <v>73</v>
       </c>
       <c r="B49" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C49" t="s">
         <v>81</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E49" t="s">
-        <v>496</v>
+        <v>524</v>
       </c>
     </row>
     <row r="50" hidden="1" spans="1:5">
@@ -6895,16 +7276,16 @@
         <v>87</v>
       </c>
       <c r="B50" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C50" t="s">
         <v>69</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E50" t="s">
-        <v>497</v>
+        <v>525</v>
       </c>
     </row>
     <row r="51" hidden="1" spans="1:5">
@@ -6912,16 +7293,16 @@
         <v>87</v>
       </c>
       <c r="B51" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C51" t="s">
         <v>60</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E51" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
     </row>
     <row r="52" hidden="1" spans="1:5">
@@ -6929,16 +7310,16 @@
         <v>87</v>
       </c>
       <c r="B52" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E52" t="s">
-        <v>498</v>
+        <v>526</v>
       </c>
     </row>
     <row r="53" hidden="1" spans="1:5">
@@ -6946,16 +7327,16 @@
         <v>87</v>
       </c>
       <c r="B53" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C53" t="s">
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E53" t="s">
-        <v>499</v>
+        <v>527</v>
       </c>
     </row>
     <row r="54" hidden="1" spans="1:5">
@@ -6963,16 +7344,16 @@
         <v>87</v>
       </c>
       <c r="B54" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E54" t="s">
-        <v>500</v>
+        <v>528</v>
       </c>
     </row>
     <row r="55" hidden="1" spans="1:5">
@@ -6980,16 +7361,16 @@
         <v>87</v>
       </c>
       <c r="B55" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E55" t="s">
-        <v>501</v>
+        <v>529</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -6997,16 +7378,16 @@
         <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C56" t="s">
         <v>87</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E56" t="s">
-        <v>502</v>
+        <v>530</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -7014,16 +7395,16 @@
         <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C57" t="s">
         <v>69</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E57" t="s">
-        <v>478</v>
+        <v>506</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -7031,16 +7412,16 @@
         <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
         <v>60</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E58" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -7048,16 +7429,16 @@
         <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E59" t="s">
-        <v>503</v>
+        <v>531</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -7065,16 +7446,16 @@
         <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C60" t="s">
         <v>12</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E60" t="s">
-        <v>504</v>
+        <v>532</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -7082,16 +7463,16 @@
         <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E61" t="s">
-        <v>505</v>
+        <v>533</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -7099,16 +7480,16 @@
         <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C62" t="s">
         <v>12</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E62" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -7116,16 +7497,16 @@
         <v>93</v>
       </c>
       <c r="B63" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="C63" t="s">
         <v>33</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E63" t="s">
-        <v>507</v>
+        <v>535</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -7133,16 +7514,16 @@
         <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C64" t="s">
         <v>87</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E64" t="s">
-        <v>508</v>
+        <v>536</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -7150,16 +7531,16 @@
         <v>93</v>
       </c>
       <c r="B65" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C65" t="s">
         <v>12</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E65" t="s">
-        <v>509</v>
+        <v>537</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -7167,16 +7548,16 @@
         <v>93</v>
       </c>
       <c r="B66" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C66" t="s">
         <v>12</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E66" t="s">
-        <v>510</v>
+        <v>538</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -7184,16 +7565,16 @@
         <v>93</v>
       </c>
       <c r="B67" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C67" t="s">
         <v>12</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E67" t="s">
-        <v>511</v>
+        <v>539</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -7201,16 +7582,16 @@
         <v>93</v>
       </c>
       <c r="B68" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E68" t="s">
-        <v>512</v>
+        <v>540</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -7218,16 +7599,16 @@
         <v>93</v>
       </c>
       <c r="B69" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C69" t="s">
         <v>12</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E69" t="s">
-        <v>513</v>
+        <v>541</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -7235,16 +7616,30 @@
         <v>93</v>
       </c>
       <c r="B70" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E70" t="s">
-        <v>514</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>101</v>
+      </c>
+      <c r="B71" t="s">
+        <v>461</v>
+      </c>
+      <c r="C71" t="s">
+        <v>97</v>
+      </c>
+      <c r="E71" t="s">
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -7264,7 +7659,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="34.6666666666667" customWidth="1"/>
@@ -7277,10 +7672,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>515</v>
+        <v>544</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>516</v>
+        <v>545</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -7288,10 +7683,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>517</v>
+        <v>546</v>
       </c>
       <c r="C2" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7299,10 +7694,10 @@
         <v>69</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>519</v>
+        <v>548</v>
       </c>
       <c r="C3" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7310,10 +7705,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>520</v>
+        <v>549</v>
       </c>
       <c r="C4" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -7321,10 +7716,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>521</v>
+        <v>550</v>
       </c>
       <c r="C5" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7332,10 +7727,10 @@
         <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>522</v>
+        <v>551</v>
       </c>
       <c r="C6" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7343,10 +7738,10 @@
         <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>522</v>
+        <v>551</v>
       </c>
       <c r="C7" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7354,10 +7749,10 @@
         <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>523</v>
+        <v>552</v>
       </c>
       <c r="C8" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" ht="28.8" spans="1:3">
@@ -7365,10 +7760,10 @@
         <v>60</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>524</v>
+        <v>553</v>
       </c>
       <c r="C9" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7376,10 +7771,10 @@
         <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="C10" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7387,10 +7782,10 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="C11" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7398,10 +7793,10 @@
         <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>527</v>
+        <v>556</v>
       </c>
       <c r="C12" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -7409,10 +7804,10 @@
         <v>44</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>528</v>
+        <v>557</v>
       </c>
       <c r="C13" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -7420,10 +7815,10 @@
         <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>529</v>
+        <v>558</v>
       </c>
       <c r="C14" t="s">
-        <v>530</v>
+        <v>559</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -7431,32 +7826,32 @@
         <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>531</v>
+        <v>560</v>
       </c>
       <c r="C15" t="s">
-        <v>530</v>
+        <v>559</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>532</v>
+        <v>561</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>533</v>
+        <v>562</v>
       </c>
       <c r="C16" t="s">
-        <v>534</v>
+        <v>563</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>535</v>
+        <v>564</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>536</v>
+        <v>565</v>
       </c>
       <c r="C17" t="s">
-        <v>534</v>
+        <v>563</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -7464,10 +7859,10 @@
         <v>63</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>537</v>
+        <v>566</v>
       </c>
       <c r="C18" t="s">
-        <v>530</v>
+        <v>559</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -7475,10 +7870,10 @@
         <v>66</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>538</v>
+        <v>567</v>
       </c>
       <c r="C19" t="s">
-        <v>530</v>
+        <v>559</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7486,10 +7881,10 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>539</v>
+        <v>568</v>
       </c>
       <c r="C20" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -7497,10 +7892,10 @@
         <v>77</v>
       </c>
       <c r="B21" t="s">
-        <v>540</v>
+        <v>569</v>
       </c>
       <c r="C21" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7508,10 +7903,10 @@
         <v>81</v>
       </c>
       <c r="B22" t="s">
-        <v>541</v>
+        <v>570</v>
       </c>
       <c r="C22" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7519,10 +7914,10 @@
         <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>542</v>
+        <v>571</v>
       </c>
       <c r="C23" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7530,10 +7925,10 @@
         <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="C24" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -7541,10 +7936,10 @@
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>544</v>
+        <v>573</v>
       </c>
       <c r="C25" t="s">
-        <v>518</v>
+        <v>547</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7552,10 +7947,32 @@
         <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>545</v>
+        <v>574</v>
       </c>
       <c r="C26" t="s">
-        <v>518</v>
+        <v>547</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>575</v>
+      </c>
+      <c r="C27" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" t="s">
+        <v>576</v>
+      </c>
+      <c r="C28" t="s">
+        <v>559</v>
       </c>
     </row>
   </sheetData>
